--- a/HelloFresh_Absorption_Fall2025.xlsx
+++ b/HelloFresh_Absorption_Fall2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/stn424_ads_northwestern_edu/Documents/Collaborations/Proposals/GO-Barrier, TFMI Proposals with Tim Wei/URAP_2023-10/Shared/Lanning, Mackenzie/Absorption Data/Fall 2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1553" documentId="13_ncr:1_{F2E763B4-4DB6-894B-B240-8188D6068E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{385178CF-0706-704A-8E7B-D8A542AC8FA8}"/>
+  <xr:revisionPtr revIDLastSave="1712" documentId="13_ncr:1_{F2E763B4-4DB6-894B-B240-8188D6068E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8CEF8C6-F78E-8742-AFFB-1CA691E0992F}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17180" activeTab="4" xr2:uid="{304DC28A-0BB6-064B-B35E-217EA1A1C90F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17180" activeTab="5" xr2:uid="{304DC28A-0BB6-064B-B35E-217EA1A1C90F}"/>
   </bookViews>
   <sheets>
     <sheet name="Crayola Method" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="Boat Method (Retest)" sheetId="4" r:id="rId3"/>
     <sheet name="Metsä EB" sheetId="3" r:id="rId4"/>
     <sheet name="Formatting for R" sheetId="5" r:id="rId5"/>
+    <sheet name="Figures for R" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="56">
   <si>
     <t>Raw Weights (gms)</t>
   </si>
@@ -200,6 +201,15 @@
   <si>
     <t>25% WBBC + 0.1% GO</t>
   </si>
+  <si>
+    <t>Absorption</t>
+  </si>
+  <si>
+    <t>RMS</t>
+  </si>
+  <si>
+    <t>0.2% GO</t>
+  </si>
 </sst>
 </file>
 
@@ -347,16 +357,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -29409,24 +29419,24 @@
       <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
     </row>
     <row r="3" spans="1:18" ht="51" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -31368,24 +31378,24 @@
       <c r="P46" s="5"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A47" s="26" t="s">
+      <c r="A47" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="26"/>
-      <c r="K47" s="26"/>
-      <c r="L47" s="26"/>
-      <c r="M47" s="26"/>
-      <c r="N47" s="26"/>
-      <c r="O47" s="26"/>
-      <c r="P47" s="26"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
+      <c r="N47" s="29"/>
+      <c r="O47" s="29"/>
+      <c r="P47" s="29"/>
     </row>
     <row r="48" spans="1:16" ht="51" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
@@ -33853,7 +33863,7 @@
         <v>1.3870523415977965E-2</v>
       </c>
       <c r="E95" s="7">
-        <f t="shared" si="112"/>
+        <f xml:space="preserve"> AVERAGE(E55:E59)</f>
         <v>5.7851239669421493E-3</v>
       </c>
       <c r="F95" s="7">
@@ -34148,7 +34158,7 @@
         <v>1.9972451790633609E-2</v>
       </c>
       <c r="E100" s="7">
-        <f t="shared" si="127"/>
+        <f xml:space="preserve"> AVERAGE(E85:E89)</f>
         <v>9.4490358126721775E-3</v>
       </c>
       <c r="F100" s="7">
@@ -34168,7 +34178,7 @@
         <v>3.1404958677685954E-3</v>
       </c>
       <c r="J100" s="7">
-        <f t="shared" si="127"/>
+        <f xml:space="preserve"> AVERAGE(J85:J89)</f>
         <v>2.9201101928374683E-3</v>
       </c>
       <c r="K100" s="7">
@@ -35060,7 +35070,7 @@
         <v>1.6643060128473974</v>
       </c>
       <c r="E120" s="7">
-        <f t="shared" si="163"/>
+        <f>AVERAGE(E73:E77)*32.258/AVERAGE(E4:E8)</f>
         <v>0.77807493552213003</v>
       </c>
       <c r="F120" s="7">
@@ -35751,13 +35761,13 @@
       <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -36925,13 +36935,13 @@
       <c r="H52" s="4"/>
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A53" s="26" t="s">
+      <c r="A53" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="29"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -40093,13 +40103,13 @@
       <c r="H1" s="2"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -42018,13 +42028,13 @@
       <c r="R52" s="5"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A53" s="26" t="s">
+      <c r="A53" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="26"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="29"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
@@ -45850,7 +45860,7 @@
         <v>0.3111973135710977</v>
       </c>
       <c r="J132" s="7">
-        <f t="shared" ref="I132:M132" si="220">AVERAGE(J67:J71)*25.8/AVERAGE(J4:J8)</f>
+        <f t="shared" ref="J132:M132" si="220">AVERAGE(J67:J71)*25.8/AVERAGE(J4:J8)</f>
         <v>0.31239990147249735</v>
       </c>
       <c r="K132" s="7">
@@ -46098,11 +46108,11 @@
       </c>
       <c r="H136" s="7"/>
       <c r="I136" s="7">
-        <f t="shared" ref="I136:M136" si="236">AVERAGE(I91:I95)*25.8/AVERAGE(I4:I8)</f>
+        <f>AVERAGE(I91:I95)*25.8/AVERAGE(I4:I8)</f>
         <v>0.35677424296025051</v>
       </c>
       <c r="J136" s="7">
-        <f t="shared" si="236"/>
+        <f t="shared" ref="I136:M136" si="236">AVERAGE(J91:J95)*25.8/AVERAGE(J4:J8)</f>
         <v>0.35096779054317595</v>
       </c>
       <c r="K136" s="7">
@@ -46297,7 +46307,7 @@
         <v>10</v>
       </c>
       <c r="C143" s="7">
-        <f t="shared" ref="C143:E143" si="243" xml:space="preserve"> STDEV(C61:C65)*22.58/AVERAGE(C4:C8)</f>
+        <f xml:space="preserve"> STDEV(C61:C65)*22.58/AVERAGE(C4:C8)</f>
         <v>9.5627734622863361E-3</v>
       </c>
       <c r="D143" s="7">
@@ -46305,7 +46315,7 @@
         <v>0.12723213842582981</v>
       </c>
       <c r="E143" s="7">
-        <f t="shared" si="243"/>
+        <f t="shared" ref="C143:E143" si="243" xml:space="preserve"> STDEV(E61:E65)*22.58/AVERAGE(E4:E8)</f>
         <v>0.10299723685496648</v>
       </c>
       <c r="F143" s="7">
@@ -46381,11 +46391,11 @@
       </c>
       <c r="H144" s="7"/>
       <c r="I144" s="7">
-        <f t="shared" ref="I144:M144" si="250" xml:space="preserve"> STDEV(I67:I71)*22.58/AVERAGE(I4:I8)</f>
+        <f xml:space="preserve"> STDEV(I67:I71)*22.58/AVERAGE(I4:I8)</f>
         <v>9.9438732493841893E-3</v>
       </c>
       <c r="J144" s="7">
-        <f t="shared" si="250"/>
+        <f t="shared" ref="I144:M144" si="250" xml:space="preserve"> STDEV(J67:J71)*22.58/AVERAGE(J4:J8)</f>
         <v>1.5473952385165919E-2</v>
       </c>
       <c r="K144" s="7">
@@ -46979,24 +46989,24 @@
       <c r="P1" s="3"/>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
-      <c r="M2" s="25"/>
-      <c r="N2" s="25"/>
-      <c r="O2" s="25"/>
-      <c r="P2" s="25"/>
+      <c r="B2" s="28"/>
+      <c r="C2" s="28"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
+      <c r="L2" s="28"/>
+      <c r="M2" s="28"/>
+      <c r="N2" s="28"/>
+      <c r="O2" s="28"/>
+      <c r="P2" s="28"/>
     </row>
     <row r="3" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -48223,24 +48233,24 @@
       <c r="P46" s="5"/>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.2">
-      <c r="A47" s="26" t="s">
+      <c r="A47" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
-      <c r="D47" s="26"/>
-      <c r="E47" s="26"/>
-      <c r="F47" s="26"/>
-      <c r="G47" s="26"/>
-      <c r="H47" s="26"/>
-      <c r="I47" s="26"/>
-      <c r="J47" s="26"/>
-      <c r="K47" s="26"/>
-      <c r="L47" s="26"/>
-      <c r="M47" s="26"/>
-      <c r="N47" s="26"/>
-      <c r="O47" s="26"/>
-      <c r="P47" s="26"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
+      <c r="N47" s="29"/>
+      <c r="O47" s="29"/>
+      <c r="P47" s="29"/>
     </row>
     <row r="48" spans="1:16" ht="34" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
@@ -50725,13 +50735,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="25" t="s">
         <v>50</v>
       </c>
     </row>
@@ -50739,7 +50749,7 @@
       <c r="A2" s="4">
         <v>0</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C2" s="10">
@@ -50750,7 +50760,7 @@
       <c r="A3" s="4">
         <v>0</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C3" s="10">
@@ -50761,7 +50771,7 @@
       <c r="A4" s="4">
         <v>0</v>
       </c>
-      <c r="B4" s="28" t="s">
+      <c r="B4" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C4" s="10">
@@ -50772,7 +50782,7 @@
       <c r="A5" s="4">
         <v>0</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C5" s="10">
@@ -50783,7 +50793,7 @@
       <c r="A6" s="4">
         <v>0</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C6" s="10">
@@ -50794,7 +50804,7 @@
       <c r="A7" s="5">
         <v>10</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C7" s="10">
@@ -50805,7 +50815,7 @@
       <c r="A8" s="5">
         <v>10</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C8" s="10">
@@ -50816,7 +50826,7 @@
       <c r="A9" s="5">
         <v>10</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C9" s="10">
@@ -50827,7 +50837,7 @@
       <c r="A10" s="5">
         <v>10</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C10" s="10">
@@ -50838,7 +50848,7 @@
       <c r="A11" s="5">
         <v>10</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C11" s="10">
@@ -50849,7 +50859,7 @@
       <c r="A12" s="5">
         <v>20</v>
       </c>
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C12" s="10">
@@ -50860,7 +50870,7 @@
       <c r="A13" s="5">
         <v>20</v>
       </c>
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C13" s="10">
@@ -50871,7 +50881,7 @@
       <c r="A14" s="5">
         <v>20</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C14" s="10">
@@ -50882,7 +50892,7 @@
       <c r="A15" s="5">
         <v>20</v>
       </c>
-      <c r="B15" s="28" t="s">
+      <c r="B15" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C15" s="10">
@@ -50893,7 +50903,7 @@
       <c r="A16" s="5">
         <v>20</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C16" s="10">
@@ -50904,7 +50914,7 @@
       <c r="A17" s="5">
         <v>30</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C17" s="10">
@@ -50915,7 +50925,7 @@
       <c r="A18" s="5">
         <v>30</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C18" s="10">
@@ -50926,7 +50936,7 @@
       <c r="A19" s="5">
         <v>30</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B19" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C19" s="10">
@@ -50937,7 +50947,7 @@
       <c r="A20" s="5">
         <v>30</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C20" s="10">
@@ -50948,7 +50958,7 @@
       <c r="A21" s="5">
         <v>30</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C21" s="10">
@@ -50959,7 +50969,7 @@
       <c r="A22" s="5">
         <v>40</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C22" s="10">
@@ -50970,7 +50980,7 @@
       <c r="A23" s="5">
         <v>40</v>
       </c>
-      <c r="B23" s="28" t="s">
+      <c r="B23" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C23" s="10">
@@ -50981,1071 +50991,1071 @@
       <c r="A24" s="5">
         <v>40</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C24" s="10">
         <v>0.48699999999999999</v>
       </c>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="29"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26"/>
+      <c r="H24" s="27"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="5">
         <v>40</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C25" s="10">
         <v>0.46500000000000002</v>
       </c>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="29"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26"/>
+      <c r="H25" s="27"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="5">
         <v>40</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C26" s="10">
         <v>0.502</v>
       </c>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
+      <c r="F26" s="26"/>
+      <c r="G26" s="26"/>
+      <c r="H26" s="27"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="5">
         <v>50</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C27" s="10">
         <v>0.48799999999999999</v>
       </c>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="29"/>
+      <c r="F27" s="26"/>
+      <c r="G27" s="26"/>
+      <c r="H27" s="27"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="5">
         <v>50</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C28" s="10">
         <v>0.48499999999999999</v>
       </c>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="29"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26"/>
+      <c r="H28" s="27"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="5">
         <v>50</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C29" s="10">
         <v>0.501</v>
       </c>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="29"/>
+      <c r="F29" s="26"/>
+      <c r="G29" s="26"/>
+      <c r="H29" s="27"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="5">
         <v>50</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C30" s="10">
         <v>0.47</v>
       </c>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
+      <c r="F30" s="26"/>
+      <c r="G30" s="26"/>
       <c r="H30" s="23"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="5">
         <v>50</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C31" s="10">
         <v>0.50600000000000001</v>
       </c>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
+      <c r="F31" s="26"/>
+      <c r="G31" s="26"/>
       <c r="H31" s="23"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="5">
         <v>60</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C32" s="10">
         <v>0.496</v>
       </c>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
+      <c r="F32" s="26"/>
+      <c r="G32" s="26"/>
       <c r="H32" s="23"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="5">
         <v>60</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C33" s="10">
         <v>0.49</v>
       </c>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28"/>
+      <c r="F33" s="26"/>
+      <c r="G33" s="26"/>
       <c r="H33" s="23"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="5">
         <v>60</v>
       </c>
-      <c r="B34" s="28" t="s">
+      <c r="B34" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C34" s="10">
         <v>0.505</v>
       </c>
-      <c r="F34" s="28"/>
-      <c r="G34" s="28"/>
+      <c r="F34" s="26"/>
+      <c r="G34" s="26"/>
       <c r="H34" s="23"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="5">
         <v>60</v>
       </c>
-      <c r="B35" s="28" t="s">
+      <c r="B35" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C35" s="10">
         <v>0.47699999999999998</v>
       </c>
-      <c r="F35" s="28"/>
-      <c r="G35" s="28"/>
+      <c r="F35" s="26"/>
+      <c r="G35" s="26"/>
       <c r="H35" s="23"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="5">
         <v>60</v>
       </c>
-      <c r="B36" s="28" t="s">
+      <c r="B36" s="26" t="s">
         <v>40</v>
       </c>
       <c r="C36" s="10">
         <v>0.51600000000000001</v>
       </c>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
+      <c r="F36" s="26"/>
+      <c r="G36" s="26"/>
       <c r="H36" s="23"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4">
         <v>0</v>
       </c>
-      <c r="B37" s="28" t="s">
+      <c r="B37" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C37" s="10">
         <v>0.34100000000000003</v>
       </c>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="29"/>
+      <c r="F37" s="26"/>
+      <c r="G37" s="26"/>
+      <c r="H37" s="27"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="4">
         <v>0</v>
       </c>
-      <c r="B38" s="28" t="s">
+      <c r="B38" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C38" s="10">
         <v>0.34</v>
       </c>
-      <c r="F38" s="28"/>
-      <c r="G38" s="28"/>
-      <c r="H38" s="29"/>
+      <c r="F38" s="26"/>
+      <c r="G38" s="26"/>
+      <c r="H38" s="27"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="4">
         <v>0</v>
       </c>
-      <c r="B39" s="28" t="s">
+      <c r="B39" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C39" s="10">
         <v>0.33600000000000002</v>
       </c>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="29"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="27"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="4">
         <v>0</v>
       </c>
-      <c r="B40" s="28" t="s">
+      <c r="B40" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C40" s="10">
         <v>0.33600000000000002</v>
       </c>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="29"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="27"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="4">
         <v>0</v>
       </c>
-      <c r="B41" s="28" t="s">
+      <c r="B41" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C41" s="10">
         <v>0.33100000000000002</v>
       </c>
-      <c r="F41" s="28"/>
-      <c r="G41" s="28"/>
-      <c r="H41" s="29"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="27"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="5">
         <v>10</v>
       </c>
-      <c r="B42" s="28" t="s">
+      <c r="B42" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C42" s="10">
         <v>0.47899999999999998</v>
       </c>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="29"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="27"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="5">
         <v>10</v>
       </c>
-      <c r="B43" s="28" t="s">
+      <c r="B43" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C43" s="10">
         <v>0.54100000000000004</v>
       </c>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="29"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26"/>
+      <c r="H43" s="27"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="5">
         <v>10</v>
       </c>
-      <c r="B44" s="28" t="s">
+      <c r="B44" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C44" s="10">
         <v>0.61599999999999999</v>
       </c>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28"/>
-      <c r="H44" s="29"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26"/>
+      <c r="H44" s="27"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="5">
         <v>10</v>
       </c>
-      <c r="B45" s="28" t="s">
+      <c r="B45" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C45" s="10">
         <v>0.46300000000000002</v>
       </c>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="29"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="27"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="5">
         <v>10</v>
       </c>
-      <c r="B46" s="28" t="s">
+      <c r="B46" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C46" s="10">
         <v>0.504</v>
       </c>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="29"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26"/>
+      <c r="H46" s="27"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="5">
         <v>20</v>
       </c>
-      <c r="B47" s="28" t="s">
+      <c r="B47" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C47" s="10">
         <v>0.51900000000000002</v>
       </c>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="29"/>
+      <c r="F47" s="26"/>
+      <c r="G47" s="26"/>
+      <c r="H47" s="27"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="5">
         <v>20</v>
       </c>
-      <c r="B48" s="28" t="s">
+      <c r="B48" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C48" s="10">
         <v>0.6</v>
       </c>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28"/>
-      <c r="H48" s="29"/>
+      <c r="F48" s="26"/>
+      <c r="G48" s="26"/>
+      <c r="H48" s="27"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="5">
         <v>20</v>
       </c>
-      <c r="B49" s="28" t="s">
+      <c r="B49" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C49" s="10">
         <v>0.63700000000000001</v>
       </c>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="29"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26"/>
+      <c r="H49" s="27"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="5">
         <v>20</v>
       </c>
-      <c r="B50" s="28" t="s">
+      <c r="B50" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C50" s="10">
         <v>0.48</v>
       </c>
-      <c r="F50" s="28"/>
-      <c r="G50" s="28"/>
-      <c r="H50" s="29"/>
+      <c r="F50" s="26"/>
+      <c r="G50" s="26"/>
+      <c r="H50" s="27"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="5">
         <v>20</v>
       </c>
-      <c r="B51" s="28" t="s">
+      <c r="B51" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C51" s="10">
         <v>0.53300000000000003</v>
       </c>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="29"/>
+      <c r="F51" s="26"/>
+      <c r="G51" s="26"/>
+      <c r="H51" s="27"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="5">
         <v>30</v>
       </c>
-      <c r="B52" s="28" t="s">
+      <c r="B52" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C52" s="10">
         <v>0.51800000000000002</v>
       </c>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="29"/>
+      <c r="F52" s="26"/>
+      <c r="G52" s="26"/>
+      <c r="H52" s="27"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="5">
         <v>30</v>
       </c>
-      <c r="B53" s="28" t="s">
+      <c r="B53" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C53" s="10">
         <v>0.61199999999999999</v>
       </c>
-      <c r="F53" s="28"/>
-      <c r="G53" s="28"/>
-      <c r="H53" s="29"/>
+      <c r="F53" s="26"/>
+      <c r="G53" s="26"/>
+      <c r="H53" s="27"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="5">
         <v>30</v>
       </c>
-      <c r="B54" s="28" t="s">
+      <c r="B54" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C54" s="10">
         <v>0.63800000000000001</v>
       </c>
-      <c r="F54" s="28"/>
-      <c r="G54" s="28"/>
-      <c r="H54" s="29"/>
+      <c r="F54" s="26"/>
+      <c r="G54" s="26"/>
+      <c r="H54" s="27"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="5">
         <v>30</v>
       </c>
-      <c r="B55" s="28" t="s">
+      <c r="B55" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C55" s="10">
         <v>0.48199999999999998</v>
       </c>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="29"/>
+      <c r="F55" s="26"/>
+      <c r="G55" s="26"/>
+      <c r="H55" s="27"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="5">
         <v>30</v>
       </c>
-      <c r="B56" s="28" t="s">
+      <c r="B56" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C56" s="10">
         <v>0.56000000000000005</v>
       </c>
-      <c r="F56" s="28"/>
-      <c r="G56" s="28"/>
-      <c r="H56" s="29"/>
+      <c r="F56" s="26"/>
+      <c r="G56" s="26"/>
+      <c r="H56" s="27"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="5">
         <v>40</v>
       </c>
-      <c r="B57" s="28" t="s">
+      <c r="B57" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C57" s="10">
         <v>0.53400000000000003</v>
       </c>
-      <c r="F57" s="28"/>
-      <c r="G57" s="28"/>
-      <c r="H57" s="29"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26"/>
+      <c r="H57" s="27"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="5">
         <v>40</v>
       </c>
-      <c r="B58" s="28" t="s">
+      <c r="B58" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C58" s="10">
         <v>0.627</v>
       </c>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="29"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26"/>
+      <c r="H58" s="27"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="5">
         <v>40</v>
       </c>
-      <c r="B59" s="28" t="s">
+      <c r="B59" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C59" s="10">
         <v>0.65</v>
       </c>
-      <c r="F59" s="28"/>
-      <c r="G59" s="28"/>
-      <c r="H59" s="29"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26"/>
+      <c r="H59" s="27"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="5">
         <v>40</v>
       </c>
-      <c r="B60" s="28" t="s">
+      <c r="B60" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C60" s="10">
         <v>0.50800000000000001</v>
       </c>
-      <c r="F60" s="28"/>
-      <c r="G60" s="28"/>
-      <c r="H60" s="29"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26"/>
+      <c r="H60" s="27"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="5">
         <v>40</v>
       </c>
-      <c r="B61" s="28" t="s">
+      <c r="B61" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C61" s="10">
         <v>0.57299999999999995</v>
       </c>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="29"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26"/>
+      <c r="H61" s="27"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="5">
         <v>50</v>
       </c>
-      <c r="B62" s="28" t="s">
+      <c r="B62" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C62" s="10">
         <v>0.55200000000000005</v>
       </c>
-      <c r="F62" s="28"/>
-      <c r="G62" s="28"/>
-      <c r="H62" s="29"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26"/>
+      <c r="H62" s="27"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="5">
         <v>50</v>
       </c>
-      <c r="B63" s="28" t="s">
+      <c r="B63" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C63" s="10">
         <v>0.63100000000000001</v>
       </c>
-      <c r="F63" s="28"/>
-      <c r="G63" s="28"/>
-      <c r="H63" s="29"/>
+      <c r="F63" s="26"/>
+      <c r="G63" s="26"/>
+      <c r="H63" s="27"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="5">
         <v>50</v>
       </c>
-      <c r="B64" s="28" t="s">
+      <c r="B64" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C64" s="10">
         <v>0.64600000000000002</v>
       </c>
-      <c r="F64" s="28"/>
-      <c r="G64" s="28"/>
-      <c r="H64" s="29"/>
+      <c r="F64" s="26"/>
+      <c r="G64" s="26"/>
+      <c r="H64" s="27"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="5">
         <v>50</v>
       </c>
-      <c r="B65" s="28" t="s">
+      <c r="B65" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C65" s="10">
         <v>0.52</v>
       </c>
-      <c r="F65" s="28"/>
-      <c r="G65" s="28"/>
-      <c r="H65" s="29"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26"/>
+      <c r="H65" s="27"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="5">
         <v>50</v>
       </c>
-      <c r="B66" s="28" t="s">
+      <c r="B66" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C66" s="10">
         <v>0.58699999999999997</v>
       </c>
-      <c r="F66" s="28"/>
-      <c r="G66" s="28"/>
-      <c r="H66" s="29"/>
+      <c r="F66" s="26"/>
+      <c r="G66" s="26"/>
+      <c r="H66" s="27"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="5">
         <v>60</v>
       </c>
-      <c r="B67" s="28" t="s">
+      <c r="B67" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C67" s="10">
         <v>0.56899999999999995</v>
       </c>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="29"/>
+      <c r="F67" s="26"/>
+      <c r="G67" s="26"/>
+      <c r="H67" s="27"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="5">
         <v>60</v>
       </c>
-      <c r="B68" s="28" t="s">
+      <c r="B68" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C68" s="10">
         <v>0.63200000000000001</v>
       </c>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28"/>
-      <c r="H68" s="29"/>
+      <c r="F68" s="26"/>
+      <c r="G68" s="26"/>
+      <c r="H68" s="27"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="5">
         <v>60</v>
       </c>
-      <c r="B69" s="28" t="s">
+      <c r="B69" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C69" s="10">
         <v>0.65600000000000003</v>
       </c>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28"/>
-      <c r="H69" s="29"/>
+      <c r="F69" s="26"/>
+      <c r="G69" s="26"/>
+      <c r="H69" s="27"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="5">
         <v>60</v>
       </c>
-      <c r="B70" s="28" t="s">
+      <c r="B70" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C70" s="10">
         <v>0.53100000000000003</v>
       </c>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="29"/>
+      <c r="F70" s="26"/>
+      <c r="G70" s="26"/>
+      <c r="H70" s="27"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="5">
         <v>60</v>
       </c>
-      <c r="B71" s="28" t="s">
+      <c r="B71" s="26" t="s">
         <v>41</v>
       </c>
       <c r="C71" s="10">
         <v>0.60499999999999998</v>
       </c>
-      <c r="F71" s="28"/>
-      <c r="G71" s="28"/>
-      <c r="H71" s="29"/>
+      <c r="F71" s="26"/>
+      <c r="G71" s="26"/>
+      <c r="H71" s="27"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="4">
         <v>0</v>
       </c>
-      <c r="B72" s="28" t="s">
+      <c r="B72" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C72" s="11">
         <v>0.33</v>
       </c>
-      <c r="F72" s="28"/>
-      <c r="G72" s="28"/>
+      <c r="F72" s="26"/>
+      <c r="G72" s="26"/>
       <c r="H72" s="23"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="4">
         <v>0</v>
       </c>
-      <c r="B73" s="28" t="s">
+      <c r="B73" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C73" s="11">
         <v>0.32500000000000001</v>
       </c>
-      <c r="F73" s="28"/>
-      <c r="G73" s="28"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26"/>
       <c r="H73" s="23"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="4">
         <v>0</v>
       </c>
-      <c r="B74" s="28" t="s">
+      <c r="B74" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C74" s="11">
         <v>0.32</v>
       </c>
-      <c r="F74" s="28"/>
-      <c r="G74" s="28"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26"/>
       <c r="H74" s="23"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="4">
         <v>0</v>
       </c>
-      <c r="B75" s="28" t="s">
+      <c r="B75" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C75" s="11">
         <v>0.32900000000000001</v>
       </c>
-      <c r="F75" s="28"/>
-      <c r="G75" s="28"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26"/>
       <c r="H75" s="23"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="4">
         <v>0</v>
       </c>
-      <c r="B76" s="28" t="s">
+      <c r="B76" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C76" s="11">
         <v>0.32800000000000001</v>
       </c>
-      <c r="F76" s="28"/>
-      <c r="G76" s="28"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26"/>
       <c r="H76" s="23"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="5">
         <v>10</v>
       </c>
-      <c r="B77" s="28" t="s">
+      <c r="B77" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C77" s="11">
         <v>0.44600000000000001</v>
       </c>
-      <c r="F77" s="28"/>
-      <c r="G77" s="28"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26"/>
       <c r="H77" s="23"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="5">
         <v>10</v>
       </c>
-      <c r="B78" s="28" t="s">
+      <c r="B78" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C78" s="11">
         <v>0.443</v>
       </c>
-      <c r="F78" s="28"/>
-      <c r="G78" s="28"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26"/>
       <c r="H78" s="23"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="5">
         <v>10</v>
       </c>
-      <c r="B79" s="28" t="s">
+      <c r="B79" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C79" s="11">
         <v>0.44600000000000001</v>
       </c>
-      <c r="F79" s="28"/>
-      <c r="G79" s="28"/>
+      <c r="F79" s="26"/>
+      <c r="G79" s="26"/>
       <c r="H79" s="23"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="5">
         <v>10</v>
       </c>
-      <c r="B80" s="28" t="s">
+      <c r="B80" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C80" s="11">
         <v>0.45100000000000001</v>
       </c>
-      <c r="F80" s="28"/>
-      <c r="G80" s="28"/>
+      <c r="F80" s="26"/>
+      <c r="G80" s="26"/>
       <c r="H80" s="23"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="5">
         <v>10</v>
       </c>
-      <c r="B81" s="28" t="s">
+      <c r="B81" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C81" s="11">
         <v>0.443</v>
       </c>
-      <c r="F81" s="28"/>
-      <c r="G81" s="28"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26"/>
       <c r="H81" s="23"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="5">
         <v>20</v>
       </c>
-      <c r="B82" s="28" t="s">
+      <c r="B82" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C82" s="11">
         <v>0.45300000000000001</v>
       </c>
-      <c r="F82" s="28"/>
-      <c r="G82" s="28"/>
+      <c r="F82" s="26"/>
+      <c r="G82" s="26"/>
       <c r="H82" s="23"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="5">
         <v>20</v>
       </c>
-      <c r="B83" s="28" t="s">
+      <c r="B83" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C83" s="11">
         <v>0.44800000000000001</v>
       </c>
-      <c r="F83" s="28"/>
-      <c r="G83" s="28"/>
+      <c r="F83" s="26"/>
+      <c r="G83" s="26"/>
       <c r="H83" s="23"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="5">
         <v>20</v>
       </c>
-      <c r="B84" s="28" t="s">
+      <c r="B84" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C84" s="11">
         <v>0.44900000000000001</v>
       </c>
-      <c r="F84" s="28"/>
-      <c r="G84" s="28"/>
+      <c r="F84" s="26"/>
+      <c r="G84" s="26"/>
       <c r="H84" s="23"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="5">
         <v>20</v>
       </c>
-      <c r="B85" s="28" t="s">
+      <c r="B85" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C85" s="11">
         <v>0.46300000000000002</v>
       </c>
-      <c r="F85" s="28"/>
-      <c r="G85" s="28"/>
+      <c r="F85" s="26"/>
+      <c r="G85" s="26"/>
       <c r="H85" s="23"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="5">
         <v>20</v>
       </c>
-      <c r="B86" s="28" t="s">
+      <c r="B86" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C86" s="11">
         <v>0.45400000000000001</v>
       </c>
-      <c r="F86" s="28"/>
-      <c r="G86" s="28"/>
+      <c r="F86" s="26"/>
+      <c r="G86" s="26"/>
       <c r="H86" s="23"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="5">
         <v>30</v>
       </c>
-      <c r="B87" s="28" t="s">
+      <c r="B87" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C87" s="11">
         <v>0.46100000000000002</v>
       </c>
-      <c r="F87" s="28"/>
-      <c r="G87" s="28"/>
+      <c r="F87" s="26"/>
+      <c r="G87" s="26"/>
       <c r="H87" s="23"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="5">
         <v>30</v>
       </c>
-      <c r="B88" s="28" t="s">
+      <c r="B88" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C88" s="11">
         <v>0.45600000000000002</v>
       </c>
-      <c r="F88" s="28"/>
-      <c r="G88" s="28"/>
+      <c r="F88" s="26"/>
+      <c r="G88" s="26"/>
       <c r="H88" s="23"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="5">
         <v>30</v>
       </c>
-      <c r="B89" s="28" t="s">
+      <c r="B89" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C89" s="11">
         <v>0.45700000000000002</v>
       </c>
-      <c r="F89" s="28"/>
-      <c r="G89" s="28"/>
+      <c r="F89" s="26"/>
+      <c r="G89" s="26"/>
       <c r="H89" s="23"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="5">
         <v>30</v>
       </c>
-      <c r="B90" s="28" t="s">
+      <c r="B90" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C90" s="11">
         <v>0.46800000000000003</v>
       </c>
-      <c r="F90" s="28"/>
-      <c r="G90" s="28"/>
+      <c r="F90" s="26"/>
+      <c r="G90" s="26"/>
       <c r="H90" s="23"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="5">
         <v>30</v>
       </c>
-      <c r="B91" s="28" t="s">
+      <c r="B91" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C91" s="11">
         <v>0.45800000000000002</v>
       </c>
-      <c r="F91" s="28"/>
-      <c r="G91" s="28"/>
+      <c r="F91" s="26"/>
+      <c r="G91" s="26"/>
       <c r="H91" s="23"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="5">
         <v>40</v>
       </c>
-      <c r="B92" s="28" t="s">
+      <c r="B92" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C92" s="11">
         <v>0.46800000000000003</v>
       </c>
-      <c r="F92" s="28"/>
-      <c r="G92" s="28"/>
+      <c r="F92" s="26"/>
+      <c r="G92" s="26"/>
       <c r="H92" s="23"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="5">
         <v>40</v>
       </c>
-      <c r="B93" s="28" t="s">
+      <c r="B93" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C93" s="11">
         <v>0.46</v>
       </c>
-      <c r="F93" s="28"/>
-      <c r="G93" s="28"/>
-      <c r="H93" s="29"/>
+      <c r="F93" s="26"/>
+      <c r="G93" s="26"/>
+      <c r="H93" s="27"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="5">
         <v>40</v>
       </c>
-      <c r="B94" s="28" t="s">
+      <c r="B94" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C94" s="11">
         <v>0.47099999999999997</v>
       </c>
-      <c r="F94" s="28"/>
-      <c r="G94" s="28"/>
-      <c r="H94" s="29"/>
+      <c r="F94" s="26"/>
+      <c r="G94" s="26"/>
+      <c r="H94" s="27"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="5">
         <v>40</v>
       </c>
-      <c r="B95" s="28" t="s">
+      <c r="B95" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C95" s="11">
         <v>0.47399999999999998</v>
       </c>
-      <c r="F95" s="28"/>
-      <c r="G95" s="28"/>
-      <c r="H95" s="29"/>
+      <c r="F95" s="26"/>
+      <c r="G95" s="26"/>
+      <c r="H95" s="27"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="5">
         <v>40</v>
       </c>
-      <c r="B96" s="28" t="s">
+      <c r="B96" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C96" s="11">
         <v>0.46400000000000002</v>
       </c>
-      <c r="F96" s="28"/>
-      <c r="G96" s="28"/>
-      <c r="H96" s="29"/>
+      <c r="F96" s="26"/>
+      <c r="G96" s="26"/>
+      <c r="H96" s="27"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="5">
         <v>50</v>
       </c>
-      <c r="B97" s="28" t="s">
+      <c r="B97" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C97" s="11">
         <v>0.47499999999999998</v>
       </c>
-      <c r="F97" s="28"/>
-      <c r="G97" s="28"/>
-      <c r="H97" s="29"/>
+      <c r="F97" s="26"/>
+      <c r="G97" s="26"/>
+      <c r="H97" s="27"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="5">
         <v>50</v>
       </c>
-      <c r="B98" s="28" t="s">
+      <c r="B98" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C98" s="11">
         <v>0.46700000000000003</v>
       </c>
-      <c r="F98" s="28"/>
-      <c r="G98" s="28"/>
-      <c r="H98" s="29"/>
+      <c r="F98" s="26"/>
+      <c r="G98" s="26"/>
+      <c r="H98" s="27"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="5">
         <v>50</v>
       </c>
-      <c r="B99" s="28" t="s">
+      <c r="B99" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C99" s="11">
         <v>0.46400000000000002</v>
       </c>
-      <c r="F99" s="28"/>
-      <c r="G99" s="28"/>
-      <c r="H99" s="29"/>
+      <c r="F99" s="26"/>
+      <c r="G99" s="26"/>
+      <c r="H99" s="27"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="5">
         <v>50</v>
       </c>
-      <c r="B100" s="28" t="s">
+      <c r="B100" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C100" s="11">
@@ -52056,7 +52066,7 @@
       <c r="A101" s="5">
         <v>50</v>
       </c>
-      <c r="B101" s="28" t="s">
+      <c r="B101" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C101" s="11">
@@ -52067,7 +52077,7 @@
       <c r="A102" s="5">
         <v>60</v>
       </c>
-      <c r="B102" s="28" t="s">
+      <c r="B102" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C102" s="11">
@@ -52078,7 +52088,7 @@
       <c r="A103" s="5">
         <v>60</v>
       </c>
-      <c r="B103" s="28" t="s">
+      <c r="B103" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C103" s="11">
@@ -52089,7 +52099,7 @@
       <c r="A104" s="5">
         <v>60</v>
       </c>
-      <c r="B104" s="28" t="s">
+      <c r="B104" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C104" s="11">
@@ -52100,7 +52110,7 @@
       <c r="A105" s="5">
         <v>60</v>
       </c>
-      <c r="B105" s="28" t="s">
+      <c r="B105" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C105" s="11">
@@ -52111,7 +52121,7 @@
       <c r="A106" s="5">
         <v>60</v>
       </c>
-      <c r="B106" s="28" t="s">
+      <c r="B106" s="26" t="s">
         <v>42</v>
       </c>
       <c r="C106" s="11">
@@ -52122,7 +52132,7 @@
       <c r="A107" s="4">
         <v>0</v>
       </c>
-      <c r="B107" s="28" t="s">
+      <c r="B107" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C107" s="11">
@@ -52133,7 +52143,7 @@
       <c r="A108" s="4">
         <v>0</v>
       </c>
-      <c r="B108" s="28" t="s">
+      <c r="B108" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C108" s="11">
@@ -52144,7 +52154,7 @@
       <c r="A109" s="4">
         <v>0</v>
       </c>
-      <c r="B109" s="28" t="s">
+      <c r="B109" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C109" s="11">
@@ -52155,7 +52165,7 @@
       <c r="A110" s="4">
         <v>0</v>
       </c>
-      <c r="B110" s="28" t="s">
+      <c r="B110" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C110" s="11">
@@ -52166,7 +52176,7 @@
       <c r="A111" s="4">
         <v>0</v>
       </c>
-      <c r="B111" s="28" t="s">
+      <c r="B111" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C111" s="11">
@@ -52177,7 +52187,7 @@
       <c r="A112" s="5">
         <v>10</v>
       </c>
-      <c r="B112" s="28" t="s">
+      <c r="B112" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C112" s="11">
@@ -52188,7 +52198,7 @@
       <c r="A113" s="5">
         <v>10</v>
       </c>
-      <c r="B113" s="28" t="s">
+      <c r="B113" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C113" s="11">
@@ -52199,7 +52209,7 @@
       <c r="A114" s="5">
         <v>10</v>
       </c>
-      <c r="B114" s="28" t="s">
+      <c r="B114" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C114" s="11">
@@ -52210,7 +52220,7 @@
       <c r="A115" s="5">
         <v>10</v>
       </c>
-      <c r="B115" s="28" t="s">
+      <c r="B115" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C115" s="11">
@@ -52221,7 +52231,7 @@
       <c r="A116" s="5">
         <v>10</v>
       </c>
-      <c r="B116" s="28" t="s">
+      <c r="B116" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C116" s="11">
@@ -52232,7 +52242,7 @@
       <c r="A117" s="5">
         <v>20</v>
       </c>
-      <c r="B117" s="28" t="s">
+      <c r="B117" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C117" s="11">
@@ -52243,7 +52253,7 @@
       <c r="A118" s="5">
         <v>20</v>
       </c>
-      <c r="B118" s="28" t="s">
+      <c r="B118" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C118" s="11">
@@ -52254,7 +52264,7 @@
       <c r="A119" s="5">
         <v>20</v>
       </c>
-      <c r="B119" s="28" t="s">
+      <c r="B119" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C119" s="11">
@@ -52265,7 +52275,7 @@
       <c r="A120" s="5">
         <v>20</v>
       </c>
-      <c r="B120" s="28" t="s">
+      <c r="B120" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C120" s="11">
@@ -52276,7 +52286,7 @@
       <c r="A121" s="5">
         <v>20</v>
       </c>
-      <c r="B121" s="28" t="s">
+      <c r="B121" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C121" s="11">
@@ -52287,7 +52297,7 @@
       <c r="A122" s="5">
         <v>30</v>
       </c>
-      <c r="B122" s="28" t="s">
+      <c r="B122" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C122" s="11">
@@ -52298,7 +52308,7 @@
       <c r="A123" s="5">
         <v>30</v>
       </c>
-      <c r="B123" s="28" t="s">
+      <c r="B123" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C123" s="11">
@@ -52309,7 +52319,7 @@
       <c r="A124" s="5">
         <v>30</v>
       </c>
-      <c r="B124" s="28" t="s">
+      <c r="B124" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C124" s="11">
@@ -52320,7 +52330,7 @@
       <c r="A125" s="5">
         <v>30</v>
       </c>
-      <c r="B125" s="28" t="s">
+      <c r="B125" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C125" s="11">
@@ -52331,7 +52341,7 @@
       <c r="A126" s="5">
         <v>30</v>
       </c>
-      <c r="B126" s="28" t="s">
+      <c r="B126" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C126" s="11">
@@ -52342,7 +52352,7 @@
       <c r="A127" s="5">
         <v>40</v>
       </c>
-      <c r="B127" s="28" t="s">
+      <c r="B127" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C127" s="11">
@@ -52353,7 +52363,7 @@
       <c r="A128" s="5">
         <v>40</v>
       </c>
-      <c r="B128" s="28" t="s">
+      <c r="B128" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C128" s="11">
@@ -52364,7 +52374,7 @@
       <c r="A129" s="5">
         <v>40</v>
       </c>
-      <c r="B129" s="28" t="s">
+      <c r="B129" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C129" s="11">
@@ -52375,7 +52385,7 @@
       <c r="A130" s="5">
         <v>40</v>
       </c>
-      <c r="B130" s="28" t="s">
+      <c r="B130" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C130" s="11">
@@ -52386,7 +52396,7 @@
       <c r="A131" s="5">
         <v>40</v>
       </c>
-      <c r="B131" s="28" t="s">
+      <c r="B131" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C131" s="11">
@@ -52397,7 +52407,7 @@
       <c r="A132" s="5">
         <v>50</v>
       </c>
-      <c r="B132" s="28" t="s">
+      <c r="B132" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C132" s="11">
@@ -52408,7 +52418,7 @@
       <c r="A133" s="5">
         <v>50</v>
       </c>
-      <c r="B133" s="28" t="s">
+      <c r="B133" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C133" s="11">
@@ -52419,7 +52429,7 @@
       <c r="A134" s="5">
         <v>50</v>
       </c>
-      <c r="B134" s="28" t="s">
+      <c r="B134" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C134" s="11">
@@ -52430,7 +52440,7 @@
       <c r="A135" s="5">
         <v>50</v>
       </c>
-      <c r="B135" s="28" t="s">
+      <c r="B135" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C135" s="11">
@@ -52441,7 +52451,7 @@
       <c r="A136" s="5">
         <v>50</v>
       </c>
-      <c r="B136" s="28" t="s">
+      <c r="B136" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C136" s="11">
@@ -52452,7 +52462,7 @@
       <c r="A137" s="5">
         <v>60</v>
       </c>
-      <c r="B137" s="28" t="s">
+      <c r="B137" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C137" s="11">
@@ -52463,7 +52473,7 @@
       <c r="A138" s="5">
         <v>60</v>
       </c>
-      <c r="B138" s="28" t="s">
+      <c r="B138" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C138" s="11">
@@ -52474,7 +52484,7 @@
       <c r="A139" s="5">
         <v>60</v>
       </c>
-      <c r="B139" s="28" t="s">
+      <c r="B139" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C139" s="11">
@@ -52485,7 +52495,7 @@
       <c r="A140" s="5">
         <v>60</v>
       </c>
-      <c r="B140" s="28" t="s">
+      <c r="B140" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C140" s="11">
@@ -52496,7 +52506,7 @@
       <c r="A141" s="5">
         <v>60</v>
       </c>
-      <c r="B141" s="28" t="s">
+      <c r="B141" s="26" t="s">
         <v>43</v>
       </c>
       <c r="C141" s="11">
@@ -52507,7 +52517,7 @@
       <c r="A142" s="4">
         <v>0</v>
       </c>
-      <c r="B142" s="28" t="s">
+      <c r="B142" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C142" s="11">
@@ -52518,7 +52528,7 @@
       <c r="A143" s="4">
         <v>0</v>
       </c>
-      <c r="B143" s="28" t="s">
+      <c r="B143" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C143" s="11">
@@ -52529,7 +52539,7 @@
       <c r="A144" s="4">
         <v>0</v>
       </c>
-      <c r="B144" s="28" t="s">
+      <c r="B144" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C144" s="11">
@@ -52540,7 +52550,7 @@
       <c r="A145" s="4">
         <v>0</v>
       </c>
-      <c r="B145" s="28" t="s">
+      <c r="B145" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C145" s="11">
@@ -52551,7 +52561,7 @@
       <c r="A146" s="4">
         <v>0</v>
       </c>
-      <c r="B146" s="28" t="s">
+      <c r="B146" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C146" s="11">
@@ -52562,7 +52572,7 @@
       <c r="A147" s="5">
         <v>10</v>
       </c>
-      <c r="B147" s="28" t="s">
+      <c r="B147" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C147" s="11">
@@ -52573,7 +52583,7 @@
       <c r="A148" s="5">
         <v>10</v>
       </c>
-      <c r="B148" s="28" t="s">
+      <c r="B148" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C148" s="11">
@@ -52584,7 +52594,7 @@
       <c r="A149" s="5">
         <v>10</v>
       </c>
-      <c r="B149" s="28" t="s">
+      <c r="B149" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C149" s="11">
@@ -52595,7 +52605,7 @@
       <c r="A150" s="5">
         <v>10</v>
       </c>
-      <c r="B150" s="28" t="s">
+      <c r="B150" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C150" s="11">
@@ -52606,7 +52616,7 @@
       <c r="A151" s="5">
         <v>10</v>
       </c>
-      <c r="B151" s="28" t="s">
+      <c r="B151" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C151" s="11">
@@ -52617,7 +52627,7 @@
       <c r="A152" s="5">
         <v>20</v>
       </c>
-      <c r="B152" s="28" t="s">
+      <c r="B152" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C152" s="11">
@@ -52628,7 +52638,7 @@
       <c r="A153" s="5">
         <v>20</v>
       </c>
-      <c r="B153" s="28" t="s">
+      <c r="B153" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C153" s="11">
@@ -52639,7 +52649,7 @@
       <c r="A154" s="5">
         <v>20</v>
       </c>
-      <c r="B154" s="28" t="s">
+      <c r="B154" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C154" s="11">
@@ -52650,7 +52660,7 @@
       <c r="A155" s="5">
         <v>20</v>
       </c>
-      <c r="B155" s="28" t="s">
+      <c r="B155" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C155" s="11">
@@ -52661,7 +52671,7 @@
       <c r="A156" s="5">
         <v>20</v>
       </c>
-      <c r="B156" s="28" t="s">
+      <c r="B156" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C156" s="11">
@@ -52672,7 +52682,7 @@
       <c r="A157" s="5">
         <v>30</v>
       </c>
-      <c r="B157" s="28" t="s">
+      <c r="B157" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C157" s="11">
@@ -52683,7 +52693,7 @@
       <c r="A158" s="5">
         <v>30</v>
       </c>
-      <c r="B158" s="28" t="s">
+      <c r="B158" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C158" s="11">
@@ -52694,7 +52704,7 @@
       <c r="A159" s="5">
         <v>30</v>
       </c>
-      <c r="B159" s="28" t="s">
+      <c r="B159" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C159" s="11">
@@ -52705,7 +52715,7 @@
       <c r="A160" s="5">
         <v>30</v>
       </c>
-      <c r="B160" s="28" t="s">
+      <c r="B160" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C160" s="11">
@@ -52716,7 +52726,7 @@
       <c r="A161" s="5">
         <v>30</v>
       </c>
-      <c r="B161" s="28" t="s">
+      <c r="B161" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C161" s="11">
@@ -52727,7 +52737,7 @@
       <c r="A162" s="5">
         <v>40</v>
       </c>
-      <c r="B162" s="28" t="s">
+      <c r="B162" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C162" s="11">
@@ -52738,7 +52748,7 @@
       <c r="A163" s="5">
         <v>40</v>
       </c>
-      <c r="B163" s="28" t="s">
+      <c r="B163" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C163" s="11">
@@ -52749,7 +52759,7 @@
       <c r="A164" s="5">
         <v>40</v>
       </c>
-      <c r="B164" s="28" t="s">
+      <c r="B164" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C164" s="11">
@@ -52760,7 +52770,7 @@
       <c r="A165" s="5">
         <v>40</v>
       </c>
-      <c r="B165" s="28" t="s">
+      <c r="B165" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C165" s="11">
@@ -52771,7 +52781,7 @@
       <c r="A166" s="5">
         <v>40</v>
       </c>
-      <c r="B166" s="28" t="s">
+      <c r="B166" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C166" s="11">
@@ -52782,7 +52792,7 @@
       <c r="A167" s="5">
         <v>50</v>
       </c>
-      <c r="B167" s="28" t="s">
+      <c r="B167" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C167" s="11">
@@ -52793,7 +52803,7 @@
       <c r="A168" s="5">
         <v>50</v>
       </c>
-      <c r="B168" s="28" t="s">
+      <c r="B168" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C168" s="11">
@@ -52804,7 +52814,7 @@
       <c r="A169" s="5">
         <v>50</v>
       </c>
-      <c r="B169" s="28" t="s">
+      <c r="B169" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C169" s="11">
@@ -52815,7 +52825,7 @@
       <c r="A170" s="5">
         <v>50</v>
       </c>
-      <c r="B170" s="28" t="s">
+      <c r="B170" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C170" s="11">
@@ -52826,7 +52836,7 @@
       <c r="A171" s="5">
         <v>50</v>
       </c>
-      <c r="B171" s="28" t="s">
+      <c r="B171" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C171" s="11">
@@ -52837,7 +52847,7 @@
       <c r="A172" s="5">
         <v>60</v>
       </c>
-      <c r="B172" s="28" t="s">
+      <c r="B172" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C172" s="11">
@@ -52848,7 +52858,7 @@
       <c r="A173" s="5">
         <v>60</v>
       </c>
-      <c r="B173" s="28" t="s">
+      <c r="B173" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C173" s="11">
@@ -52859,7 +52869,7 @@
       <c r="A174" s="5">
         <v>60</v>
       </c>
-      <c r="B174" s="28" t="s">
+      <c r="B174" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C174" s="11">
@@ -52870,7 +52880,7 @@
       <c r="A175" s="5">
         <v>60</v>
       </c>
-      <c r="B175" s="28" t="s">
+      <c r="B175" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C175" s="11">
@@ -52881,7 +52891,7 @@
       <c r="A176" s="5">
         <v>60</v>
       </c>
-      <c r="B176" s="28" t="s">
+      <c r="B176" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C176" s="11">
@@ -52892,7 +52902,7 @@
       <c r="A177" s="4">
         <v>0</v>
       </c>
-      <c r="B177" s="28" t="s">
+      <c r="B177" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C177" s="11">
@@ -52903,7 +52913,7 @@
       <c r="A178" s="4">
         <v>0</v>
       </c>
-      <c r="B178" s="28" t="s">
+      <c r="B178" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C178" s="11">
@@ -52914,7 +52924,7 @@
       <c r="A179" s="4">
         <v>0</v>
       </c>
-      <c r="B179" s="28" t="s">
+      <c r="B179" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C179" s="11">
@@ -52925,7 +52935,7 @@
       <c r="A180" s="4">
         <v>0</v>
       </c>
-      <c r="B180" s="28" t="s">
+      <c r="B180" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C180" s="11">
@@ -52936,7 +52946,7 @@
       <c r="A181" s="4">
         <v>0</v>
       </c>
-      <c r="B181" s="28" t="s">
+      <c r="B181" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C181" s="11">
@@ -52947,7 +52957,7 @@
       <c r="A182" s="5">
         <v>10</v>
       </c>
-      <c r="B182" s="28" t="s">
+      <c r="B182" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C182" s="11">
@@ -52958,7 +52968,7 @@
       <c r="A183" s="5">
         <v>10</v>
       </c>
-      <c r="B183" s="28" t="s">
+      <c r="B183" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C183" s="11">
@@ -52969,7 +52979,7 @@
       <c r="A184" s="5">
         <v>10</v>
       </c>
-      <c r="B184" s="28" t="s">
+      <c r="B184" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C184" s="11">
@@ -52980,7 +52990,7 @@
       <c r="A185" s="5">
         <v>10</v>
       </c>
-      <c r="B185" s="28" t="s">
+      <c r="B185" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C185" s="11">
@@ -52991,7 +53001,7 @@
       <c r="A186" s="5">
         <v>10</v>
       </c>
-      <c r="B186" s="28" t="s">
+      <c r="B186" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C186" s="11">
@@ -53002,7 +53012,7 @@
       <c r="A187" s="5">
         <v>20</v>
       </c>
-      <c r="B187" s="28" t="s">
+      <c r="B187" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C187" s="11">
@@ -53013,7 +53023,7 @@
       <c r="A188" s="5">
         <v>20</v>
       </c>
-      <c r="B188" s="28" t="s">
+      <c r="B188" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C188" s="11">
@@ -53024,7 +53034,7 @@
       <c r="A189" s="5">
         <v>20</v>
       </c>
-      <c r="B189" s="28" t="s">
+      <c r="B189" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C189" s="11">
@@ -53035,7 +53045,7 @@
       <c r="A190" s="5">
         <v>20</v>
       </c>
-      <c r="B190" s="28" t="s">
+      <c r="B190" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C190" s="11">
@@ -53046,7 +53056,7 @@
       <c r="A191" s="5">
         <v>20</v>
       </c>
-      <c r="B191" s="28" t="s">
+      <c r="B191" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C191" s="11">
@@ -53057,7 +53067,7 @@
       <c r="A192" s="5">
         <v>30</v>
       </c>
-      <c r="B192" s="28" t="s">
+      <c r="B192" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C192" s="11">
@@ -53068,7 +53078,7 @@
       <c r="A193" s="5">
         <v>30</v>
       </c>
-      <c r="B193" s="28" t="s">
+      <c r="B193" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C193" s="11">
@@ -53079,7 +53089,7 @@
       <c r="A194" s="5">
         <v>30</v>
       </c>
-      <c r="B194" s="28" t="s">
+      <c r="B194" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C194" s="11">
@@ -53090,7 +53100,7 @@
       <c r="A195" s="5">
         <v>30</v>
       </c>
-      <c r="B195" s="28" t="s">
+      <c r="B195" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C195" s="11">
@@ -53101,7 +53111,7 @@
       <c r="A196" s="5">
         <v>30</v>
       </c>
-      <c r="B196" s="28" t="s">
+      <c r="B196" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C196" s="11">
@@ -53112,7 +53122,7 @@
       <c r="A197" s="5">
         <v>40</v>
       </c>
-      <c r="B197" s="28" t="s">
+      <c r="B197" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C197" s="11">
@@ -53123,7 +53133,7 @@
       <c r="A198" s="5">
         <v>40</v>
       </c>
-      <c r="B198" s="28" t="s">
+      <c r="B198" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C198" s="11">
@@ -53134,7 +53144,7 @@
       <c r="A199" s="5">
         <v>40</v>
       </c>
-      <c r="B199" s="28" t="s">
+      <c r="B199" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C199" s="11">
@@ -53145,7 +53155,7 @@
       <c r="A200" s="5">
         <v>40</v>
       </c>
-      <c r="B200" s="28" t="s">
+      <c r="B200" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C200" s="11">
@@ -53156,7 +53166,7 @@
       <c r="A201" s="5">
         <v>40</v>
       </c>
-      <c r="B201" s="28" t="s">
+      <c r="B201" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C201" s="11">
@@ -53167,7 +53177,7 @@
       <c r="A202" s="5">
         <v>50</v>
       </c>
-      <c r="B202" s="28" t="s">
+      <c r="B202" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C202" s="11">
@@ -53178,7 +53188,7 @@
       <c r="A203" s="5">
         <v>50</v>
       </c>
-      <c r="B203" s="28" t="s">
+      <c r="B203" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C203" s="11">
@@ -53189,7 +53199,7 @@
       <c r="A204" s="5">
         <v>50</v>
       </c>
-      <c r="B204" s="28" t="s">
+      <c r="B204" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C204" s="11">
@@ -53200,7 +53210,7 @@
       <c r="A205" s="5">
         <v>50</v>
       </c>
-      <c r="B205" s="28" t="s">
+      <c r="B205" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C205" s="11">
@@ -53211,7 +53221,7 @@
       <c r="A206" s="5">
         <v>50</v>
       </c>
-      <c r="B206" s="28" t="s">
+      <c r="B206" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C206" s="11">
@@ -53222,7 +53232,7 @@
       <c r="A207" s="5">
         <v>60</v>
       </c>
-      <c r="B207" s="28" t="s">
+      <c r="B207" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C207" s="11">
@@ -53233,7 +53243,7 @@
       <c r="A208" s="5">
         <v>60</v>
       </c>
-      <c r="B208" s="28" t="s">
+      <c r="B208" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C208" s="11">
@@ -53244,7 +53254,7 @@
       <c r="A209" s="5">
         <v>60</v>
       </c>
-      <c r="B209" s="28" t="s">
+      <c r="B209" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C209" s="11">
@@ -53255,7 +53265,7 @@
       <c r="A210" s="5">
         <v>60</v>
       </c>
-      <c r="B210" s="28" t="s">
+      <c r="B210" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C210" s="11">
@@ -53266,7 +53276,7 @@
       <c r="A211" s="5">
         <v>60</v>
       </c>
-      <c r="B211" s="28" t="s">
+      <c r="B211" s="26" t="s">
         <v>44</v>
       </c>
       <c r="C211" s="11">
@@ -53277,7 +53287,7 @@
       <c r="A212" s="4">
         <v>0</v>
       </c>
-      <c r="B212" s="28" t="s">
+      <c r="B212" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C212" s="11">
@@ -53288,7 +53298,7 @@
       <c r="A213" s="4">
         <v>0</v>
       </c>
-      <c r="B213" s="28" t="s">
+      <c r="B213" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C213" s="11">
@@ -53299,7 +53309,7 @@
       <c r="A214" s="4">
         <v>0</v>
       </c>
-      <c r="B214" s="28" t="s">
+      <c r="B214" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C214" s="11">
@@ -53310,7 +53320,7 @@
       <c r="A215" s="4">
         <v>0</v>
       </c>
-      <c r="B215" s="28" t="s">
+      <c r="B215" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C215" s="11">
@@ -53321,7 +53331,7 @@
       <c r="A216" s="4">
         <v>0</v>
       </c>
-      <c r="B216" s="28" t="s">
+      <c r="B216" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C216" s="11">
@@ -53332,7 +53342,7 @@
       <c r="A217" s="5">
         <v>10</v>
       </c>
-      <c r="B217" s="28" t="s">
+      <c r="B217" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C217" s="11">
@@ -53343,7 +53353,7 @@
       <c r="A218" s="5">
         <v>10</v>
       </c>
-      <c r="B218" s="28" t="s">
+      <c r="B218" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C218" s="11">
@@ -53354,7 +53364,7 @@
       <c r="A219" s="5">
         <v>10</v>
       </c>
-      <c r="B219" s="28" t="s">
+      <c r="B219" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C219" s="11">
@@ -53365,7 +53375,7 @@
       <c r="A220" s="5">
         <v>10</v>
       </c>
-      <c r="B220" s="28" t="s">
+      <c r="B220" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C220" s="11">
@@ -53376,7 +53386,7 @@
       <c r="A221" s="5">
         <v>10</v>
       </c>
-      <c r="B221" s="28" t="s">
+      <c r="B221" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C221" s="11">
@@ -53387,7 +53397,7 @@
       <c r="A222" s="5">
         <v>20</v>
       </c>
-      <c r="B222" s="28" t="s">
+      <c r="B222" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C222" s="11">
@@ -53398,7 +53408,7 @@
       <c r="A223" s="5">
         <v>20</v>
       </c>
-      <c r="B223" s="28" t="s">
+      <c r="B223" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C223" s="11">
@@ -53409,7 +53419,7 @@
       <c r="A224" s="5">
         <v>20</v>
       </c>
-      <c r="B224" s="28" t="s">
+      <c r="B224" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C224" s="11">
@@ -53420,7 +53430,7 @@
       <c r="A225" s="5">
         <v>20</v>
       </c>
-      <c r="B225" s="28" t="s">
+      <c r="B225" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C225" s="11">
@@ -53431,7 +53441,7 @@
       <c r="A226" s="5">
         <v>20</v>
       </c>
-      <c r="B226" s="28" t="s">
+      <c r="B226" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C226" s="11">
@@ -53442,7 +53452,7 @@
       <c r="A227" s="5">
         <v>30</v>
       </c>
-      <c r="B227" s="28" t="s">
+      <c r="B227" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C227" s="11">
@@ -53453,7 +53463,7 @@
       <c r="A228" s="5">
         <v>30</v>
       </c>
-      <c r="B228" s="28" t="s">
+      <c r="B228" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C228" s="11">
@@ -53464,7 +53474,7 @@
       <c r="A229" s="5">
         <v>30</v>
       </c>
-      <c r="B229" s="28" t="s">
+      <c r="B229" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C229" s="11">
@@ -53475,7 +53485,7 @@
       <c r="A230" s="5">
         <v>30</v>
       </c>
-      <c r="B230" s="28" t="s">
+      <c r="B230" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C230" s="11">
@@ -53486,7 +53496,7 @@
       <c r="A231" s="5">
         <v>30</v>
       </c>
-      <c r="B231" s="28" t="s">
+      <c r="B231" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C231" s="11">
@@ -53497,7 +53507,7 @@
       <c r="A232" s="5">
         <v>40</v>
       </c>
-      <c r="B232" s="28" t="s">
+      <c r="B232" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C232" s="11">
@@ -53508,7 +53518,7 @@
       <c r="A233" s="5">
         <v>40</v>
       </c>
-      <c r="B233" s="28" t="s">
+      <c r="B233" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C233" s="11">
@@ -53519,7 +53529,7 @@
       <c r="A234" s="5">
         <v>40</v>
       </c>
-      <c r="B234" s="28" t="s">
+      <c r="B234" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C234" s="11">
@@ -53530,7 +53540,7 @@
       <c r="A235" s="5">
         <v>40</v>
       </c>
-      <c r="B235" s="28" t="s">
+      <c r="B235" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C235" s="11">
@@ -53541,7 +53551,7 @@
       <c r="A236" s="5">
         <v>40</v>
       </c>
-      <c r="B236" s="28" t="s">
+      <c r="B236" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C236" s="11">
@@ -53552,7 +53562,7 @@
       <c r="A237" s="5">
         <v>50</v>
       </c>
-      <c r="B237" s="28" t="s">
+      <c r="B237" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C237" s="11">
@@ -53563,7 +53573,7 @@
       <c r="A238" s="5">
         <v>50</v>
       </c>
-      <c r="B238" s="28" t="s">
+      <c r="B238" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C238" s="11">
@@ -53574,7 +53584,7 @@
       <c r="A239" s="5">
         <v>50</v>
       </c>
-      <c r="B239" s="28" t="s">
+      <c r="B239" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C239" s="11">
@@ -53585,7 +53595,7 @@
       <c r="A240" s="5">
         <v>50</v>
       </c>
-      <c r="B240" s="28" t="s">
+      <c r="B240" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C240" s="11">
@@ -53596,7 +53606,7 @@
       <c r="A241" s="5">
         <v>50</v>
       </c>
-      <c r="B241" s="28" t="s">
+      <c r="B241" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C241" s="11">
@@ -53607,7 +53617,7 @@
       <c r="A242" s="5">
         <v>60</v>
       </c>
-      <c r="B242" s="28" t="s">
+      <c r="B242" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C242" s="11">
@@ -53618,7 +53628,7 @@
       <c r="A243" s="5">
         <v>60</v>
       </c>
-      <c r="B243" s="28" t="s">
+      <c r="B243" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C243" s="11">
@@ -53629,7 +53639,7 @@
       <c r="A244" s="5">
         <v>60</v>
       </c>
-      <c r="B244" s="28" t="s">
+      <c r="B244" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C244" s="11">
@@ -53640,7 +53650,7 @@
       <c r="A245" s="5">
         <v>60</v>
       </c>
-      <c r="B245" s="28" t="s">
+      <c r="B245" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C245" s="11">
@@ -53651,7 +53661,7 @@
       <c r="A246" s="5">
         <v>60</v>
       </c>
-      <c r="B246" s="28" t="s">
+      <c r="B246" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C246" s="11">
@@ -53662,7 +53672,7 @@
       <c r="A247" s="4">
         <v>0</v>
       </c>
-      <c r="B247" s="28" t="s">
+      <c r="B247" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C247" s="11">
@@ -53673,7 +53683,7 @@
       <c r="A248" s="4">
         <v>0</v>
       </c>
-      <c r="B248" s="28" t="s">
+      <c r="B248" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C248" s="11">
@@ -53684,7 +53694,7 @@
       <c r="A249" s="4">
         <v>0</v>
       </c>
-      <c r="B249" s="28" t="s">
+      <c r="B249" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C249" s="11">
@@ -53695,7 +53705,7 @@
       <c r="A250" s="4">
         <v>0</v>
       </c>
-      <c r="B250" s="28" t="s">
+      <c r="B250" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C250" s="11">
@@ -53706,7 +53716,7 @@
       <c r="A251" s="4">
         <v>0</v>
       </c>
-      <c r="B251" s="28" t="s">
+      <c r="B251" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C251" s="11">
@@ -53717,7 +53727,7 @@
       <c r="A252" s="5">
         <v>10</v>
       </c>
-      <c r="B252" s="28" t="s">
+      <c r="B252" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C252" s="11">
@@ -53728,7 +53738,7 @@
       <c r="A253" s="5">
         <v>10</v>
       </c>
-      <c r="B253" s="28" t="s">
+      <c r="B253" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C253" s="11">
@@ -53739,7 +53749,7 @@
       <c r="A254" s="5">
         <v>10</v>
       </c>
-      <c r="B254" s="28" t="s">
+      <c r="B254" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C254" s="11">
@@ -53750,7 +53760,7 @@
       <c r="A255" s="5">
         <v>10</v>
       </c>
-      <c r="B255" s="28" t="s">
+      <c r="B255" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C255" s="11">
@@ -53761,7 +53771,7 @@
       <c r="A256" s="5">
         <v>10</v>
       </c>
-      <c r="B256" s="28" t="s">
+      <c r="B256" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C256" s="11">
@@ -53772,7 +53782,7 @@
       <c r="A257" s="5">
         <v>20</v>
       </c>
-      <c r="B257" s="28" t="s">
+      <c r="B257" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C257" s="11">
@@ -53783,7 +53793,7 @@
       <c r="A258" s="5">
         <v>20</v>
       </c>
-      <c r="B258" s="28" t="s">
+      <c r="B258" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C258" s="11">
@@ -53794,7 +53804,7 @@
       <c r="A259" s="5">
         <v>20</v>
       </c>
-      <c r="B259" s="28" t="s">
+      <c r="B259" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C259" s="11">
@@ -53805,7 +53815,7 @@
       <c r="A260" s="5">
         <v>20</v>
       </c>
-      <c r="B260" s="28" t="s">
+      <c r="B260" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C260" s="11">
@@ -53816,7 +53826,7 @@
       <c r="A261" s="5">
         <v>20</v>
       </c>
-      <c r="B261" s="28" t="s">
+      <c r="B261" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C261" s="11">
@@ -53827,7 +53837,7 @@
       <c r="A262" s="5">
         <v>30</v>
       </c>
-      <c r="B262" s="28" t="s">
+      <c r="B262" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C262" s="11">
@@ -53838,7 +53848,7 @@
       <c r="A263" s="5">
         <v>30</v>
       </c>
-      <c r="B263" s="28" t="s">
+      <c r="B263" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C263" s="11">
@@ -53849,7 +53859,7 @@
       <c r="A264" s="5">
         <v>30</v>
       </c>
-      <c r="B264" s="28" t="s">
+      <c r="B264" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C264" s="11">
@@ -53860,7 +53870,7 @@
       <c r="A265" s="5">
         <v>30</v>
       </c>
-      <c r="B265" s="28" t="s">
+      <c r="B265" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C265" s="11">
@@ -53871,7 +53881,7 @@
       <c r="A266" s="5">
         <v>30</v>
       </c>
-      <c r="B266" s="28" t="s">
+      <c r="B266" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C266" s="11">
@@ -53882,7 +53892,7 @@
       <c r="A267" s="5">
         <v>40</v>
       </c>
-      <c r="B267" s="28" t="s">
+      <c r="B267" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C267" s="11">
@@ -53893,7 +53903,7 @@
       <c r="A268" s="5">
         <v>40</v>
       </c>
-      <c r="B268" s="28" t="s">
+      <c r="B268" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C268" s="11">
@@ -53904,7 +53914,7 @@
       <c r="A269" s="5">
         <v>40</v>
       </c>
-      <c r="B269" s="28" t="s">
+      <c r="B269" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C269" s="11">
@@ -53915,7 +53925,7 @@
       <c r="A270" s="5">
         <v>40</v>
       </c>
-      <c r="B270" s="28" t="s">
+      <c r="B270" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C270" s="11">
@@ -53926,7 +53936,7 @@
       <c r="A271" s="5">
         <v>40</v>
       </c>
-      <c r="B271" s="28" t="s">
+      <c r="B271" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C271" s="11">
@@ -53937,7 +53947,7 @@
       <c r="A272" s="5">
         <v>50</v>
       </c>
-      <c r="B272" s="28" t="s">
+      <c r="B272" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C272" s="11">
@@ -53948,7 +53958,7 @@
       <c r="A273" s="5">
         <v>50</v>
       </c>
-      <c r="B273" s="28" t="s">
+      <c r="B273" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C273" s="11">
@@ -53959,7 +53969,7 @@
       <c r="A274" s="5">
         <v>50</v>
       </c>
-      <c r="B274" s="28" t="s">
+      <c r="B274" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C274" s="11">
@@ -53970,7 +53980,7 @@
       <c r="A275" s="5">
         <v>50</v>
       </c>
-      <c r="B275" s="28" t="s">
+      <c r="B275" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C275" s="11">
@@ -53981,7 +53991,7 @@
       <c r="A276" s="5">
         <v>50</v>
       </c>
-      <c r="B276" s="28" t="s">
+      <c r="B276" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C276" s="11">
@@ -53992,7 +54002,7 @@
       <c r="A277" s="5">
         <v>60</v>
       </c>
-      <c r="B277" s="28" t="s">
+      <c r="B277" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C277" s="11">
@@ -54003,7 +54013,7 @@
       <c r="A278" s="5">
         <v>60</v>
       </c>
-      <c r="B278" s="28" t="s">
+      <c r="B278" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C278" s="11">
@@ -54014,7 +54024,7 @@
       <c r="A279" s="5">
         <v>60</v>
       </c>
-      <c r="B279" s="28" t="s">
+      <c r="B279" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C279" s="11">
@@ -54025,7 +54035,7 @@
       <c r="A280" s="5">
         <v>60</v>
       </c>
-      <c r="B280" s="28" t="s">
+      <c r="B280" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C280" s="11">
@@ -54036,7 +54046,7 @@
       <c r="A281" s="5">
         <v>60</v>
       </c>
-      <c r="B281" s="28" t="s">
+      <c r="B281" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C281" s="11">
@@ -54047,7 +54057,7 @@
       <c r="A282" s="4">
         <v>0</v>
       </c>
-      <c r="B282" s="28" t="s">
+      <c r="B282" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C282" s="11">
@@ -54058,7 +54068,7 @@
       <c r="A283" s="4">
         <v>0</v>
       </c>
-      <c r="B283" s="28" t="s">
+      <c r="B283" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C283" s="11">
@@ -54069,7 +54079,7 @@
       <c r="A284" s="4">
         <v>0</v>
       </c>
-      <c r="B284" s="28" t="s">
+      <c r="B284" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C284" s="11">
@@ -54080,7 +54090,7 @@
       <c r="A285" s="4">
         <v>0</v>
       </c>
-      <c r="B285" s="28" t="s">
+      <c r="B285" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C285" s="11">
@@ -54091,7 +54101,7 @@
       <c r="A286" s="4">
         <v>0</v>
       </c>
-      <c r="B286" s="28" t="s">
+      <c r="B286" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C286" s="11">
@@ -54102,7 +54112,7 @@
       <c r="A287" s="5">
         <v>10</v>
       </c>
-      <c r="B287" s="28" t="s">
+      <c r="B287" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C287" s="11">
@@ -54113,7 +54123,7 @@
       <c r="A288" s="5">
         <v>10</v>
       </c>
-      <c r="B288" s="28" t="s">
+      <c r="B288" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C288" s="11">
@@ -54124,7 +54134,7 @@
       <c r="A289" s="5">
         <v>10</v>
       </c>
-      <c r="B289" s="28" t="s">
+      <c r="B289" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C289" s="11">
@@ -54135,7 +54145,7 @@
       <c r="A290" s="5">
         <v>10</v>
       </c>
-      <c r="B290" s="28" t="s">
+      <c r="B290" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C290" s="11">
@@ -54146,7 +54156,7 @@
       <c r="A291" s="5">
         <v>10</v>
       </c>
-      <c r="B291" s="28" t="s">
+      <c r="B291" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C291" s="11">
@@ -54157,7 +54167,7 @@
       <c r="A292" s="5">
         <v>20</v>
       </c>
-      <c r="B292" s="28" t="s">
+      <c r="B292" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C292" s="11">
@@ -54168,7 +54178,7 @@
       <c r="A293" s="5">
         <v>20</v>
       </c>
-      <c r="B293" s="28" t="s">
+      <c r="B293" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C293" s="11">
@@ -54179,7 +54189,7 @@
       <c r="A294" s="5">
         <v>20</v>
       </c>
-      <c r="B294" s="28" t="s">
+      <c r="B294" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C294" s="11">
@@ -54190,7 +54200,7 @@
       <c r="A295" s="5">
         <v>20</v>
       </c>
-      <c r="B295" s="28" t="s">
+      <c r="B295" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C295" s="11">
@@ -54201,7 +54211,7 @@
       <c r="A296" s="5">
         <v>20</v>
       </c>
-      <c r="B296" s="28" t="s">
+      <c r="B296" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C296" s="11">
@@ -54212,7 +54222,7 @@
       <c r="A297" s="5">
         <v>30</v>
       </c>
-      <c r="B297" s="28" t="s">
+      <c r="B297" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C297" s="11">
@@ -54223,7 +54233,7 @@
       <c r="A298" s="5">
         <v>30</v>
       </c>
-      <c r="B298" s="28" t="s">
+      <c r="B298" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C298" s="11">
@@ -54234,7 +54244,7 @@
       <c r="A299" s="5">
         <v>30</v>
       </c>
-      <c r="B299" s="28" t="s">
+      <c r="B299" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C299" s="11">
@@ -54245,7 +54255,7 @@
       <c r="A300" s="5">
         <v>30</v>
       </c>
-      <c r="B300" s="28" t="s">
+      <c r="B300" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C300" s="11">
@@ -54256,7 +54266,7 @@
       <c r="A301" s="5">
         <v>30</v>
       </c>
-      <c r="B301" s="28" t="s">
+      <c r="B301" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C301" s="11">
@@ -54267,7 +54277,7 @@
       <c r="A302" s="5">
         <v>40</v>
       </c>
-      <c r="B302" s="28" t="s">
+      <c r="B302" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C302" s="11">
@@ -54278,7 +54288,7 @@
       <c r="A303" s="5">
         <v>40</v>
       </c>
-      <c r="B303" s="28" t="s">
+      <c r="B303" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C303" s="11">
@@ -54289,7 +54299,7 @@
       <c r="A304" s="5">
         <v>40</v>
       </c>
-      <c r="B304" s="28" t="s">
+      <c r="B304" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C304" s="11">
@@ -54300,7 +54310,7 @@
       <c r="A305" s="5">
         <v>40</v>
       </c>
-      <c r="B305" s="28" t="s">
+      <c r="B305" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C305" s="11">
@@ -54311,7 +54321,7 @@
       <c r="A306" s="5">
         <v>40</v>
       </c>
-      <c r="B306" s="28" t="s">
+      <c r="B306" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C306" s="11">
@@ -54322,7 +54332,7 @@
       <c r="A307" s="5">
         <v>50</v>
       </c>
-      <c r="B307" s="28" t="s">
+      <c r="B307" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C307" s="11">
@@ -54333,7 +54343,7 @@
       <c r="A308" s="5">
         <v>50</v>
       </c>
-      <c r="B308" s="28" t="s">
+      <c r="B308" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C308" s="11">
@@ -54344,7 +54354,7 @@
       <c r="A309" s="5">
         <v>50</v>
       </c>
-      <c r="B309" s="28" t="s">
+      <c r="B309" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C309" s="11">
@@ -54355,7 +54365,7 @@
       <c r="A310" s="5">
         <v>50</v>
       </c>
-      <c r="B310" s="28" t="s">
+      <c r="B310" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C310" s="11">
@@ -54366,7 +54376,7 @@
       <c r="A311" s="5">
         <v>50</v>
       </c>
-      <c r="B311" s="28" t="s">
+      <c r="B311" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C311" s="11">
@@ -54377,7 +54387,7 @@
       <c r="A312" s="5">
         <v>60</v>
       </c>
-      <c r="B312" s="28" t="s">
+      <c r="B312" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C312" s="11">
@@ -54388,7 +54398,7 @@
       <c r="A313" s="5">
         <v>60</v>
       </c>
-      <c r="B313" s="28" t="s">
+      <c r="B313" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C313" s="11">
@@ -54399,7 +54409,7 @@
       <c r="A314" s="5">
         <v>60</v>
       </c>
-      <c r="B314" s="28" t="s">
+      <c r="B314" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C314" s="11">
@@ -54410,7 +54420,7 @@
       <c r="A315" s="5">
         <v>60</v>
       </c>
-      <c r="B315" s="28" t="s">
+      <c r="B315" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C315" s="11">
@@ -54421,7 +54431,7 @@
       <c r="A316" s="5">
         <v>60</v>
       </c>
-      <c r="B316" s="28" t="s">
+      <c r="B316" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C316" s="11">
@@ -54432,7 +54442,7 @@
       <c r="A317" s="4">
         <v>0</v>
       </c>
-      <c r="B317" s="28" t="s">
+      <c r="B317" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C317" s="11">
@@ -54443,7 +54453,7 @@
       <c r="A318" s="4">
         <v>0</v>
       </c>
-      <c r="B318" s="28" t="s">
+      <c r="B318" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C318" s="11">
@@ -54454,7 +54464,7 @@
       <c r="A319" s="4">
         <v>0</v>
       </c>
-      <c r="B319" s="28" t="s">
+      <c r="B319" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C319" s="11">
@@ -54465,7 +54475,7 @@
       <c r="A320" s="4">
         <v>0</v>
       </c>
-      <c r="B320" s="28" t="s">
+      <c r="B320" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C320" s="11">
@@ -54476,7 +54486,7 @@
       <c r="A321" s="4">
         <v>0</v>
       </c>
-      <c r="B321" s="28" t="s">
+      <c r="B321" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C321" s="11">
@@ -54487,7 +54497,7 @@
       <c r="A322" s="5">
         <v>10</v>
       </c>
-      <c r="B322" s="28" t="s">
+      <c r="B322" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C322" s="11">
@@ -54498,7 +54508,7 @@
       <c r="A323" s="5">
         <v>10</v>
       </c>
-      <c r="B323" s="28" t="s">
+      <c r="B323" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C323" s="11">
@@ -54509,7 +54519,7 @@
       <c r="A324" s="5">
         <v>10</v>
       </c>
-      <c r="B324" s="28" t="s">
+      <c r="B324" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C324" s="11">
@@ -54520,7 +54530,7 @@
       <c r="A325" s="5">
         <v>10</v>
       </c>
-      <c r="B325" s="28" t="s">
+      <c r="B325" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C325" s="11">
@@ -54531,7 +54541,7 @@
       <c r="A326" s="5">
         <v>10</v>
       </c>
-      <c r="B326" s="28" t="s">
+      <c r="B326" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C326" s="11">
@@ -54542,7 +54552,7 @@
       <c r="A327" s="5">
         <v>20</v>
       </c>
-      <c r="B327" s="28" t="s">
+      <c r="B327" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C327" s="11">
@@ -54553,7 +54563,7 @@
       <c r="A328" s="5">
         <v>20</v>
       </c>
-      <c r="B328" s="28" t="s">
+      <c r="B328" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C328" s="11">
@@ -54564,7 +54574,7 @@
       <c r="A329" s="5">
         <v>20</v>
       </c>
-      <c r="B329" s="28" t="s">
+      <c r="B329" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C329" s="11">
@@ -54575,7 +54585,7 @@
       <c r="A330" s="5">
         <v>20</v>
       </c>
-      <c r="B330" s="28" t="s">
+      <c r="B330" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C330" s="11">
@@ -54586,7 +54596,7 @@
       <c r="A331" s="5">
         <v>20</v>
       </c>
-      <c r="B331" s="28" t="s">
+      <c r="B331" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C331" s="11">
@@ -54597,7 +54607,7 @@
       <c r="A332" s="5">
         <v>30</v>
       </c>
-      <c r="B332" s="28" t="s">
+      <c r="B332" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C332" s="11">
@@ -54608,7 +54618,7 @@
       <c r="A333" s="5">
         <v>30</v>
       </c>
-      <c r="B333" s="28" t="s">
+      <c r="B333" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C333" s="11">
@@ -54619,7 +54629,7 @@
       <c r="A334" s="5">
         <v>30</v>
       </c>
-      <c r="B334" s="28" t="s">
+      <c r="B334" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C334" s="11">
@@ -54630,7 +54640,7 @@
       <c r="A335" s="5">
         <v>30</v>
       </c>
-      <c r="B335" s="28" t="s">
+      <c r="B335" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C335" s="11">
@@ -54641,7 +54651,7 @@
       <c r="A336" s="5">
         <v>30</v>
       </c>
-      <c r="B336" s="28" t="s">
+      <c r="B336" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C336" s="11">
@@ -54652,7 +54662,7 @@
       <c r="A337" s="5">
         <v>40</v>
       </c>
-      <c r="B337" s="28" t="s">
+      <c r="B337" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C337" s="11">
@@ -54663,7 +54673,7 @@
       <c r="A338" s="5">
         <v>40</v>
       </c>
-      <c r="B338" s="28" t="s">
+      <c r="B338" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C338" s="11">
@@ -54674,7 +54684,7 @@
       <c r="A339" s="5">
         <v>40</v>
       </c>
-      <c r="B339" s="28" t="s">
+      <c r="B339" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C339" s="11">
@@ -54685,7 +54695,7 @@
       <c r="A340" s="5">
         <v>40</v>
       </c>
-      <c r="B340" s="28" t="s">
+      <c r="B340" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C340" s="11">
@@ -54696,7 +54706,7 @@
       <c r="A341" s="5">
         <v>40</v>
       </c>
-      <c r="B341" s="28" t="s">
+      <c r="B341" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C341" s="11">
@@ -54707,7 +54717,7 @@
       <c r="A342" s="5">
         <v>50</v>
       </c>
-      <c r="B342" s="28" t="s">
+      <c r="B342" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C342" s="11">
@@ -54718,7 +54728,7 @@
       <c r="A343" s="5">
         <v>50</v>
       </c>
-      <c r="B343" s="28" t="s">
+      <c r="B343" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C343" s="11">
@@ -54729,7 +54739,7 @@
       <c r="A344" s="5">
         <v>50</v>
       </c>
-      <c r="B344" s="28" t="s">
+      <c r="B344" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C344" s="11">
@@ -54740,7 +54750,7 @@
       <c r="A345" s="5">
         <v>50</v>
       </c>
-      <c r="B345" s="28" t="s">
+      <c r="B345" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C345" s="11">
@@ -54751,7 +54761,7 @@
       <c r="A346" s="5">
         <v>50</v>
       </c>
-      <c r="B346" s="28" t="s">
+      <c r="B346" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C346" s="11">
@@ -54762,7 +54772,7 @@
       <c r="A347" s="5">
         <v>60</v>
       </c>
-      <c r="B347" s="28" t="s">
+      <c r="B347" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C347" s="11">
@@ -54773,7 +54783,7 @@
       <c r="A348" s="5">
         <v>60</v>
       </c>
-      <c r="B348" s="28" t="s">
+      <c r="B348" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C348" s="11">
@@ -54784,7 +54794,7 @@
       <c r="A349" s="5">
         <v>60</v>
       </c>
-      <c r="B349" s="28" t="s">
+      <c r="B349" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C349" s="11">
@@ -54795,7 +54805,7 @@
       <c r="A350" s="5">
         <v>60</v>
       </c>
-      <c r="B350" s="28" t="s">
+      <c r="B350" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C350" s="11">
@@ -54806,7 +54816,7 @@
       <c r="A351" s="5">
         <v>60</v>
       </c>
-      <c r="B351" s="28" t="s">
+      <c r="B351" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C351" s="11">
@@ -54817,7 +54827,7 @@
       <c r="A352" s="4">
         <v>0</v>
       </c>
-      <c r="B352" s="28" t="s">
+      <c r="B352" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C352" s="11">
@@ -54828,7 +54838,7 @@
       <c r="A353" s="4">
         <v>0</v>
       </c>
-      <c r="B353" s="28" t="s">
+      <c r="B353" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C353" s="11">
@@ -54839,7 +54849,7 @@
       <c r="A354" s="4">
         <v>0</v>
       </c>
-      <c r="B354" s="28" t="s">
+      <c r="B354" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C354" s="11">
@@ -54850,7 +54860,7 @@
       <c r="A355" s="4">
         <v>0</v>
       </c>
-      <c r="B355" s="28" t="s">
+      <c r="B355" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C355" s="11">
@@ -54861,7 +54871,7 @@
       <c r="A356" s="4">
         <v>0</v>
       </c>
-      <c r="B356" s="28" t="s">
+      <c r="B356" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C356" s="11">
@@ -54872,7 +54882,7 @@
       <c r="A357" s="5">
         <v>10</v>
       </c>
-      <c r="B357" s="28" t="s">
+      <c r="B357" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C357" s="11">
@@ -54883,7 +54893,7 @@
       <c r="A358" s="5">
         <v>10</v>
       </c>
-      <c r="B358" s="28" t="s">
+      <c r="B358" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C358" s="11">
@@ -54894,7 +54904,7 @@
       <c r="A359" s="5">
         <v>10</v>
       </c>
-      <c r="B359" s="28" t="s">
+      <c r="B359" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C359" s="11">
@@ -54905,7 +54915,7 @@
       <c r="A360" s="5">
         <v>10</v>
       </c>
-      <c r="B360" s="28" t="s">
+      <c r="B360" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C360" s="11">
@@ -54916,7 +54926,7 @@
       <c r="A361" s="5">
         <v>10</v>
       </c>
-      <c r="B361" s="28" t="s">
+      <c r="B361" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C361" s="11">
@@ -54927,7 +54937,7 @@
       <c r="A362" s="5">
         <v>20</v>
       </c>
-      <c r="B362" s="28" t="s">
+      <c r="B362" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C362" s="11">
@@ -54938,7 +54948,7 @@
       <c r="A363" s="5">
         <v>20</v>
       </c>
-      <c r="B363" s="28" t="s">
+      <c r="B363" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C363" s="11">
@@ -54949,7 +54959,7 @@
       <c r="A364" s="5">
         <v>20</v>
       </c>
-      <c r="B364" s="28" t="s">
+      <c r="B364" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C364" s="11">
@@ -54960,7 +54970,7 @@
       <c r="A365" s="5">
         <v>20</v>
       </c>
-      <c r="B365" s="28" t="s">
+      <c r="B365" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C365" s="11">
@@ -54971,7 +54981,7 @@
       <c r="A366" s="5">
         <v>20</v>
       </c>
-      <c r="B366" s="28" t="s">
+      <c r="B366" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C366" s="11">
@@ -54982,7 +54992,7 @@
       <c r="A367" s="5">
         <v>30</v>
       </c>
-      <c r="B367" s="28" t="s">
+      <c r="B367" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C367" s="11">
@@ -54993,7 +55003,7 @@
       <c r="A368" s="5">
         <v>30</v>
       </c>
-      <c r="B368" s="28" t="s">
+      <c r="B368" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C368" s="11">
@@ -55004,7 +55014,7 @@
       <c r="A369" s="5">
         <v>30</v>
       </c>
-      <c r="B369" s="28" t="s">
+      <c r="B369" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C369" s="11">
@@ -55015,7 +55025,7 @@
       <c r="A370" s="5">
         <v>30</v>
       </c>
-      <c r="B370" s="28" t="s">
+      <c r="B370" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C370" s="11">
@@ -55026,7 +55036,7 @@
       <c r="A371" s="5">
         <v>30</v>
       </c>
-      <c r="B371" s="28" t="s">
+      <c r="B371" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C371" s="11">
@@ -55037,7 +55047,7 @@
       <c r="A372" s="5">
         <v>40</v>
       </c>
-      <c r="B372" s="28" t="s">
+      <c r="B372" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C372" s="11">
@@ -55048,7 +55058,7 @@
       <c r="A373" s="5">
         <v>40</v>
       </c>
-      <c r="B373" s="28" t="s">
+      <c r="B373" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C373" s="11">
@@ -55059,7 +55069,7 @@
       <c r="A374" s="5">
         <v>40</v>
       </c>
-      <c r="B374" s="28" t="s">
+      <c r="B374" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C374" s="11">
@@ -55070,7 +55080,7 @@
       <c r="A375" s="5">
         <v>40</v>
       </c>
-      <c r="B375" s="28" t="s">
+      <c r="B375" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C375" s="11">
@@ -55081,7 +55091,7 @@
       <c r="A376" s="5">
         <v>40</v>
       </c>
-      <c r="B376" s="28" t="s">
+      <c r="B376" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C376" s="11">
@@ -55092,7 +55102,7 @@
       <c r="A377" s="5">
         <v>50</v>
       </c>
-      <c r="B377" s="28" t="s">
+      <c r="B377" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C377" s="11">
@@ -55103,7 +55113,7 @@
       <c r="A378" s="5">
         <v>50</v>
       </c>
-      <c r="B378" s="28" t="s">
+      <c r="B378" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C378" s="11">
@@ -55114,7 +55124,7 @@
       <c r="A379" s="5">
         <v>50</v>
       </c>
-      <c r="B379" s="28" t="s">
+      <c r="B379" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C379" s="11">
@@ -55125,7 +55135,7 @@
       <c r="A380" s="5">
         <v>50</v>
       </c>
-      <c r="B380" s="28" t="s">
+      <c r="B380" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C380" s="11">
@@ -55136,7 +55146,7 @@
       <c r="A381" s="5">
         <v>50</v>
       </c>
-      <c r="B381" s="28" t="s">
+      <c r="B381" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C381" s="11">
@@ -55147,7 +55157,7 @@
       <c r="A382" s="5">
         <v>60</v>
       </c>
-      <c r="B382" s="28" t="s">
+      <c r="B382" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C382" s="11">
@@ -55158,7 +55168,7 @@
       <c r="A383" s="5">
         <v>60</v>
       </c>
-      <c r="B383" s="28" t="s">
+      <c r="B383" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C383" s="11">
@@ -55169,7 +55179,7 @@
       <c r="A384" s="5">
         <v>60</v>
       </c>
-      <c r="B384" s="28" t="s">
+      <c r="B384" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C384" s="11">
@@ -55180,7 +55190,7 @@
       <c r="A385" s="5">
         <v>60</v>
       </c>
-      <c r="B385" s="28" t="s">
+      <c r="B385" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C385" s="11">
@@ -55191,7 +55201,7 @@
       <c r="A386" s="5">
         <v>60</v>
       </c>
-      <c r="B386" s="28" t="s">
+      <c r="B386" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C386" s="11">
@@ -55202,7 +55212,7 @@
       <c r="A387" s="4">
         <v>0</v>
       </c>
-      <c r="B387" s="28" t="s">
+      <c r="B387" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C387" s="11">
@@ -55213,7 +55223,7 @@
       <c r="A388" s="4">
         <v>0</v>
       </c>
-      <c r="B388" s="28" t="s">
+      <c r="B388" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C388" s="11">
@@ -55224,7 +55234,7 @@
       <c r="A389" s="4">
         <v>0</v>
       </c>
-      <c r="B389" s="28" t="s">
+      <c r="B389" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C389" s="11">
@@ -55235,7 +55245,7 @@
       <c r="A390" s="4">
         <v>0</v>
       </c>
-      <c r="B390" s="28" t="s">
+      <c r="B390" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C390" s="11">
@@ -55246,7 +55256,7 @@
       <c r="A391" s="4">
         <v>0</v>
       </c>
-      <c r="B391" s="28" t="s">
+      <c r="B391" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C391" s="11">
@@ -55257,7 +55267,7 @@
       <c r="A392" s="5">
         <v>10</v>
       </c>
-      <c r="B392" s="28" t="s">
+      <c r="B392" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C392" s="11">
@@ -55268,7 +55278,7 @@
       <c r="A393" s="5">
         <v>10</v>
       </c>
-      <c r="B393" s="28" t="s">
+      <c r="B393" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C393" s="11">
@@ -55279,7 +55289,7 @@
       <c r="A394" s="5">
         <v>10</v>
       </c>
-      <c r="B394" s="28" t="s">
+      <c r="B394" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C394" s="11">
@@ -55290,7 +55300,7 @@
       <c r="A395" s="5">
         <v>10</v>
       </c>
-      <c r="B395" s="28" t="s">
+      <c r="B395" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C395" s="11">
@@ -55301,7 +55311,7 @@
       <c r="A396" s="5">
         <v>10</v>
       </c>
-      <c r="B396" s="28" t="s">
+      <c r="B396" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C396" s="11">
@@ -55312,7 +55322,7 @@
       <c r="A397" s="5">
         <v>20</v>
       </c>
-      <c r="B397" s="28" t="s">
+      <c r="B397" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C397" s="11">
@@ -55323,7 +55333,7 @@
       <c r="A398" s="5">
         <v>20</v>
       </c>
-      <c r="B398" s="28" t="s">
+      <c r="B398" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C398" s="11">
@@ -55334,7 +55344,7 @@
       <c r="A399" s="5">
         <v>20</v>
       </c>
-      <c r="B399" s="28" t="s">
+      <c r="B399" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C399" s="11">
@@ -55345,7 +55355,7 @@
       <c r="A400" s="5">
         <v>20</v>
       </c>
-      <c r="B400" s="28" t="s">
+      <c r="B400" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C400" s="11">
@@ -55356,7 +55366,7 @@
       <c r="A401" s="5">
         <v>20</v>
       </c>
-      <c r="B401" s="28" t="s">
+      <c r="B401" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C401" s="11">
@@ -55367,7 +55377,7 @@
       <c r="A402" s="5">
         <v>30</v>
       </c>
-      <c r="B402" s="28" t="s">
+      <c r="B402" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C402" s="11">
@@ -55378,7 +55388,7 @@
       <c r="A403" s="5">
         <v>30</v>
       </c>
-      <c r="B403" s="28" t="s">
+      <c r="B403" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C403" s="11">
@@ -55389,7 +55399,7 @@
       <c r="A404" s="5">
         <v>30</v>
       </c>
-      <c r="B404" s="28" t="s">
+      <c r="B404" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C404" s="11">
@@ -55400,7 +55410,7 @@
       <c r="A405" s="5">
         <v>30</v>
       </c>
-      <c r="B405" s="28" t="s">
+      <c r="B405" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C405" s="11">
@@ -55411,7 +55421,7 @@
       <c r="A406" s="5">
         <v>30</v>
       </c>
-      <c r="B406" s="28" t="s">
+      <c r="B406" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C406" s="11">
@@ -55422,7 +55432,7 @@
       <c r="A407" s="5">
         <v>40</v>
       </c>
-      <c r="B407" s="28" t="s">
+      <c r="B407" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C407" s="11">
@@ -55433,7 +55443,7 @@
       <c r="A408" s="5">
         <v>40</v>
       </c>
-      <c r="B408" s="28" t="s">
+      <c r="B408" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C408" s="11">
@@ -55444,7 +55454,7 @@
       <c r="A409" s="5">
         <v>40</v>
       </c>
-      <c r="B409" s="28" t="s">
+      <c r="B409" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C409" s="11">
@@ -55455,7 +55465,7 @@
       <c r="A410" s="5">
         <v>40</v>
       </c>
-      <c r="B410" s="28" t="s">
+      <c r="B410" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C410" s="11">
@@ -55466,7 +55476,7 @@
       <c r="A411" s="5">
         <v>40</v>
       </c>
-      <c r="B411" s="28" t="s">
+      <c r="B411" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C411" s="11">
@@ -55477,7 +55487,7 @@
       <c r="A412" s="5">
         <v>50</v>
       </c>
-      <c r="B412" s="28" t="s">
+      <c r="B412" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C412" s="11">
@@ -55488,7 +55498,7 @@
       <c r="A413" s="5">
         <v>50</v>
       </c>
-      <c r="B413" s="28" t="s">
+      <c r="B413" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C413" s="11">
@@ -55499,7 +55509,7 @@
       <c r="A414" s="5">
         <v>50</v>
       </c>
-      <c r="B414" s="28" t="s">
+      <c r="B414" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C414" s="11">
@@ -55510,7 +55520,7 @@
       <c r="A415" s="5">
         <v>50</v>
       </c>
-      <c r="B415" s="28" t="s">
+      <c r="B415" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C415" s="11">
@@ -55521,7 +55531,7 @@
       <c r="A416" s="5">
         <v>50</v>
       </c>
-      <c r="B416" s="28" t="s">
+      <c r="B416" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C416" s="11">
@@ -55532,7 +55542,7 @@
       <c r="A417" s="5">
         <v>60</v>
       </c>
-      <c r="B417" s="28" t="s">
+      <c r="B417" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C417" s="11">
@@ -55543,7 +55553,7 @@
       <c r="A418" s="5">
         <v>60</v>
       </c>
-      <c r="B418" s="28" t="s">
+      <c r="B418" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C418" s="11">
@@ -55554,7 +55564,7 @@
       <c r="A419" s="5">
         <v>60</v>
       </c>
-      <c r="B419" s="28" t="s">
+      <c r="B419" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C419" s="11">
@@ -55565,7 +55575,7 @@
       <c r="A420" s="5">
         <v>60</v>
       </c>
-      <c r="B420" s="28" t="s">
+      <c r="B420" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C420" s="11">
@@ -55576,12 +55586,2883 @@
       <c r="A421" s="5">
         <v>60</v>
       </c>
-      <c r="B421" s="28" t="s">
+      <c r="B421" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C421" s="11">
         <v>0.51300000000000001</v>
       </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B91D78A-59F5-754B-92FA-07DC9469041F}">
+  <dimension ref="A1:D421"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="23.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="5">
+        <v>0</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="11">
+        <v>0</v>
+      </c>
+      <c r="D2" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="5">
+        <v>10</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="11">
+        <v>0.2944</v>
+      </c>
+      <c r="D3" s="10">
+        <v>9.5627734622863361E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="5">
+        <v>20</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="11">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="D4" s="10">
+        <v>1.3590260363414099E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="5">
+        <v>30</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="11">
+        <v>0.35649999999999998</v>
+      </c>
+      <c r="D5" s="10">
+        <v>1.5740451787141351E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="5">
+        <v>40</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="11">
+        <v>0.36670000000000003</v>
+      </c>
+      <c r="D6" s="10">
+        <v>1.9533386971887765E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="5">
+        <v>50</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="11">
+        <v>0.38850000000000001</v>
+      </c>
+      <c r="D7" s="10">
+        <v>1.9989303345219721E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="5">
+        <v>60</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="11">
+        <v>0.40500000000000003</v>
+      </c>
+      <c r="D8" s="10">
+        <v>2.0903630297561517E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="5">
+        <v>0</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="10">
+        <v>0</v>
+      </c>
+      <c r="D9" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="5">
+        <v>10</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="10">
+        <v>0.4364713004960451</v>
+      </c>
+      <c r="D10" s="10">
+        <v>0.12723213842582981</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="5">
+        <v>20</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="10">
+        <v>0.51531160069446025</v>
+      </c>
+      <c r="D11" s="10">
+        <v>0.13136292466267202</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="5">
+        <v>30</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="10">
+        <v>0.53478420496033385</v>
+      </c>
+      <c r="D12" s="10">
+        <v>0.134284860746891</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="5">
+        <v>40</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="10">
+        <v>0.57372941349208095</v>
+      </c>
+      <c r="D13" s="10">
+        <v>0.12517170131277844</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="5">
+        <v>50</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="10">
+        <v>0.59462684246033559</v>
+      </c>
+      <c r="D14" s="10">
+        <v>0.109941473521196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="5">
+        <v>60</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C15" s="10">
+        <v>0.62169851180557445</v>
+      </c>
+      <c r="D15" s="10">
+        <v>0.10419045694508391</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="5">
+        <v>0</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="11">
+        <v>0</v>
+      </c>
+      <c r="D16" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="5">
+        <v>10</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="11">
+        <v>0.29260000000000003</v>
+      </c>
+      <c r="D17" s="10">
+        <v>9.7806567434322901E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="5">
+        <v>20</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="11">
+        <v>0.31119999999999998</v>
+      </c>
+      <c r="D18" s="10">
+        <v>9.9438732493841893E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="5">
+        <v>30</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="11">
+        <v>0.32740000000000002</v>
+      </c>
+      <c r="D19" s="10">
+        <v>8.7900428216988822E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="5">
+        <v>40</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="11">
+        <v>0.34549999999999997</v>
+      </c>
+      <c r="D20" s="10">
+        <v>1.4623887128068565E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="5">
+        <v>50</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="11">
+        <v>0.34749999999999998</v>
+      </c>
+      <c r="D21" s="10">
+        <v>8.4974022258437216E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="5">
+        <v>60</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="11">
+        <v>0.35680000000000001</v>
+      </c>
+      <c r="D22" s="10">
+        <v>1.2651032514078193E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="5">
+        <v>0</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="10">
+        <v>0</v>
+      </c>
+      <c r="D23" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="5">
+        <v>10</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" s="10">
+        <v>0.29504435139069196</v>
+      </c>
+      <c r="D24" s="10">
+        <v>1.2265025866744881E-2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="5">
+        <v>20</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" s="10">
+        <v>0.31239990147249735</v>
+      </c>
+      <c r="D25" s="10">
+        <v>1.5473952385165919E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="5">
+        <v>30</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C26" s="10">
+        <v>0.3230060709669339</v>
+      </c>
+      <c r="D26" s="10">
+        <v>1.7587435617507027E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="5">
+        <v>40</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C27" s="10">
+        <v>0.33120174739445313</v>
+      </c>
+      <c r="D27" s="10">
+        <v>2.0486414932924874E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="5">
+        <v>50</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" s="10">
+        <v>0.34759310024949164</v>
+      </c>
+      <c r="D28" s="10">
+        <v>2.2196470845322846E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="5">
+        <v>60</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" s="10">
+        <v>0.35096779054317595</v>
+      </c>
+      <c r="D29" s="10">
+        <v>2.195454023291064E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="5">
+        <v>0</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C30" s="10">
+        <v>0</v>
+      </c>
+      <c r="D30" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="5">
+        <v>10</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C31" s="10">
+        <v>0.26497392836152356</v>
+      </c>
+      <c r="D31" s="10">
+        <v>7.3353113849861807E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="5">
+        <v>20</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C32" s="10">
+        <v>0.28254126062858592</v>
+      </c>
+      <c r="D32" s="10">
+        <v>8.461110697118376E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="5">
+        <v>30</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" s="10">
+        <v>0.29181290821397998</v>
+      </c>
+      <c r="D33" s="10">
+        <v>7.1782201313358371E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="5">
+        <v>40</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C34" s="10">
+        <v>0.30791629612545385</v>
+      </c>
+      <c r="D34" s="10">
+        <v>5.5273243739283415E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="5">
+        <v>50</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C35" s="10">
+        <v>0.31279611064408219</v>
+      </c>
+      <c r="D35" s="10">
+        <v>5.925471496531525E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="5">
+        <v>60</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C36" s="10">
+        <v>0.31084418483663079</v>
+      </c>
+      <c r="D36" s="10">
+        <v>6.8532435045261355E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="5">
+        <v>0</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C37" s="10">
+        <v>0</v>
+      </c>
+      <c r="D37" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="5">
+        <v>10</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" s="10">
+        <v>0.26756998968543388</v>
+      </c>
+      <c r="D38" s="10">
+        <v>1.1771936706442653E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="5">
+        <v>20</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C39" s="10">
+        <v>0.28647439113060041</v>
+      </c>
+      <c r="D39" s="10">
+        <v>1.5543889598050321E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="5">
+        <v>30</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C40" s="10">
+        <v>0.29132167355243793</v>
+      </c>
+      <c r="D40" s="10">
+        <v>1.8085885022230175E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="5">
+        <v>40</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41" s="10">
+        <v>0.30101623839611308</v>
+      </c>
+      <c r="D41" s="10">
+        <v>1.8637223368858143E-2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="5">
+        <v>50</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" s="10">
+        <v>0.31071080323978822</v>
+      </c>
+      <c r="D42" s="10">
+        <v>1.6661540079348138E-2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="5">
+        <v>60</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C43" s="10">
+        <v>0.31168025972415586</v>
+      </c>
+      <c r="D43" s="10">
+        <v>1.86492902029931E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="5">
+        <v>0</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C44" s="10">
+        <v>0</v>
+      </c>
+      <c r="D44" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="5">
+        <v>10</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C45" s="10">
+        <v>0.26322584290738199</v>
+      </c>
+      <c r="D45" s="10">
+        <v>1.005131877908739E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="5">
+        <v>20</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C46" s="10">
+        <v>0.28009929437580394</v>
+      </c>
+      <c r="D46" s="10">
+        <v>7.8085501145171996E-3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="5">
+        <v>30</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C47" s="10">
+        <v>0.29166966109700754</v>
+      </c>
+      <c r="D47" s="10">
+        <v>3.3356472930014302E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="5">
+        <v>40</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C48" s="10">
+        <v>0.2960085486174589</v>
+      </c>
+      <c r="D48" s="10">
+        <v>6.9008407788440718E-3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="5">
+        <v>50</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C49" s="10">
+        <v>0.3008295347512937</v>
+      </c>
+      <c r="D49" s="10">
+        <v>9.3636081594044348E-3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="5">
+        <v>60</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C50" s="10">
+        <v>0.30275792920482769</v>
+      </c>
+      <c r="D50" s="10">
+        <v>7.8369966572315822E-3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="5">
+        <v>0</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="10">
+        <v>0</v>
+      </c>
+      <c r="D51" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="5">
+        <v>10</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" s="10">
+        <v>0.22274759513889572</v>
+      </c>
+      <c r="D52" s="10">
+        <v>1.2845354630746006E-2</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="5">
+        <v>20</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" s="10">
+        <v>0.28591482361111992</v>
+      </c>
+      <c r="D53" s="10">
+        <v>1.4293710689389647E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="5">
+        <v>30</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="10">
+        <v>0.28543988204365961</v>
+      </c>
+      <c r="D54" s="10">
+        <v>2.1417889596185888E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="5">
+        <v>40</v>
+      </c>
+      <c r="B55" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C55" s="10">
+        <v>0.29541365496032651</v>
+      </c>
+      <c r="D55" s="10">
+        <v>2.6801588923239916E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="5">
+        <v>50</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="10">
+        <v>0.30301272003969187</v>
+      </c>
+      <c r="D56" s="10">
+        <v>3.0139361912708013E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="5">
+        <v>60</v>
+      </c>
+      <c r="B57" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C57" s="10">
+        <v>0.30918696041667609</v>
+      </c>
+      <c r="D57" s="10">
+        <v>2.9880279496428856E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="5">
+        <v>0</v>
+      </c>
+      <c r="B58" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C58" s="10">
+        <v>0</v>
+      </c>
+      <c r="D58" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="5">
+        <v>10</v>
+      </c>
+      <c r="B59" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C59" s="10">
+        <v>0.21305799464995823</v>
+      </c>
+      <c r="D59" s="10">
+        <v>7.6065963088521463E-3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="5">
+        <v>20</v>
+      </c>
+      <c r="B60" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C60" s="10">
+        <v>0.25404901822914489</v>
+      </c>
+      <c r="D60" s="11">
+        <v>1.5083960702534734E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="5">
+        <v>30</v>
+      </c>
+      <c r="B61" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C61" s="10">
+        <v>0.27263797078249691</v>
+      </c>
+      <c r="D61" s="11">
+        <v>1.2479755049677079E-2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="5">
+        <v>40</v>
+      </c>
+      <c r="B62" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C62" s="10">
+        <v>0.28693716505430628</v>
+      </c>
+      <c r="D62" s="11">
+        <v>7.8873763989627619E-3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="5">
+        <v>50</v>
+      </c>
+      <c r="B63" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C63" s="10">
+        <v>0.28646052524524601</v>
+      </c>
+      <c r="D63" s="11">
+        <v>8.7750819505777733E-3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="5">
+        <v>60</v>
+      </c>
+      <c r="B64" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C64" s="10">
+        <v>0.29122692333584904</v>
+      </c>
+      <c r="D64" s="11">
+        <v>9.0195599833044204E-3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="5">
+        <v>0</v>
+      </c>
+      <c r="B65" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C65" s="10">
+        <v>0</v>
+      </c>
+      <c r="D65" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="5">
+        <v>10</v>
+      </c>
+      <c r="B66" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C66" s="10">
+        <v>0.18855657823047495</v>
+      </c>
+      <c r="D66" s="11">
+        <v>5.0986820404856012E-3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="5">
+        <v>20</v>
+      </c>
+      <c r="B67" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C67" s="10">
+        <v>0.2238550845816776</v>
+      </c>
+      <c r="D67" s="11">
+        <v>1.151776493383903E-2</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="5">
+        <v>30</v>
+      </c>
+      <c r="B68" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C68" s="10">
+        <v>0.22698280033431581</v>
+      </c>
+      <c r="D68" s="11">
+        <v>1.6393856749615025E-2</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="5">
+        <v>40</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C69" s="10">
+        <v>0.23100414915913636</v>
+      </c>
+      <c r="D69" s="11">
+        <v>6.7165225474816962E-3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="5">
+        <v>50</v>
+      </c>
+      <c r="B70" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C70" s="10">
+        <v>0.23189778223131868</v>
+      </c>
+      <c r="D70" s="11">
+        <v>1.2396997108579062E-2</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="5">
+        <v>60</v>
+      </c>
+      <c r="B71" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C71" s="10">
+        <v>0.23457868144786573</v>
+      </c>
+      <c r="D71" s="11">
+        <v>9.3770750381959502E-3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="5">
+        <v>0</v>
+      </c>
+      <c r="B72" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C72" s="10">
+        <v>0</v>
+      </c>
+      <c r="D72" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="5">
+        <v>10</v>
+      </c>
+      <c r="B73" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C73" s="10">
+        <v>0.13836403442827419</v>
+      </c>
+      <c r="D73" s="11">
+        <v>5.7661530307589123E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="5">
+        <v>20</v>
+      </c>
+      <c r="B74" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C74" s="10">
+        <v>0.21103594568585438</v>
+      </c>
+      <c r="D74" s="11">
+        <v>1.1104505748550418E-2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="5">
+        <v>30</v>
+      </c>
+      <c r="B75" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C75" s="10">
+        <v>0.23731279495413199</v>
+      </c>
+      <c r="D75" s="11">
+        <v>9.2139409800817244E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="5">
+        <v>40</v>
+      </c>
+      <c r="B76" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C76" s="10">
+        <v>0.24470315881083501</v>
+      </c>
+      <c r="D76" s="11">
+        <v>6.0127972963679201E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="5">
+        <v>50</v>
+      </c>
+      <c r="B77" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C77" s="10">
+        <v>0.25086179535808761</v>
+      </c>
+      <c r="D77" s="11">
+        <v>7.3421928480699675E-3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="5">
+        <v>60</v>
+      </c>
+      <c r="B78" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C78" s="10">
+        <v>0.25250409843735494</v>
+      </c>
+      <c r="D78" s="11">
+        <v>4.2135572253192803E-3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="5">
+        <v>0</v>
+      </c>
+      <c r="B79" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C79" s="10">
+        <v>0</v>
+      </c>
+      <c r="D79" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="5">
+        <v>10</v>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C80" s="10">
+        <v>0.13323378267704167</v>
+      </c>
+      <c r="D80" s="11">
+        <v>1.8531223133912804E-2</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="5">
+        <v>20</v>
+      </c>
+      <c r="B81" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C81" s="10">
+        <v>0.19386712090132405</v>
+      </c>
+      <c r="D81" s="11">
+        <v>1.9256946174855408E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="5">
+        <v>30</v>
+      </c>
+      <c r="B82" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C82" s="10">
+        <v>0.21540791211258231</v>
+      </c>
+      <c r="D82" s="11">
+        <v>1.687904740208173E-2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="5">
+        <v>40</v>
+      </c>
+      <c r="B83" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C83" s="10">
+        <v>0.2309651502096022</v>
+      </c>
+      <c r="D83" s="11">
+        <v>1.7646865486710461E-2</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="5">
+        <v>50</v>
+      </c>
+      <c r="B84" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C84" s="10">
+        <v>0.23415637853719601</v>
+      </c>
+      <c r="D84" s="11">
+        <v>1.8905629100599442E-2</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="5">
+        <v>60</v>
+      </c>
+      <c r="B85" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C85" s="10">
+        <v>0.24333115997902818</v>
+      </c>
+      <c r="D85" s="11">
+        <v>1.775874627156249E-2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="5"/>
+      <c r="B86" s="26"/>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="5"/>
+      <c r="B87" s="26"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" s="5"/>
+      <c r="B88" s="26"/>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="5"/>
+      <c r="B89" s="26"/>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" s="5"/>
+      <c r="B90" s="26"/>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" s="5"/>
+      <c r="B91" s="26"/>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="5"/>
+      <c r="B92" s="26"/>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="5"/>
+      <c r="B93" s="26"/>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="5"/>
+      <c r="B94" s="26"/>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="5"/>
+      <c r="B95" s="26"/>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="5"/>
+      <c r="B96" s="26"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A97" s="5"/>
+      <c r="B97" s="26"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A98" s="5"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="11"/>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A99" s="5"/>
+      <c r="B99" s="26"/>
+      <c r="C99" s="11"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A100" s="5"/>
+      <c r="B100" s="26"/>
+      <c r="C100" s="11"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A101" s="5"/>
+      <c r="B101" s="26"/>
+      <c r="C101" s="11"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A102" s="5"/>
+      <c r="B102" s="26"/>
+      <c r="C102" s="11"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A103" s="5"/>
+      <c r="B103" s="26"/>
+      <c r="C103" s="11"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A104" s="5"/>
+      <c r="B104" s="26"/>
+      <c r="C104" s="11"/>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A105" s="5"/>
+      <c r="B105" s="26"/>
+      <c r="C105" s="11"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A106" s="5"/>
+      <c r="B106" s="26"/>
+      <c r="C106" s="11"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A107" s="4"/>
+      <c r="B107" s="26"/>
+      <c r="C107" s="11"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A108" s="4"/>
+      <c r="B108" s="26"/>
+      <c r="C108" s="11"/>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A109" s="4"/>
+      <c r="B109" s="26"/>
+      <c r="C109" s="11"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A110" s="4"/>
+      <c r="B110" s="26"/>
+      <c r="C110" s="11"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A111" s="4"/>
+      <c r="B111" s="26"/>
+      <c r="C111" s="11"/>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A112" s="5"/>
+      <c r="B112" s="26"/>
+      <c r="C112" s="11"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A113" s="5"/>
+      <c r="B113" s="26"/>
+      <c r="C113" s="11"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A114" s="5"/>
+      <c r="B114" s="26"/>
+      <c r="C114" s="11"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A115" s="5"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="11"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A116" s="5"/>
+      <c r="B116" s="26"/>
+      <c r="C116" s="11"/>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A117" s="5"/>
+      <c r="B117" s="26"/>
+      <c r="C117" s="11"/>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A118" s="5"/>
+      <c r="B118" s="26"/>
+      <c r="C118" s="11"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A119" s="5"/>
+      <c r="B119" s="26"/>
+      <c r="C119" s="11"/>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A120" s="5"/>
+      <c r="B120" s="26"/>
+      <c r="C120" s="11"/>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A121" s="5"/>
+      <c r="B121" s="26"/>
+      <c r="C121" s="11"/>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A122" s="5"/>
+      <c r="B122" s="26"/>
+      <c r="C122" s="11"/>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A123" s="5"/>
+      <c r="B123" s="26"/>
+      <c r="C123" s="11"/>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A124" s="5"/>
+      <c r="B124" s="26"/>
+      <c r="C124" s="11"/>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A125" s="5"/>
+      <c r="B125" s="26"/>
+      <c r="C125" s="11"/>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A126" s="5"/>
+      <c r="B126" s="26"/>
+      <c r="C126" s="11"/>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A127" s="5"/>
+      <c r="B127" s="26"/>
+      <c r="C127" s="11"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A128" s="5"/>
+      <c r="B128" s="26"/>
+      <c r="C128" s="11"/>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A129" s="5"/>
+      <c r="B129" s="26"/>
+      <c r="C129" s="11"/>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A130" s="5"/>
+      <c r="B130" s="26"/>
+      <c r="C130" s="11"/>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A131" s="5"/>
+      <c r="B131" s="26"/>
+      <c r="C131" s="11"/>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A132" s="5"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="11"/>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A133" s="5"/>
+      <c r="B133" s="26"/>
+      <c r="C133" s="11"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A134" s="5"/>
+      <c r="B134" s="26"/>
+      <c r="C134" s="11"/>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A135" s="5"/>
+      <c r="B135" s="26"/>
+      <c r="C135" s="11"/>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A136" s="5"/>
+      <c r="B136" s="26"/>
+      <c r="C136" s="11"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A137" s="5"/>
+      <c r="B137" s="26"/>
+      <c r="C137" s="11"/>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A138" s="5"/>
+      <c r="B138" s="26"/>
+      <c r="C138" s="11"/>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A139" s="5"/>
+      <c r="B139" s="26"/>
+      <c r="C139" s="11"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A140" s="5"/>
+      <c r="B140" s="26"/>
+      <c r="C140" s="11"/>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A141" s="5"/>
+      <c r="B141" s="26"/>
+      <c r="C141" s="11"/>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A142" s="4"/>
+      <c r="B142" s="26"/>
+      <c r="C142" s="11"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A143" s="4"/>
+      <c r="B143" s="26"/>
+      <c r="C143" s="11"/>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A144" s="4"/>
+      <c r="B144" s="26"/>
+      <c r="C144" s="11"/>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A145" s="4"/>
+      <c r="B145" s="26"/>
+      <c r="C145" s="11"/>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A146" s="4"/>
+      <c r="B146" s="26"/>
+      <c r="C146" s="11"/>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A147" s="5"/>
+      <c r="B147" s="26"/>
+      <c r="C147" s="11"/>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A148" s="5"/>
+      <c r="B148" s="26"/>
+      <c r="C148" s="11"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A149" s="5"/>
+      <c r="B149" s="26"/>
+      <c r="C149" s="11"/>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A150" s="5"/>
+      <c r="B150" s="26"/>
+      <c r="C150" s="11"/>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A151" s="5"/>
+      <c r="B151" s="26"/>
+      <c r="C151" s="11"/>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A152" s="5"/>
+      <c r="B152" s="26"/>
+      <c r="C152" s="11"/>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A153" s="5"/>
+      <c r="B153" s="26"/>
+      <c r="C153" s="11"/>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A154" s="5"/>
+      <c r="B154" s="26"/>
+      <c r="C154" s="11"/>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A155" s="5"/>
+      <c r="B155" s="26"/>
+      <c r="C155" s="11"/>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A156" s="5"/>
+      <c r="B156" s="26"/>
+      <c r="C156" s="11"/>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A157" s="5"/>
+      <c r="B157" s="26"/>
+      <c r="C157" s="11"/>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A158" s="5"/>
+      <c r="B158" s="26"/>
+      <c r="C158" s="11"/>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A159" s="5"/>
+      <c r="B159" s="26"/>
+      <c r="C159" s="11"/>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A160" s="5"/>
+      <c r="B160" s="26"/>
+      <c r="C160" s="11"/>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A161" s="5"/>
+      <c r="B161" s="26"/>
+      <c r="C161" s="11"/>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A162" s="5"/>
+      <c r="B162" s="26"/>
+      <c r="C162" s="11"/>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A163" s="5"/>
+      <c r="B163" s="26"/>
+      <c r="C163" s="11"/>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A164" s="5"/>
+      <c r="B164" s="26"/>
+      <c r="C164" s="11"/>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A165" s="5"/>
+      <c r="B165" s="26"/>
+      <c r="C165" s="11"/>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A166" s="5"/>
+      <c r="B166" s="26"/>
+      <c r="C166" s="11"/>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A167" s="5"/>
+      <c r="B167" s="26"/>
+      <c r="C167" s="11"/>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A168" s="5"/>
+      <c r="B168" s="26"/>
+      <c r="C168" s="11"/>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A169" s="5"/>
+      <c r="B169" s="26"/>
+      <c r="C169" s="11"/>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A170" s="5"/>
+      <c r="B170" s="26"/>
+      <c r="C170" s="11"/>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A171" s="5"/>
+      <c r="B171" s="26"/>
+      <c r="C171" s="11"/>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A172" s="5"/>
+      <c r="B172" s="26"/>
+      <c r="C172" s="11"/>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A173" s="5"/>
+      <c r="B173" s="26"/>
+      <c r="C173" s="11"/>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A174" s="5"/>
+      <c r="B174" s="26"/>
+      <c r="C174" s="11"/>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A175" s="5"/>
+      <c r="B175" s="26"/>
+      <c r="C175" s="11"/>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A176" s="5"/>
+      <c r="B176" s="26"/>
+      <c r="C176" s="11"/>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A177" s="4"/>
+      <c r="B177" s="26"/>
+      <c r="C177" s="11"/>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A178" s="4"/>
+      <c r="B178" s="26"/>
+      <c r="C178" s="11"/>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A179" s="4"/>
+      <c r="B179" s="26"/>
+      <c r="C179" s="11"/>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A180" s="4"/>
+      <c r="B180" s="26"/>
+      <c r="C180" s="11"/>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A181" s="4"/>
+      <c r="B181" s="26"/>
+      <c r="C181" s="11"/>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A182" s="5"/>
+      <c r="B182" s="26"/>
+      <c r="C182" s="11"/>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A183" s="5"/>
+      <c r="B183" s="26"/>
+      <c r="C183" s="11"/>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A184" s="5"/>
+      <c r="B184" s="26"/>
+      <c r="C184" s="11"/>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A185" s="5"/>
+      <c r="B185" s="26"/>
+      <c r="C185" s="11"/>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A186" s="5"/>
+      <c r="B186" s="26"/>
+      <c r="C186" s="11"/>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A187" s="5"/>
+      <c r="B187" s="26"/>
+      <c r="C187" s="11"/>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A188" s="5"/>
+      <c r="B188" s="26"/>
+      <c r="C188" s="11"/>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A189" s="5"/>
+      <c r="B189" s="26"/>
+      <c r="C189" s="11"/>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A190" s="5"/>
+      <c r="B190" s="26"/>
+      <c r="C190" s="11"/>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A191" s="5"/>
+      <c r="B191" s="26"/>
+      <c r="C191" s="11"/>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A192" s="5"/>
+      <c r="B192" s="26"/>
+      <c r="C192" s="11"/>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A193" s="5"/>
+      <c r="B193" s="26"/>
+      <c r="C193" s="11"/>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A194" s="5"/>
+      <c r="B194" s="26"/>
+      <c r="C194" s="11"/>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A195" s="5"/>
+      <c r="B195" s="26"/>
+      <c r="C195" s="11"/>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A196" s="5"/>
+      <c r="B196" s="26"/>
+      <c r="C196" s="11"/>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A197" s="5"/>
+      <c r="B197" s="26"/>
+      <c r="C197" s="11"/>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A198" s="5"/>
+      <c r="B198" s="26"/>
+      <c r="C198" s="11"/>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A199" s="5"/>
+      <c r="B199" s="26"/>
+      <c r="C199" s="11"/>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A200" s="5"/>
+      <c r="B200" s="26"/>
+      <c r="C200" s="11"/>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A201" s="5"/>
+      <c r="B201" s="26"/>
+      <c r="C201" s="11"/>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A202" s="5"/>
+      <c r="B202" s="26"/>
+      <c r="C202" s="11"/>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A203" s="5"/>
+      <c r="B203" s="26"/>
+      <c r="C203" s="11"/>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A204" s="5"/>
+      <c r="B204" s="26"/>
+      <c r="C204" s="11"/>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A205" s="5"/>
+      <c r="B205" s="26"/>
+      <c r="C205" s="11"/>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A206" s="5"/>
+      <c r="B206" s="26"/>
+      <c r="C206" s="11"/>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A207" s="5"/>
+      <c r="B207" s="26"/>
+      <c r="C207" s="11"/>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A208" s="5"/>
+      <c r="B208" s="26"/>
+      <c r="C208" s="11"/>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A209" s="5"/>
+      <c r="B209" s="26"/>
+      <c r="C209" s="11"/>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A210" s="5"/>
+      <c r="B210" s="26"/>
+      <c r="C210" s="11"/>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A211" s="5"/>
+      <c r="B211" s="26"/>
+      <c r="C211" s="11"/>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A212" s="4"/>
+      <c r="B212" s="26"/>
+      <c r="C212" s="11"/>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A213" s="4"/>
+      <c r="B213" s="26"/>
+      <c r="C213" s="11"/>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A214" s="4"/>
+      <c r="B214" s="26"/>
+      <c r="C214" s="11"/>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A215" s="4"/>
+      <c r="B215" s="26"/>
+      <c r="C215" s="11"/>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A216" s="4"/>
+      <c r="B216" s="26"/>
+      <c r="C216" s="11"/>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A217" s="5"/>
+      <c r="B217" s="26"/>
+      <c r="C217" s="11"/>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A218" s="5"/>
+      <c r="B218" s="26"/>
+      <c r="C218" s="11"/>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A219" s="5"/>
+      <c r="B219" s="26"/>
+      <c r="C219" s="11"/>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A220" s="5"/>
+      <c r="B220" s="26"/>
+      <c r="C220" s="11"/>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A221" s="5"/>
+      <c r="B221" s="26"/>
+      <c r="C221" s="11"/>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A222" s="5"/>
+      <c r="B222" s="26"/>
+      <c r="C222" s="11"/>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A223" s="5"/>
+      <c r="B223" s="26"/>
+      <c r="C223" s="11"/>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A224" s="5"/>
+      <c r="B224" s="26"/>
+      <c r="C224" s="11"/>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A225" s="5"/>
+      <c r="B225" s="26"/>
+      <c r="C225" s="11"/>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A226" s="5"/>
+      <c r="B226" s="26"/>
+      <c r="C226" s="11"/>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A227" s="5"/>
+      <c r="B227" s="26"/>
+      <c r="C227" s="11"/>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A228" s="5"/>
+      <c r="B228" s="26"/>
+      <c r="C228" s="11"/>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A229" s="5"/>
+      <c r="B229" s="26"/>
+      <c r="C229" s="11"/>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A230" s="5"/>
+      <c r="B230" s="26"/>
+      <c r="C230" s="11"/>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A231" s="5"/>
+      <c r="B231" s="26"/>
+      <c r="C231" s="11"/>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A232" s="5"/>
+      <c r="B232" s="26"/>
+      <c r="C232" s="11"/>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A233" s="5"/>
+      <c r="B233" s="26"/>
+      <c r="C233" s="11"/>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A234" s="5"/>
+      <c r="B234" s="26"/>
+      <c r="C234" s="11"/>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A235" s="5"/>
+      <c r="B235" s="26"/>
+      <c r="C235" s="11"/>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A236" s="5"/>
+      <c r="B236" s="26"/>
+      <c r="C236" s="11"/>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A237" s="5"/>
+      <c r="B237" s="26"/>
+      <c r="C237" s="11"/>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A238" s="5"/>
+      <c r="B238" s="26"/>
+      <c r="C238" s="11"/>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A239" s="5"/>
+      <c r="B239" s="26"/>
+      <c r="C239" s="11"/>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A240" s="5"/>
+      <c r="B240" s="26"/>
+      <c r="C240" s="11"/>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A241" s="5"/>
+      <c r="B241" s="26"/>
+      <c r="C241" s="11"/>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A242" s="5"/>
+      <c r="B242" s="26"/>
+      <c r="C242" s="11"/>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A243" s="5"/>
+      <c r="B243" s="26"/>
+      <c r="C243" s="11"/>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A244" s="5"/>
+      <c r="B244" s="26"/>
+      <c r="C244" s="11"/>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A245" s="5"/>
+      <c r="B245" s="26"/>
+      <c r="C245" s="11"/>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A246" s="5"/>
+      <c r="B246" s="26"/>
+      <c r="C246" s="11"/>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A247" s="4"/>
+      <c r="B247" s="26"/>
+      <c r="C247" s="11"/>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A248" s="4"/>
+      <c r="B248" s="26"/>
+      <c r="C248" s="11"/>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A249" s="4"/>
+      <c r="B249" s="26"/>
+      <c r="C249" s="11"/>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A250" s="4"/>
+      <c r="B250" s="26"/>
+      <c r="C250" s="11"/>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A251" s="4"/>
+      <c r="B251" s="26"/>
+      <c r="C251" s="11"/>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A252" s="5"/>
+      <c r="B252" s="26"/>
+      <c r="C252" s="11"/>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A253" s="5"/>
+      <c r="B253" s="26"/>
+      <c r="C253" s="11"/>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A254" s="5"/>
+      <c r="B254" s="26"/>
+      <c r="C254" s="11"/>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A255" s="5"/>
+      <c r="B255" s="26"/>
+      <c r="C255" s="11"/>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A256" s="5"/>
+      <c r="B256" s="26"/>
+      <c r="C256" s="11"/>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A257" s="5"/>
+      <c r="B257" s="26"/>
+      <c r="C257" s="11"/>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A258" s="5"/>
+      <c r="B258" s="26"/>
+      <c r="C258" s="11"/>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A259" s="5"/>
+      <c r="B259" s="26"/>
+      <c r="C259" s="11"/>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A260" s="5"/>
+      <c r="B260" s="26"/>
+      <c r="C260" s="11"/>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A261" s="5"/>
+      <c r="B261" s="26"/>
+      <c r="C261" s="11"/>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A262" s="5"/>
+      <c r="B262" s="26"/>
+      <c r="C262" s="11"/>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A263" s="5"/>
+      <c r="B263" s="26"/>
+      <c r="C263" s="11"/>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A264" s="5"/>
+      <c r="B264" s="26"/>
+      <c r="C264" s="11"/>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A265" s="5"/>
+      <c r="B265" s="26"/>
+      <c r="C265" s="11"/>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A266" s="5"/>
+      <c r="B266" s="26"/>
+      <c r="C266" s="11"/>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A267" s="5"/>
+      <c r="B267" s="26"/>
+      <c r="C267" s="11"/>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A268" s="5"/>
+      <c r="B268" s="26"/>
+      <c r="C268" s="11"/>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A269" s="5"/>
+      <c r="B269" s="26"/>
+      <c r="C269" s="11"/>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A270" s="5"/>
+      <c r="B270" s="26"/>
+      <c r="C270" s="11"/>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A271" s="5"/>
+      <c r="B271" s="26"/>
+      <c r="C271" s="11"/>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A272" s="5"/>
+      <c r="B272" s="26"/>
+      <c r="C272" s="11"/>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A273" s="5"/>
+      <c r="B273" s="26"/>
+      <c r="C273" s="11"/>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A274" s="5"/>
+      <c r="B274" s="26"/>
+      <c r="C274" s="11"/>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A275" s="5"/>
+      <c r="B275" s="26"/>
+      <c r="C275" s="11"/>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A276" s="5"/>
+      <c r="B276" s="26"/>
+      <c r="C276" s="11"/>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A277" s="5"/>
+      <c r="B277" s="26"/>
+      <c r="C277" s="11"/>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A278" s="5"/>
+      <c r="B278" s="26"/>
+      <c r="C278" s="11"/>
+    </row>
+    <row r="279" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A279" s="5"/>
+      <c r="B279" s="26"/>
+      <c r="C279" s="11"/>
+    </row>
+    <row r="280" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A280" s="5"/>
+      <c r="B280" s="26"/>
+      <c r="C280" s="11"/>
+    </row>
+    <row r="281" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A281" s="5"/>
+      <c r="B281" s="26"/>
+      <c r="C281" s="11"/>
+    </row>
+    <row r="282" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A282" s="4"/>
+      <c r="B282" s="26"/>
+      <c r="C282" s="11"/>
+    </row>
+    <row r="283" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A283" s="4"/>
+      <c r="B283" s="26"/>
+      <c r="C283" s="11"/>
+    </row>
+    <row r="284" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A284" s="4"/>
+      <c r="B284" s="26"/>
+      <c r="C284" s="11"/>
+    </row>
+    <row r="285" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A285" s="4"/>
+      <c r="B285" s="26"/>
+      <c r="C285" s="11"/>
+    </row>
+    <row r="286" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A286" s="4"/>
+      <c r="B286" s="26"/>
+      <c r="C286" s="11"/>
+    </row>
+    <row r="287" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A287" s="5"/>
+      <c r="B287" s="26"/>
+      <c r="C287" s="11"/>
+    </row>
+    <row r="288" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A288" s="5"/>
+      <c r="B288" s="26"/>
+      <c r="C288" s="11"/>
+    </row>
+    <row r="289" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A289" s="5"/>
+      <c r="B289" s="26"/>
+      <c r="C289" s="11"/>
+    </row>
+    <row r="290" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A290" s="5"/>
+      <c r="B290" s="26"/>
+      <c r="C290" s="11"/>
+    </row>
+    <row r="291" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A291" s="5"/>
+      <c r="B291" s="26"/>
+      <c r="C291" s="11"/>
+    </row>
+    <row r="292" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A292" s="5"/>
+      <c r="B292" s="26"/>
+      <c r="C292" s="11"/>
+    </row>
+    <row r="293" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A293" s="5"/>
+      <c r="B293" s="26"/>
+      <c r="C293" s="11"/>
+    </row>
+    <row r="294" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A294" s="5"/>
+      <c r="B294" s="26"/>
+      <c r="C294" s="11"/>
+    </row>
+    <row r="295" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A295" s="5"/>
+      <c r="B295" s="26"/>
+      <c r="C295" s="11"/>
+    </row>
+    <row r="296" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A296" s="5"/>
+      <c r="B296" s="26"/>
+      <c r="C296" s="11"/>
+    </row>
+    <row r="297" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A297" s="5"/>
+      <c r="B297" s="26"/>
+      <c r="C297" s="11"/>
+    </row>
+    <row r="298" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A298" s="5"/>
+      <c r="B298" s="26"/>
+      <c r="C298" s="11"/>
+    </row>
+    <row r="299" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A299" s="5"/>
+      <c r="B299" s="26"/>
+      <c r="C299" s="11"/>
+    </row>
+    <row r="300" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A300" s="5"/>
+      <c r="B300" s="26"/>
+      <c r="C300" s="11"/>
+    </row>
+    <row r="301" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A301" s="5"/>
+      <c r="B301" s="26"/>
+      <c r="C301" s="11"/>
+    </row>
+    <row r="302" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A302" s="5"/>
+      <c r="B302" s="26"/>
+      <c r="C302" s="11"/>
+    </row>
+    <row r="303" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A303" s="5"/>
+      <c r="B303" s="26"/>
+      <c r="C303" s="11"/>
+    </row>
+    <row r="304" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A304" s="5"/>
+      <c r="B304" s="26"/>
+      <c r="C304" s="11"/>
+    </row>
+    <row r="305" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A305" s="5"/>
+      <c r="B305" s="26"/>
+      <c r="C305" s="11"/>
+    </row>
+    <row r="306" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A306" s="5"/>
+      <c r="B306" s="26"/>
+      <c r="C306" s="11"/>
+    </row>
+    <row r="307" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A307" s="5"/>
+      <c r="B307" s="26"/>
+      <c r="C307" s="11"/>
+    </row>
+    <row r="308" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A308" s="5"/>
+      <c r="B308" s="26"/>
+      <c r="C308" s="11"/>
+    </row>
+    <row r="309" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A309" s="5"/>
+      <c r="B309" s="26"/>
+      <c r="C309" s="11"/>
+    </row>
+    <row r="310" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A310" s="5"/>
+      <c r="B310" s="26"/>
+      <c r="C310" s="11"/>
+    </row>
+    <row r="311" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A311" s="5"/>
+      <c r="B311" s="26"/>
+      <c r="C311" s="11"/>
+    </row>
+    <row r="312" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A312" s="5"/>
+      <c r="B312" s="26"/>
+      <c r="C312" s="11"/>
+    </row>
+    <row r="313" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A313" s="5"/>
+      <c r="B313" s="26"/>
+      <c r="C313" s="11"/>
+    </row>
+    <row r="314" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A314" s="5"/>
+      <c r="B314" s="26"/>
+      <c r="C314" s="11"/>
+    </row>
+    <row r="315" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A315" s="5"/>
+      <c r="B315" s="26"/>
+      <c r="C315" s="11"/>
+    </row>
+    <row r="316" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A316" s="5"/>
+      <c r="B316" s="26"/>
+      <c r="C316" s="11"/>
+    </row>
+    <row r="317" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A317" s="4"/>
+      <c r="B317" s="26"/>
+      <c r="C317" s="11"/>
+    </row>
+    <row r="318" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A318" s="4"/>
+      <c r="B318" s="26"/>
+      <c r="C318" s="11"/>
+    </row>
+    <row r="319" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A319" s="4"/>
+      <c r="B319" s="26"/>
+      <c r="C319" s="11"/>
+    </row>
+    <row r="320" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A320" s="4"/>
+      <c r="B320" s="26"/>
+      <c r="C320" s="11"/>
+    </row>
+    <row r="321" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A321" s="4"/>
+      <c r="B321" s="26"/>
+      <c r="C321" s="11"/>
+    </row>
+    <row r="322" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A322" s="5"/>
+      <c r="B322" s="26"/>
+      <c r="C322" s="11"/>
+    </row>
+    <row r="323" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A323" s="5"/>
+      <c r="B323" s="26"/>
+      <c r="C323" s="11"/>
+    </row>
+    <row r="324" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A324" s="5"/>
+      <c r="B324" s="26"/>
+      <c r="C324" s="11"/>
+    </row>
+    <row r="325" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A325" s="5"/>
+      <c r="B325" s="26"/>
+      <c r="C325" s="11"/>
+    </row>
+    <row r="326" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A326" s="5"/>
+      <c r="B326" s="26"/>
+      <c r="C326" s="11"/>
+    </row>
+    <row r="327" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A327" s="5"/>
+      <c r="B327" s="26"/>
+      <c r="C327" s="11"/>
+    </row>
+    <row r="328" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A328" s="5"/>
+      <c r="B328" s="26"/>
+      <c r="C328" s="11"/>
+    </row>
+    <row r="329" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A329" s="5"/>
+      <c r="B329" s="26"/>
+      <c r="C329" s="11"/>
+    </row>
+    <row r="330" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A330" s="5"/>
+      <c r="B330" s="26"/>
+      <c r="C330" s="11"/>
+    </row>
+    <row r="331" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A331" s="5"/>
+      <c r="B331" s="26"/>
+      <c r="C331" s="11"/>
+    </row>
+    <row r="332" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A332" s="5"/>
+      <c r="B332" s="26"/>
+      <c r="C332" s="11"/>
+    </row>
+    <row r="333" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A333" s="5"/>
+      <c r="B333" s="26"/>
+      <c r="C333" s="11"/>
+    </row>
+    <row r="334" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A334" s="5"/>
+      <c r="B334" s="26"/>
+      <c r="C334" s="11"/>
+    </row>
+    <row r="335" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A335" s="5"/>
+      <c r="B335" s="26"/>
+      <c r="C335" s="11"/>
+    </row>
+    <row r="336" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A336" s="5"/>
+      <c r="B336" s="26"/>
+      <c r="C336" s="11"/>
+    </row>
+    <row r="337" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A337" s="5"/>
+      <c r="B337" s="26"/>
+      <c r="C337" s="11"/>
+    </row>
+    <row r="338" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A338" s="5"/>
+      <c r="B338" s="26"/>
+      <c r="C338" s="11"/>
+    </row>
+    <row r="339" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A339" s="5"/>
+      <c r="B339" s="26"/>
+      <c r="C339" s="11"/>
+    </row>
+    <row r="340" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A340" s="5"/>
+      <c r="B340" s="26"/>
+      <c r="C340" s="11"/>
+    </row>
+    <row r="341" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A341" s="5"/>
+      <c r="B341" s="26"/>
+      <c r="C341" s="11"/>
+    </row>
+    <row r="342" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A342" s="5"/>
+      <c r="B342" s="26"/>
+      <c r="C342" s="11"/>
+    </row>
+    <row r="343" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A343" s="5"/>
+      <c r="B343" s="26"/>
+      <c r="C343" s="11"/>
+    </row>
+    <row r="344" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A344" s="5"/>
+      <c r="B344" s="26"/>
+      <c r="C344" s="11"/>
+    </row>
+    <row r="345" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A345" s="5"/>
+      <c r="B345" s="26"/>
+      <c r="C345" s="11"/>
+    </row>
+    <row r="346" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A346" s="5"/>
+      <c r="B346" s="26"/>
+      <c r="C346" s="11"/>
+    </row>
+    <row r="347" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A347" s="5"/>
+      <c r="B347" s="26"/>
+      <c r="C347" s="11"/>
+    </row>
+    <row r="348" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A348" s="5"/>
+      <c r="B348" s="26"/>
+      <c r="C348" s="11"/>
+    </row>
+    <row r="349" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A349" s="5"/>
+      <c r="B349" s="26"/>
+      <c r="C349" s="11"/>
+    </row>
+    <row r="350" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A350" s="5"/>
+      <c r="B350" s="26"/>
+      <c r="C350" s="11"/>
+    </row>
+    <row r="351" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A351" s="5"/>
+      <c r="B351" s="26"/>
+      <c r="C351" s="11"/>
+    </row>
+    <row r="352" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A352" s="4"/>
+      <c r="B352" s="26"/>
+      <c r="C352" s="11"/>
+    </row>
+    <row r="353" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A353" s="4"/>
+      <c r="B353" s="26"/>
+      <c r="C353" s="11"/>
+    </row>
+    <row r="354" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A354" s="4"/>
+      <c r="B354" s="26"/>
+      <c r="C354" s="11"/>
+    </row>
+    <row r="355" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A355" s="4"/>
+      <c r="B355" s="26"/>
+      <c r="C355" s="11"/>
+    </row>
+    <row r="356" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A356" s="4"/>
+      <c r="B356" s="26"/>
+      <c r="C356" s="11"/>
+    </row>
+    <row r="357" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A357" s="5"/>
+      <c r="B357" s="26"/>
+      <c r="C357" s="11"/>
+    </row>
+    <row r="358" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A358" s="5"/>
+      <c r="B358" s="26"/>
+      <c r="C358" s="11"/>
+    </row>
+    <row r="359" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A359" s="5"/>
+      <c r="B359" s="26"/>
+      <c r="C359" s="11"/>
+    </row>
+    <row r="360" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A360" s="5"/>
+      <c r="B360" s="26"/>
+      <c r="C360" s="11"/>
+    </row>
+    <row r="361" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A361" s="5"/>
+      <c r="B361" s="26"/>
+      <c r="C361" s="11"/>
+    </row>
+    <row r="362" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A362" s="5"/>
+      <c r="B362" s="26"/>
+      <c r="C362" s="11"/>
+    </row>
+    <row r="363" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A363" s="5"/>
+      <c r="B363" s="26"/>
+      <c r="C363" s="11"/>
+    </row>
+    <row r="364" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A364" s="5"/>
+      <c r="B364" s="26"/>
+      <c r="C364" s="11"/>
+    </row>
+    <row r="365" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A365" s="5"/>
+      <c r="B365" s="26"/>
+      <c r="C365" s="11"/>
+    </row>
+    <row r="366" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A366" s="5"/>
+      <c r="B366" s="26"/>
+      <c r="C366" s="11"/>
+    </row>
+    <row r="367" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A367" s="5"/>
+      <c r="B367" s="26"/>
+      <c r="C367" s="11"/>
+    </row>
+    <row r="368" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A368" s="5"/>
+      <c r="B368" s="26"/>
+      <c r="C368" s="11"/>
+    </row>
+    <row r="369" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A369" s="5"/>
+      <c r="B369" s="26"/>
+      <c r="C369" s="11"/>
+    </row>
+    <row r="370" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A370" s="5"/>
+      <c r="B370" s="26"/>
+      <c r="C370" s="11"/>
+    </row>
+    <row r="371" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A371" s="5"/>
+      <c r="B371" s="26"/>
+      <c r="C371" s="11"/>
+    </row>
+    <row r="372" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A372" s="5"/>
+      <c r="B372" s="26"/>
+      <c r="C372" s="11"/>
+    </row>
+    <row r="373" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A373" s="5"/>
+      <c r="B373" s="26"/>
+      <c r="C373" s="11"/>
+    </row>
+    <row r="374" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A374" s="5"/>
+      <c r="B374" s="26"/>
+      <c r="C374" s="11"/>
+    </row>
+    <row r="375" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A375" s="5"/>
+      <c r="B375" s="26"/>
+      <c r="C375" s="11"/>
+    </row>
+    <row r="376" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A376" s="5"/>
+      <c r="B376" s="26"/>
+      <c r="C376" s="11"/>
+    </row>
+    <row r="377" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A377" s="5"/>
+      <c r="B377" s="26"/>
+      <c r="C377" s="11"/>
+    </row>
+    <row r="378" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A378" s="5"/>
+      <c r="B378" s="26"/>
+      <c r="C378" s="11"/>
+    </row>
+    <row r="379" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A379" s="5"/>
+      <c r="B379" s="26"/>
+      <c r="C379" s="11"/>
+    </row>
+    <row r="380" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A380" s="5"/>
+      <c r="B380" s="26"/>
+      <c r="C380" s="11"/>
+    </row>
+    <row r="381" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A381" s="5"/>
+      <c r="B381" s="26"/>
+      <c r="C381" s="11"/>
+    </row>
+    <row r="382" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A382" s="5"/>
+      <c r="B382" s="26"/>
+      <c r="C382" s="11"/>
+    </row>
+    <row r="383" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A383" s="5"/>
+      <c r="B383" s="26"/>
+      <c r="C383" s="11"/>
+    </row>
+    <row r="384" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A384" s="5"/>
+      <c r="B384" s="26"/>
+      <c r="C384" s="11"/>
+    </row>
+    <row r="385" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A385" s="5"/>
+      <c r="B385" s="26"/>
+      <c r="C385" s="11"/>
+    </row>
+    <row r="386" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A386" s="5"/>
+      <c r="B386" s="26"/>
+      <c r="C386" s="11"/>
+    </row>
+    <row r="387" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A387" s="4"/>
+      <c r="B387" s="26"/>
+      <c r="C387" s="11"/>
+    </row>
+    <row r="388" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A388" s="4"/>
+      <c r="B388" s="26"/>
+      <c r="C388" s="11"/>
+    </row>
+    <row r="389" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A389" s="4"/>
+      <c r="B389" s="26"/>
+      <c r="C389" s="11"/>
+    </row>
+    <row r="390" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A390" s="4"/>
+      <c r="B390" s="26"/>
+      <c r="C390" s="11"/>
+    </row>
+    <row r="391" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A391" s="4"/>
+      <c r="B391" s="26"/>
+      <c r="C391" s="11"/>
+    </row>
+    <row r="392" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A392" s="5"/>
+      <c r="B392" s="26"/>
+      <c r="C392" s="11"/>
+    </row>
+    <row r="393" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A393" s="5"/>
+      <c r="B393" s="26"/>
+      <c r="C393" s="11"/>
+    </row>
+    <row r="394" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A394" s="5"/>
+      <c r="B394" s="26"/>
+      <c r="C394" s="11"/>
+    </row>
+    <row r="395" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A395" s="5"/>
+      <c r="B395" s="26"/>
+      <c r="C395" s="11"/>
+    </row>
+    <row r="396" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A396" s="5"/>
+      <c r="B396" s="26"/>
+      <c r="C396" s="11"/>
+    </row>
+    <row r="397" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A397" s="5"/>
+      <c r="B397" s="26"/>
+      <c r="C397" s="11"/>
+    </row>
+    <row r="398" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A398" s="5"/>
+      <c r="B398" s="26"/>
+      <c r="C398" s="11"/>
+    </row>
+    <row r="399" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A399" s="5"/>
+      <c r="B399" s="26"/>
+      <c r="C399" s="11"/>
+    </row>
+    <row r="400" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A400" s="5"/>
+      <c r="B400" s="26"/>
+      <c r="C400" s="11"/>
+    </row>
+    <row r="401" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A401" s="5"/>
+      <c r="B401" s="26"/>
+      <c r="C401" s="11"/>
+    </row>
+    <row r="402" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A402" s="5"/>
+      <c r="B402" s="26"/>
+      <c r="C402" s="11"/>
+    </row>
+    <row r="403" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A403" s="5"/>
+      <c r="B403" s="26"/>
+      <c r="C403" s="11"/>
+    </row>
+    <row r="404" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A404" s="5"/>
+      <c r="B404" s="26"/>
+      <c r="C404" s="11"/>
+    </row>
+    <row r="405" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A405" s="5"/>
+      <c r="B405" s="26"/>
+      <c r="C405" s="11"/>
+    </row>
+    <row r="406" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A406" s="5"/>
+      <c r="B406" s="26"/>
+      <c r="C406" s="11"/>
+    </row>
+    <row r="407" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A407" s="5"/>
+      <c r="B407" s="26"/>
+      <c r="C407" s="11"/>
+    </row>
+    <row r="408" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A408" s="5"/>
+      <c r="B408" s="26"/>
+      <c r="C408" s="11"/>
+    </row>
+    <row r="409" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A409" s="5"/>
+      <c r="B409" s="26"/>
+      <c r="C409" s="11"/>
+    </row>
+    <row r="410" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A410" s="5"/>
+      <c r="B410" s="26"/>
+      <c r="C410" s="11"/>
+    </row>
+    <row r="411" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A411" s="5"/>
+      <c r="B411" s="26"/>
+      <c r="C411" s="11"/>
+    </row>
+    <row r="412" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A412" s="5"/>
+      <c r="B412" s="26"/>
+      <c r="C412" s="11"/>
+    </row>
+    <row r="413" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A413" s="5"/>
+      <c r="B413" s="26"/>
+      <c r="C413" s="11"/>
+    </row>
+    <row r="414" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A414" s="5"/>
+      <c r="B414" s="26"/>
+      <c r="C414" s="11"/>
+    </row>
+    <row r="415" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A415" s="5"/>
+      <c r="B415" s="26"/>
+      <c r="C415" s="11"/>
+    </row>
+    <row r="416" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A416" s="5"/>
+      <c r="B416" s="26"/>
+      <c r="C416" s="11"/>
+    </row>
+    <row r="417" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A417" s="5"/>
+      <c r="B417" s="26"/>
+      <c r="C417" s="11"/>
+    </row>
+    <row r="418" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A418" s="5"/>
+      <c r="B418" s="26"/>
+      <c r="C418" s="11"/>
+    </row>
+    <row r="419" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A419" s="5"/>
+      <c r="B419" s="26"/>
+      <c r="C419" s="11"/>
+    </row>
+    <row r="420" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A420" s="5"/>
+      <c r="B420" s="26"/>
+      <c r="C420" s="11"/>
+    </row>
+    <row r="421" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A421" s="5"/>
+      <c r="B421" s="26"/>
+      <c r="C421" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/HelloFresh_Absorption_Fall2025.xlsx
+++ b/HelloFresh_Absorption_Fall2025.xlsx
@@ -8,17 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/stn424_ads_northwestern_edu/Documents/Collaborations/Proposals/GO-Barrier, TFMI Proposals with Tim Wei/URAP_2023-10/Shared/Lanning, Mackenzie/Absorption Data/Fall 2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1712" documentId="13_ncr:1_{F2E763B4-4DB6-894B-B240-8188D6068E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8CEF8C6-F78E-8742-AFFB-1CA691E0992F}"/>
+  <xr:revisionPtr revIDLastSave="2119" documentId="13_ncr:1_{F2E763B4-4DB6-894B-B240-8188D6068E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EB26540-F5B1-1341-95D7-B9E92C4367C1}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17180" activeTab="5" xr2:uid="{304DC28A-0BB6-064B-B35E-217EA1A1C90F}"/>
+    <workbookView xWindow="13980" yWindow="740" windowWidth="15420" windowHeight="17180" firstSheet="1" activeTab="4" xr2:uid="{304DC28A-0BB6-064B-B35E-217EA1A1C90F}"/>
   </bookViews>
   <sheets>
     <sheet name="Crayola Method" sheetId="1" r:id="rId1"/>
     <sheet name="Boat Method" sheetId="2" r:id="rId2"/>
     <sheet name="Boat Method (Retest)" sheetId="4" r:id="rId3"/>
     <sheet name="Metsä EB" sheetId="3" r:id="rId4"/>
-    <sheet name="Formatting for R" sheetId="5" r:id="rId5"/>
-    <sheet name="Figures for R" sheetId="6" r:id="rId6"/>
+    <sheet name="Absorption for R" sheetId="7" r:id="rId5"/>
+    <sheet name="Formatting for R" sheetId="5" r:id="rId6"/>
+    <sheet name="Figures for R" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="58">
   <si>
     <t>Raw Weights (gms)</t>
   </si>
@@ -209,6 +210,12 @@
   </si>
   <si>
     <t>0.2% GO</t>
+  </si>
+  <si>
+    <t>Absorption Raw</t>
+  </si>
+  <si>
+    <t>Absorption Large</t>
   </si>
 </sst>
 </file>
@@ -9551,6 +9558,1705 @@
 </file>
 
 <file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1200" i="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>HelloFresh</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Boat Method (Retest)'!$D$141</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DI Water @ 100°C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:errBars>
+            <c:errDir val="y"/>
+            <c:errBarType val="both"/>
+            <c:errValType val="cust"/>
+            <c:noEndCap val="0"/>
+            <c:plus>
+              <c:numRef>
+                <c:f>'Boat Method (Retest)'!$D$142:$D$148</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="7"/>
+                  <c:pt idx="0">
+                    <c:v>0</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0.12723213842582981</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0.13136292466267202</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>0.134284860746891</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>0.12517170131277844</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>0.109941473521196</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>0.10419045694508391</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:plus>
+            <c:minus>
+              <c:numRef>
+                <c:f>'Boat Method (Retest)'!$D$142:$D$148</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="7"/>
+                  <c:pt idx="0">
+                    <c:v>0</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0.12723213842582981</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0.13136292466267202</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>0.134284860746891</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>0.12517170131277844</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>0.109941473521196</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>0.10419045694508391</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:minus>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Boat Method (Retest)'!$B$130:$B$136</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Boat Method (Retest)'!$D$130:$D$136</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.4364713004960451</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.51531160069446025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.53478420496033385</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.57372941349208095</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.59462684246033559</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.62169851180557445</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-8742-6A45-8E5C-190D3C5459B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Boat Method (Retest)'!$I$129</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.1% GO @ 100°C </c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Boat Method (Retest)'!$B$130:$B$136</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Boat Method (Retest)'!$I$130:$I$136</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.29257448220778787</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.3111973135710977</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.32736977238660353</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.34550252924035252</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.34746282727859573</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.35677424296025051</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000008-8742-6A45-8E5C-190D3C5459B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Boat Method (Retest)'!$R$129</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>25% WBBC @ 100°C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Boat Method (Retest)'!$B$130:$B$136</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Boat Method (Retest)'!$R$130:$R$136</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13836403442827419</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.21103594568585438</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.23731279495413199</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.24470315881083501</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.25086179535808761</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.25250409843735494</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000009-8742-6A45-8E5C-190D3C5459B4}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="35411248"/>
+        <c:axId val="9409920"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="35411248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="60"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t>time (min)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="in"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="9409920"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="9409920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t>absorbed water weight / unit dry paper weight (gm/gm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="in"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="35411248"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.8038751991516695"/>
+          <c:y val="0.17533106156733624"/>
+          <c:w val="0.17693780588355021"/>
+          <c:h val="0.11296035888095081"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" sz="1200" i="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>HelloFresh</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Boat Method (Retest)'!$D$141</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>DI Water @ 100°C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:prstDash val="sysDot"/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:errBars>
+            <c:errDir val="y"/>
+            <c:errBarType val="both"/>
+            <c:errValType val="cust"/>
+            <c:noEndCap val="0"/>
+            <c:plus>
+              <c:numRef>
+                <c:f>'Boat Method (Retest)'!$D$142:$D$148</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="7"/>
+                  <c:pt idx="0">
+                    <c:v>0</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0.12723213842582981</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0.13136292466267202</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>0.134284860746891</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>0.12517170131277844</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>0.109941473521196</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>0.10419045694508391</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:plus>
+            <c:minus>
+              <c:numRef>
+                <c:f>'Boat Method (Retest)'!$D$142:$D$148</c:f>
+                <c:numCache>
+                  <c:formatCode>General</c:formatCode>
+                  <c:ptCount val="7"/>
+                  <c:pt idx="0">
+                    <c:v>0</c:v>
+                  </c:pt>
+                  <c:pt idx="1">
+                    <c:v>0.12723213842582981</c:v>
+                  </c:pt>
+                  <c:pt idx="2">
+                    <c:v>0.13136292466267202</c:v>
+                  </c:pt>
+                  <c:pt idx="3">
+                    <c:v>0.134284860746891</c:v>
+                  </c:pt>
+                  <c:pt idx="4">
+                    <c:v>0.12517170131277844</c:v>
+                  </c:pt>
+                  <c:pt idx="5">
+                    <c:v>0.109941473521196</c:v>
+                  </c:pt>
+                  <c:pt idx="6">
+                    <c:v>0.10419045694508391</c:v>
+                  </c:pt>
+                </c:numCache>
+              </c:numRef>
+            </c:minus>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:round/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:errBars>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Boat Method (Retest)'!$B$130:$B$136</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Boat Method (Retest)'!$D$130:$D$136</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.4364713004960451</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.51531160069446025</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.53478420496033385</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.57372941349208095</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.59462684246033559</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.62169851180557445</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-6117-724C-AB49-EC257783BEDE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Boat Method (Retest)'!$M$129</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.5 wt% GO @ 100°C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="6"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Boat Method (Retest)'!$B$130:$B$136</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Boat Method (Retest)'!$M$130:$M$136</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.26322584290738199</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.28009929437580394</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.29166966109700754</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.2960085486174589</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.3008295347512937</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.30275792920482769</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-6117-724C-AB49-EC257783BEDE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Boat Method (Retest)'!$Q$129</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>15% WBBC @ 100°C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Boat Method (Retest)'!$B$130:$B$136</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Boat Method (Retest)'!$Q$130:$Q$136</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.18855657823047495</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.2238550845816776</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.22698280033431581</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.23100414915913636</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.23189778223131868</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.23457868144786573</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-6117-724C-AB49-EC257783BEDE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Boat Method (Retest)'!$K$129</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.2 wt% GO @ 100°C</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent4"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Boat Method (Retest)'!$B$130:$B$136</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>20</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>50</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>60</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Boat Method (Retest)'!$K$130:$K$136</c:f>
+              <c:numCache>
+                <c:formatCode>0.0000</c:formatCode>
+                <c:ptCount val="7"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.26497392836152356</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.28254126062858592</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.29181290821397998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.30791629612545385</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.31279611064408219</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.31084418483663079</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-6117-724C-AB49-EC257783BEDE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="35411248"/>
+        <c:axId val="9409920"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="35411248"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="60"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t>time (min)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="in"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="9409920"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="9409920"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="1"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US" sz="1200" i="1">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
+                  <a:t>absorbed water weight / unit dry paper weight (gm/gm)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="0"/>
+        <c:majorTickMark val="in"/>
+        <c:minorTickMark val="in"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="35411248"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.8038751991516695"/>
+          <c:y val="0.17533106156733624"/>
+          <c:w val="0.17693780588355021"/>
+          <c:h val="0.15061381184126774"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -19824,6 +21530,86 @@
 </file>
 
 <file path=xl/charts/colors16.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors17.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors18.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -23796,6 +25582,1038 @@
 </file>
 
 <file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style17.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style18.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -29021,6 +31839,82 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>216</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>178931</xdr:colOff>
+      <xdr:row>244</xdr:row>
+      <xdr:rowOff>14625</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CBA7F87-0856-434F-A5AC-3CBD2D74C179}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>172469</xdr:colOff>
+      <xdr:row>217</xdr:row>
+      <xdr:rowOff>141112</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>194610</xdr:colOff>
+      <xdr:row>245</xdr:row>
+      <xdr:rowOff>155737</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D128520D-850E-574E-9D2D-6B60E4E7BE08}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -29764,7 +32658,10 @@
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
+      <c r="C9" s="5">
+        <f>AVERAGE(C4:C8)</f>
+        <v>0.33939999999999998</v>
+      </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -31453,11 +34350,11 @@
         <v>0</v>
       </c>
       <c r="C49" s="7">
-        <f t="shared" ref="C49:F53" si="0" xml:space="preserve"> (C4-C4)/14.52</f>
+        <f xml:space="preserve"> (C4-C4)/14.52</f>
         <v>0</v>
       </c>
       <c r="D49" s="7">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="C49:F53" si="0" xml:space="preserve"> (D4-D4)/14.52</f>
         <v>0</v>
       </c>
       <c r="E49" s="7">
@@ -32605,7 +35502,7 @@
         <v>30</v>
       </c>
       <c r="C70" s="7">
-        <f t="shared" si="44"/>
+        <f xml:space="preserve"> (C25-C7)/14.52</f>
         <v>5.2341597796143223E-3</v>
       </c>
       <c r="D70" s="7">
@@ -32928,7 +35825,7 @@
         <v>40</v>
       </c>
       <c r="C76" s="7">
-        <f t="shared" si="61"/>
+        <f xml:space="preserve"> (C31-C7)/14.52</f>
         <v>5.9228650137741028E-3</v>
       </c>
       <c r="D76" s="7">
@@ -34488,11 +37385,11 @@
         <v>30</v>
       </c>
       <c r="C108" s="7">
-        <f t="shared" ref="C108:K108" si="139" xml:space="preserve"> STDEV(C67:C71)*32.258/AVERAGE(C4:C8)</f>
+        <f xml:space="preserve"> STDEV(C67:C71)*32.258/AVERAGE(C4:C8)</f>
         <v>5.1207632133280175E-2</v>
       </c>
       <c r="D108" s="7">
-        <f t="shared" si="139"/>
+        <f t="shared" ref="D108:K108" si="139" xml:space="preserve"> STDEV(D67:D71)*32.258/AVERAGE(D4:D8)</f>
         <v>0.53417540201550062</v>
       </c>
       <c r="E108" s="7">
@@ -34547,11 +37444,11 @@
         <v>40</v>
       </c>
       <c r="C109" s="7">
-        <f t="shared" ref="C109:K109" si="142" xml:space="preserve"> STDEV(C73:C77)*32.258/AVERAGE(C4:C8)</f>
+        <f xml:space="preserve"> STDEV(C73:C77)*32.258/AVERAGE(C4:C8)</f>
         <v>6.902578857180762E-2</v>
       </c>
       <c r="D109" s="7">
-        <f t="shared" si="142"/>
+        <f t="shared" ref="D109:K109" si="142" xml:space="preserve"> STDEV(D73:D77)*32.258/AVERAGE(D4:D8)</f>
         <v>0.47029695344489003</v>
       </c>
       <c r="E109" s="7">
@@ -40388,6 +43285,7 @@
       <c r="G8" s="11">
         <v>0.32100000000000001</v>
       </c>
+      <c r="H8" s="24"/>
       <c r="I8" s="11">
         <v>0.32800000000000001</v>
       </c>
@@ -42852,7 +45750,7 @@
         <v>20</v>
       </c>
       <c r="C68" s="7">
-        <f t="shared" si="42"/>
+        <f xml:space="preserve"> (C17-C5)/32.258</f>
         <v>4.061008122016244E-3</v>
       </c>
       <c r="D68" s="7">
@@ -44700,11 +47598,11 @@
         <v>10</v>
       </c>
       <c r="C107" s="12">
-        <f t="shared" ref="C107:G107" si="151" xml:space="preserve"> AVERAGE(C61:C65)*10000</f>
+        <f xml:space="preserve"> AVERAGE(C61:C65)*10000</f>
         <v>37.634075268150532</v>
       </c>
       <c r="D107" s="12">
-        <f t="shared" si="151"/>
+        <f t="shared" ref="C107:G107" si="151" xml:space="preserve"> AVERAGE(D61:D65)*10000</f>
         <v>56.978113956227901</v>
       </c>
       <c r="E107" s="12">
@@ -45772,11 +48670,11 @@
         <v>10</v>
       </c>
       <c r="C131" s="7">
-        <f t="shared" ref="C131:E131" si="214">AVERAGE(C61:C65)*25.8/AVERAGE(C4:C8)</f>
+        <f>AVERAGE(C61:C65)*25.8/AVERAGE(C4:C8)</f>
         <v>0.2944084723827422</v>
       </c>
       <c r="D131" s="7">
-        <f t="shared" si="214"/>
+        <f t="shared" ref="C131:E131" si="214">AVERAGE(D61:D65)*25.8/AVERAGE(D4:D8)</f>
         <v>0.4364713004960451</v>
       </c>
       <c r="E131" s="7">
@@ -45835,11 +48733,11 @@
         <v>20</v>
       </c>
       <c r="C132" s="7">
-        <f t="shared" ref="C132:E132" si="218">AVERAGE(C67:C71)*25.8/AVERAGE(C4:C8)</f>
+        <f>AVERAGE(C67:C71)*25.8/AVERAGE(C4:C8)</f>
         <v>0.32496487066958368</v>
       </c>
       <c r="D132" s="7">
-        <f t="shared" si="218"/>
+        <f t="shared" ref="C132:E132" si="218">AVERAGE(D67:D71)*25.8/AVERAGE(D4:D8)</f>
         <v>0.51531160069446025</v>
       </c>
       <c r="E132" s="7">
@@ -46112,7 +49010,7 @@
         <v>0.35677424296025051</v>
       </c>
       <c r="J136" s="7">
-        <f t="shared" ref="I136:M136" si="236">AVERAGE(J91:J95)*25.8/AVERAGE(J4:J8)</f>
+        <f t="shared" ref="J136:M136" si="236">AVERAGE(J91:J95)*25.8/AVERAGE(J4:J8)</f>
         <v>0.35096779054317595</v>
       </c>
       <c r="K136" s="7">
@@ -46315,7 +49213,7 @@
         <v>0.12723213842582981</v>
       </c>
       <c r="E143" s="7">
-        <f t="shared" ref="C143:E143" si="243" xml:space="preserve"> STDEV(E61:E65)*22.58/AVERAGE(E4:E8)</f>
+        <f t="shared" ref="E143" si="243" xml:space="preserve"> STDEV(E61:E65)*22.58/AVERAGE(E4:E8)</f>
         <v>0.10299723685496648</v>
       </c>
       <c r="F143" s="7">
@@ -46395,7 +49293,7 @@
         <v>9.9438732493841893E-3</v>
       </c>
       <c r="J144" s="7">
-        <f t="shared" ref="I144:M144" si="250" xml:space="preserve"> STDEV(J67:J71)*22.58/AVERAGE(J4:J8)</f>
+        <f t="shared" ref="J144:M144" si="250" xml:space="preserve"> STDEV(J67:J71)*22.58/AVERAGE(J4:J8)</f>
         <v>1.5473952385165919E-2</v>
       </c>
       <c r="K144" s="7">
@@ -50726,6 +53624,6334 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43CB27B-6453-3E45-8189-F45331D133AA}">
+  <dimension ref="A1:D421"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="3" max="3" width="16.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A1" s="25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="25" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>0</v>
+      </c>
+      <c r="B2" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C2" s="27">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <f>C2 * 10000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A3" s="4">
+        <v>0</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" s="27">
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f t="shared" ref="D3:D66" si="0">C3 * 10000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A4" s="4">
+        <v>0</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="27">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="4">
+        <v>0</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="27">
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
+        <v>0</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="27">
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="5">
+        <v>10</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="27">
+        <v>3.7510075020150036E-3</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="0"/>
+        <v>37.510075020150033</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="5">
+        <v>10</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="27">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D8">
+        <f t="shared" si="0"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A9" s="5">
+        <v>10</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" s="27">
+        <v>3.9680079360158715E-3</v>
+      </c>
+      <c r="D9">
+        <f t="shared" si="0"/>
+        <v>39.680079360158715</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A10" s="5">
+        <v>10</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C10" s="27">
+        <v>3.5960071920143836E-3</v>
+      </c>
+      <c r="D10">
+        <f t="shared" si="0"/>
+        <v>35.960071920143832</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="27">
+        <v>3.8130076260152516E-3</v>
+      </c>
+      <c r="D11">
+        <f t="shared" si="0"/>
+        <v>38.130076260152514</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A12" s="5">
+        <v>20</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C12" s="27">
+        <v>4.2470084940169879E-3</v>
+      </c>
+      <c r="D12">
+        <f t="shared" si="0"/>
+        <v>42.470084940169876</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A13" s="5">
+        <v>20</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" s="27">
+        <v>4.061008122016244E-3</v>
+      </c>
+      <c r="D13">
+        <f t="shared" si="0"/>
+        <v>40.610081220162442</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A14" s="5">
+        <v>20</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C14" s="27">
+        <v>4.123008246016492E-3</v>
+      </c>
+      <c r="D14">
+        <f t="shared" si="0"/>
+        <v>41.230082460164923</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A15" s="5">
+        <v>20</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="27">
+        <v>3.9060078120156235E-3</v>
+      </c>
+      <c r="D15">
+        <f t="shared" si="0"/>
+        <v>39.060078120156234</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A16" s="5">
+        <v>20</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="27">
+        <v>4.4330088660177302E-3</v>
+      </c>
+      <c r="D16">
+        <f t="shared" si="0"/>
+        <v>44.330088660177303</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="5">
+        <v>30</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="27">
+        <v>4.5260090520181026E-3</v>
+      </c>
+      <c r="D17">
+        <f t="shared" si="0"/>
+        <v>45.260090520181024</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="5">
+        <v>30</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="27">
+        <v>4.3400086800173586E-3</v>
+      </c>
+      <c r="D18">
+        <f t="shared" si="0"/>
+        <v>43.40008680017359</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="5">
+        <v>30</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="27">
+        <v>4.5880091760183506E-3</v>
+      </c>
+      <c r="D19">
+        <f t="shared" si="0"/>
+        <v>45.880091760183504</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="5">
+        <v>30</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C20" s="27">
+        <v>4.4020088040176084E-3</v>
+      </c>
+      <c r="D20">
+        <f t="shared" si="0"/>
+        <v>44.020088040176084</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="5">
+        <v>30</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="27">
+        <v>4.929009858019715E-3</v>
+      </c>
+      <c r="D21">
+        <f t="shared" si="0"/>
+        <v>49.290098580197153</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="5">
+        <v>40</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="10">
+        <v>4.6190092380184742E-3</v>
+      </c>
+      <c r="D22">
+        <f t="shared" si="0"/>
+        <v>46.190092380184744</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="5">
+        <v>40</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="10">
+        <v>4.4020088040176066E-3</v>
+      </c>
+      <c r="D23">
+        <f t="shared" si="0"/>
+        <v>44.020088040176063</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="5">
+        <v>40</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C24" s="10">
+        <v>4.867009734019467E-3</v>
+      </c>
+      <c r="D24">
+        <f t="shared" si="0"/>
+        <v>48.670097340194673</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="5">
+        <v>40</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" s="10">
+        <v>4.4640089280178563E-3</v>
+      </c>
+      <c r="D25">
+        <f t="shared" si="0"/>
+        <v>44.640089280178564</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="5">
+        <v>40</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C26" s="10">
+        <v>5.0840101680203345E-3</v>
+      </c>
+      <c r="D26">
+        <f t="shared" si="0"/>
+        <v>50.840101680203347</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="5">
+        <v>50</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="10">
+        <v>4.9600099200198386E-3</v>
+      </c>
+      <c r="D27">
+        <f t="shared" si="0"/>
+        <v>49.600099200198386</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="5">
+        <v>50</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C28" s="10">
+        <v>4.743009486018971E-3</v>
+      </c>
+      <c r="D28">
+        <f t="shared" si="0"/>
+        <v>47.430094860189712</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="5">
+        <v>50</v>
+      </c>
+      <c r="B29" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C29" s="10">
+        <v>5.301010602021203E-3</v>
+      </c>
+      <c r="D29">
+        <f t="shared" si="0"/>
+        <v>53.010106020212028</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="5">
+        <v>50</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="10">
+        <v>4.6190092380184742E-3</v>
+      </c>
+      <c r="D30">
+        <f t="shared" si="0"/>
+        <v>46.190092380184744</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="5">
+        <v>50</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C31" s="10">
+        <v>5.2080104160208314E-3</v>
+      </c>
+      <c r="D31">
+        <f t="shared" si="0"/>
+        <v>52.080104160208315</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="5">
+        <v>60</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C32" s="10">
+        <v>5.2080104160208314E-3</v>
+      </c>
+      <c r="D32">
+        <f t="shared" si="0"/>
+        <v>52.080104160208315</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="5">
+        <v>60</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C33" s="10">
+        <v>4.8980097960195906E-3</v>
+      </c>
+      <c r="D33">
+        <f t="shared" si="0"/>
+        <v>48.980097960195906</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="5">
+        <v>60</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="10">
+        <v>5.4250108500216989E-3</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="0"/>
+        <v>54.250108500216989</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="5">
+        <v>60</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" s="10">
+        <v>4.8360096720193426E-3</v>
+      </c>
+      <c r="D35">
+        <f t="shared" si="0"/>
+        <v>48.360096720193425</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="5">
+        <v>60</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="10">
+        <v>5.5180110360220714E-3</v>
+      </c>
+      <c r="D36">
+        <f t="shared" si="0"/>
+        <v>55.180110360220716</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="4">
+        <v>0</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C37" s="10">
+        <v>0</v>
+      </c>
+      <c r="D37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="4">
+        <v>0</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38" s="10">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="4">
+        <v>0</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C39" s="10">
+        <v>0</v>
+      </c>
+      <c r="D39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="4">
+        <v>0</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C40" s="10">
+        <v>0</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="4">
+        <v>0</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C41" s="10">
+        <v>0</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="5">
+        <v>10</v>
+      </c>
+      <c r="B42" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C42" s="10">
+        <v>4.2780085560171106E-3</v>
+      </c>
+      <c r="D42">
+        <f t="shared" si="0"/>
+        <v>42.780085560171109</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="5">
+        <v>10</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C43" s="10">
+        <v>6.2310124620249237E-3</v>
+      </c>
+      <c r="D43">
+        <f t="shared" si="0"/>
+        <v>62.31012462024924</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="5">
+        <v>10</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C44" s="10">
+        <v>8.680017360034719E-3</v>
+      </c>
+      <c r="D44">
+        <f t="shared" si="0"/>
+        <v>86.800173600347193</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="5">
+        <v>10</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C45" s="10">
+        <v>3.937007874015748E-3</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="0"/>
+        <v>39.370078740157481</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="5">
+        <v>10</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="10">
+        <v>5.3630107260214509E-3</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="0"/>
+        <v>53.630107260214508</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="5">
+        <v>20</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C47" s="10">
+        <v>5.5180110360220714E-3</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="0"/>
+        <v>55.180110360220716</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="5">
+        <v>20</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C48" s="10">
+        <v>8.0600161200322373E-3</v>
+      </c>
+      <c r="D48">
+        <f t="shared" si="0"/>
+        <v>80.600161200322376</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="5">
+        <v>20</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C49" s="10">
+        <v>9.3310186620373225E-3</v>
+      </c>
+      <c r="D49">
+        <f t="shared" si="0"/>
+        <v>93.31018662037323</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="5">
+        <v>20</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C50" s="10">
+        <v>4.4640089280178546E-3</v>
+      </c>
+      <c r="D50">
+        <f t="shared" si="0"/>
+        <v>44.640089280178543</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="5">
+        <v>20</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C51" s="10">
+        <v>6.2620125240250481E-3</v>
+      </c>
+      <c r="D51">
+        <f t="shared" si="0"/>
+        <v>62.620125240250481</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="5">
+        <v>30</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C52" s="10">
+        <v>5.4870109740219469E-3</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="0"/>
+        <v>54.870109740219469</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="5">
+        <v>30</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C53" s="10">
+        <v>8.432016864033727E-3</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="0"/>
+        <v>84.320168640337272</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="5">
+        <v>30</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C54" s="10">
+        <v>9.3620187240374478E-3</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="0"/>
+        <v>93.620187240374477</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="5">
+        <v>30</v>
+      </c>
+      <c r="B55" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C55" s="10">
+        <v>4.5260090520181026E-3</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="0"/>
+        <v>45.260090520181024</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="5">
+        <v>30</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C56" s="10">
+        <v>7.0990141980283965E-3</v>
+      </c>
+      <c r="D56">
+        <f t="shared" si="0"/>
+        <v>70.990141980283965</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="5">
+        <v>40</v>
+      </c>
+      <c r="B57" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C57" s="10">
+        <v>5.9830119660239317E-3</v>
+      </c>
+      <c r="D57">
+        <f t="shared" si="0"/>
+        <v>59.830119660239319</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="5">
+        <v>40</v>
+      </c>
+      <c r="B58" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C58" s="10">
+        <v>8.8970177940355874E-3</v>
+      </c>
+      <c r="D58">
+        <f t="shared" si="0"/>
+        <v>88.970177940355867</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="5">
+        <v>40</v>
+      </c>
+      <c r="B59" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C59" s="10">
+        <v>9.7340194680389357E-3</v>
+      </c>
+      <c r="D59">
+        <f t="shared" si="0"/>
+        <v>97.340194680389359</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="5">
+        <v>40</v>
+      </c>
+      <c r="B60" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C60" s="10">
+        <v>5.3320106640213274E-3</v>
+      </c>
+      <c r="D60">
+        <f t="shared" si="0"/>
+        <v>53.320106640213275</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="5">
+        <v>40</v>
+      </c>
+      <c r="B61" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C61" s="10">
+        <v>7.5020150040300054E-3</v>
+      </c>
+      <c r="D61">
+        <f t="shared" si="0"/>
+        <v>75.020150040300052</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="5">
+        <v>50</v>
+      </c>
+      <c r="B62" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C62" s="10">
+        <v>6.5410130820261645E-3</v>
+      </c>
+      <c r="D62">
+        <f t="shared" si="0"/>
+        <v>65.410130820261642</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="5">
+        <v>50</v>
+      </c>
+      <c r="B63" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C63" s="10">
+        <v>9.0210180420360834E-3</v>
+      </c>
+      <c r="D63">
+        <f t="shared" si="0"/>
+        <v>90.210180420360828</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="5">
+        <v>50</v>
+      </c>
+      <c r="B64" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C64" s="10">
+        <v>9.6100192200384398E-3</v>
+      </c>
+      <c r="D64">
+        <f t="shared" si="0"/>
+        <v>96.100192200384399</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="5">
+        <v>50</v>
+      </c>
+      <c r="B65" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C65" s="10">
+        <v>5.7040114080228153E-3</v>
+      </c>
+      <c r="D65">
+        <f t="shared" si="0"/>
+        <v>57.04011408022815</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="5">
+        <v>50</v>
+      </c>
+      <c r="B66" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C66" s="10">
+        <v>7.9360158720317413E-3</v>
+      </c>
+      <c r="D66">
+        <f t="shared" si="0"/>
+        <v>79.360158720317415</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="5">
+        <v>60</v>
+      </c>
+      <c r="B67" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C67" s="10">
+        <v>7.0680141360282694E-3</v>
+      </c>
+      <c r="D67">
+        <f t="shared" ref="D67:D130" si="1">C67 * 10000</f>
+        <v>70.68014136028269</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="5">
+        <v>60</v>
+      </c>
+      <c r="B68" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C68" s="10">
+        <v>9.0520181040362069E-3</v>
+      </c>
+      <c r="D68">
+        <f t="shared" si="1"/>
+        <v>90.520181040362075</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="5">
+        <v>60</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C69" s="10">
+        <v>9.9200198400396788E-3</v>
+      </c>
+      <c r="D69">
+        <f t="shared" si="1"/>
+        <v>99.200198400396786</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="5">
+        <v>60</v>
+      </c>
+      <c r="B70" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C70" s="10">
+        <v>6.0450120900241797E-3</v>
+      </c>
+      <c r="D70">
+        <f t="shared" si="1"/>
+        <v>60.450120900241799</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="5">
+        <v>60</v>
+      </c>
+      <c r="B71" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C71" s="10">
+        <v>8.4940169880339741E-3</v>
+      </c>
+      <c r="D71">
+        <f t="shared" si="1"/>
+        <v>84.940169880339738</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="4">
+        <v>0</v>
+      </c>
+      <c r="B72" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C72" s="11">
+        <v>0</v>
+      </c>
+      <c r="D72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="4">
+        <v>0</v>
+      </c>
+      <c r="B73" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C73" s="11">
+        <v>0</v>
+      </c>
+      <c r="D73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="4">
+        <v>0</v>
+      </c>
+      <c r="B74" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C74" s="11">
+        <v>0</v>
+      </c>
+      <c r="D74">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="4">
+        <v>0</v>
+      </c>
+      <c r="B75" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C75" s="11">
+        <v>0</v>
+      </c>
+      <c r="D75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="4">
+        <v>0</v>
+      </c>
+      <c r="B76" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C76" s="11">
+        <v>0</v>
+      </c>
+      <c r="D76">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="5">
+        <v>10</v>
+      </c>
+      <c r="B77" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C77" s="11">
+        <v>3.5960071920143836E-3</v>
+      </c>
+      <c r="D77">
+        <f t="shared" si="1"/>
+        <v>35.960071920143832</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="5">
+        <v>10</v>
+      </c>
+      <c r="B78" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C78" s="11">
+        <v>3.6580073160146316E-3</v>
+      </c>
+      <c r="D78">
+        <f t="shared" si="1"/>
+        <v>36.580073160146313</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="5">
+        <v>10</v>
+      </c>
+      <c r="B79" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C79" s="11">
+        <v>3.9060078120156235E-3</v>
+      </c>
+      <c r="D79">
+        <f t="shared" si="1"/>
+        <v>39.060078120156234</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="5">
+        <v>10</v>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C80" s="11">
+        <v>3.7820075640151276E-3</v>
+      </c>
+      <c r="D80">
+        <f t="shared" si="1"/>
+        <v>37.820075640151273</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="5">
+        <v>10</v>
+      </c>
+      <c r="B81" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C81" s="11">
+        <v>3.5650071300142596E-3</v>
+      </c>
+      <c r="D81">
+        <f t="shared" si="1"/>
+        <v>35.650071300142599</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="5">
+        <v>20</v>
+      </c>
+      <c r="B82" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C82" s="11">
+        <v>3.8130076260152516E-3</v>
+      </c>
+      <c r="D82">
+        <f t="shared" si="1"/>
+        <v>38.130076260152514</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="5">
+        <v>20</v>
+      </c>
+      <c r="B83" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C83" s="11">
+        <v>3.8130076260152516E-3</v>
+      </c>
+      <c r="D83">
+        <f t="shared" si="1"/>
+        <v>38.130076260152514</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="5">
+        <v>20</v>
+      </c>
+      <c r="B84" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C84" s="11">
+        <v>3.999007998015996E-3</v>
+      </c>
+      <c r="D84">
+        <f t="shared" si="1"/>
+        <v>39.990079980159962</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="5">
+        <v>20</v>
+      </c>
+      <c r="B85" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C85" s="11">
+        <v>4.1540083080166155E-3</v>
+      </c>
+      <c r="D85">
+        <f t="shared" si="1"/>
+        <v>41.540083080166156</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="5">
+        <v>20</v>
+      </c>
+      <c r="B86" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C86" s="11">
+        <v>3.9060078120156235E-3</v>
+      </c>
+      <c r="D86">
+        <f t="shared" si="1"/>
+        <v>39.060078120156234</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="5">
+        <v>30</v>
+      </c>
+      <c r="B87" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C87" s="11">
+        <v>4.061008122016244E-3</v>
+      </c>
+      <c r="D87">
+        <f t="shared" si="1"/>
+        <v>40.610081220162442</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" s="5">
+        <v>30</v>
+      </c>
+      <c r="B88" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C88" s="11">
+        <v>4.061008122016244E-3</v>
+      </c>
+      <c r="D88">
+        <f t="shared" si="1"/>
+        <v>40.610081220162442</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="5">
+        <v>30</v>
+      </c>
+      <c r="B89" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C89" s="11">
+        <v>4.2470084940169879E-3</v>
+      </c>
+      <c r="D89">
+        <f t="shared" si="1"/>
+        <v>42.470084940169876</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" s="5">
+        <v>30</v>
+      </c>
+      <c r="B90" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C90" s="11">
+        <v>4.3090086180172359E-3</v>
+      </c>
+      <c r="D90">
+        <f t="shared" si="1"/>
+        <v>43.090086180172356</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" s="5">
+        <v>30</v>
+      </c>
+      <c r="B91" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C91" s="11">
+        <v>4.0300080600161195E-3</v>
+      </c>
+      <c r="D91">
+        <f t="shared" si="1"/>
+        <v>40.300080600161195</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="5">
+        <v>40</v>
+      </c>
+      <c r="B92" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C92" s="11">
+        <v>4.2780085560171124E-3</v>
+      </c>
+      <c r="D92">
+        <f t="shared" si="1"/>
+        <v>42.780085560171123</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="5">
+        <v>40</v>
+      </c>
+      <c r="B93" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C93" s="11">
+        <v>4.1850083700167399E-3</v>
+      </c>
+      <c r="D93">
+        <f t="shared" si="1"/>
+        <v>41.850083700167403</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="5">
+        <v>40</v>
+      </c>
+      <c r="B94" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C94" s="11">
+        <v>4.681009362018723E-3</v>
+      </c>
+      <c r="D94">
+        <f t="shared" si="1"/>
+        <v>46.810093620187232</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="5">
+        <v>40</v>
+      </c>
+      <c r="B95" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C95" s="11">
+        <v>4.4950089900179782E-3</v>
+      </c>
+      <c r="D95">
+        <f t="shared" si="1"/>
+        <v>44.950089900179783</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="5">
+        <v>40</v>
+      </c>
+      <c r="B96" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C96" s="11">
+        <v>4.2160084320168644E-3</v>
+      </c>
+      <c r="D96">
+        <f t="shared" si="1"/>
+        <v>42.160084320168643</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97" s="5">
+        <v>50</v>
+      </c>
+      <c r="B97" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C97" s="11">
+        <v>4.4950089900179782E-3</v>
+      </c>
+      <c r="D97">
+        <f t="shared" si="1"/>
+        <v>44.950089900179783</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" s="5">
+        <v>50</v>
+      </c>
+      <c r="B98" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C98" s="11">
+        <v>4.4020088040176084E-3</v>
+      </c>
+      <c r="D98">
+        <f t="shared" si="1"/>
+        <v>44.020088040176084</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" s="5">
+        <v>50</v>
+      </c>
+      <c r="B99" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C99" s="11">
+        <v>4.4640089280178563E-3</v>
+      </c>
+      <c r="D99">
+        <f t="shared" si="1"/>
+        <v>44.640089280178564</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" s="5">
+        <v>50</v>
+      </c>
+      <c r="B100" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C100" s="11">
+        <v>4.4330088660177302E-3</v>
+      </c>
+      <c r="D100">
+        <f t="shared" si="1"/>
+        <v>44.330088660177303</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101" s="5">
+        <v>50</v>
+      </c>
+      <c r="B101" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C101" s="11">
+        <v>4.1850083700167399E-3</v>
+      </c>
+      <c r="D101">
+        <f t="shared" si="1"/>
+        <v>41.850083700167403</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" s="5">
+        <v>60</v>
+      </c>
+      <c r="B102" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C102" s="11">
+        <v>4.2780085560171124E-3</v>
+      </c>
+      <c r="D102">
+        <f t="shared" si="1"/>
+        <v>42.780085560171123</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" s="5">
+        <v>60</v>
+      </c>
+      <c r="B103" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C103" s="11">
+        <v>4.5570091140182262E-3</v>
+      </c>
+      <c r="D103">
+        <f t="shared" si="1"/>
+        <v>45.570091140182264</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104" s="5">
+        <v>60</v>
+      </c>
+      <c r="B104" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C104" s="11">
+        <v>4.681009362018723E-3</v>
+      </c>
+      <c r="D104">
+        <f t="shared" si="1"/>
+        <v>46.810093620187232</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" s="5">
+        <v>60</v>
+      </c>
+      <c r="B105" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C105" s="11">
+        <v>4.681009362018723E-3</v>
+      </c>
+      <c r="D105">
+        <f t="shared" si="1"/>
+        <v>46.810093620187232</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106" s="5">
+        <v>60</v>
+      </c>
+      <c r="B106" s="26" t="s">
+        <v>42</v>
+      </c>
+      <c r="C106" s="11">
+        <v>4.3710087420174822E-3</v>
+      </c>
+      <c r="D106">
+        <f t="shared" si="1"/>
+        <v>43.710087420174823</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107" s="4">
+        <v>0</v>
+      </c>
+      <c r="B107" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C107" s="11">
+        <v>0</v>
+      </c>
+      <c r="D107">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108" s="4">
+        <v>0</v>
+      </c>
+      <c r="B108" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C108" s="11">
+        <v>0</v>
+      </c>
+      <c r="D108">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109" s="4">
+        <v>0</v>
+      </c>
+      <c r="B109" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C109" s="11">
+        <v>0</v>
+      </c>
+      <c r="D109">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110" s="4">
+        <v>0</v>
+      </c>
+      <c r="B110" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C110" s="11">
+        <v>0</v>
+      </c>
+      <c r="D110">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A111" s="4">
+        <v>0</v>
+      </c>
+      <c r="B111" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C111" s="11">
+        <v>0</v>
+      </c>
+      <c r="D111">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A112" s="5">
+        <v>10</v>
+      </c>
+      <c r="B112" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C112" s="11">
+        <v>4.0920081840163675E-3</v>
+      </c>
+      <c r="D112">
+        <f t="shared" si="1"/>
+        <v>40.920081840163675</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113" s="5">
+        <v>10</v>
+      </c>
+      <c r="B113" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C113" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D113">
+        <f t="shared" si="1"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114" s="5">
+        <v>10</v>
+      </c>
+      <c r="B114" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C114" s="11">
+        <v>3.8130076260152516E-3</v>
+      </c>
+      <c r="D114">
+        <f t="shared" si="1"/>
+        <v>38.130076260152514</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115" s="5">
+        <v>10</v>
+      </c>
+      <c r="B115" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C115" s="11">
+        <v>3.7510075020150036E-3</v>
+      </c>
+      <c r="D115">
+        <f t="shared" si="1"/>
+        <v>37.510075020150033</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116" s="5">
+        <v>10</v>
+      </c>
+      <c r="B116" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C116" s="11">
+        <v>3.6270072540145076E-3</v>
+      </c>
+      <c r="D116">
+        <f t="shared" si="1"/>
+        <v>36.270072540145073</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A117" s="5">
+        <v>20</v>
+      </c>
+      <c r="B117" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C117" s="11">
+        <v>4.2160084320168626E-3</v>
+      </c>
+      <c r="D117">
+        <f t="shared" si="1"/>
+        <v>42.160084320168629</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A118" s="5">
+        <v>20</v>
+      </c>
+      <c r="B118" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C118" s="11">
+        <v>3.937007874015748E-3</v>
+      </c>
+      <c r="D118">
+        <f t="shared" si="1"/>
+        <v>39.370078740157481</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119" s="5">
+        <v>20</v>
+      </c>
+      <c r="B119" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C119" s="11">
+        <v>4.2470084940169862E-3</v>
+      </c>
+      <c r="D119">
+        <f t="shared" si="1"/>
+        <v>42.470084940169862</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120" s="5">
+        <v>20</v>
+      </c>
+      <c r="B120" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C120" s="11">
+        <v>3.9990079980159942E-3</v>
+      </c>
+      <c r="D120">
+        <f t="shared" si="1"/>
+        <v>39.99007998015994</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121" s="5">
+        <v>20</v>
+      </c>
+      <c r="B121" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C121" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D121">
+        <f t="shared" si="1"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A122" s="5">
+        <v>30</v>
+      </c>
+      <c r="B122" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C122" s="11">
+        <v>4.4640089280178546E-3</v>
+      </c>
+      <c r="D122">
+        <f t="shared" si="1"/>
+        <v>44.640089280178543</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A123" s="5">
+        <v>30</v>
+      </c>
+      <c r="B123" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C123" s="11">
+        <v>3.999007998015996E-3</v>
+      </c>
+      <c r="D123">
+        <f t="shared" si="1"/>
+        <v>39.990079980159962</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124" s="5">
+        <v>30</v>
+      </c>
+      <c r="B124" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C124" s="11">
+        <v>4.3710087420174822E-3</v>
+      </c>
+      <c r="D124">
+        <f t="shared" si="1"/>
+        <v>43.710087420174823</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" s="5">
+        <v>30</v>
+      </c>
+      <c r="B125" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C125" s="11">
+        <v>4.0920081840163658E-3</v>
+      </c>
+      <c r="D125">
+        <f t="shared" si="1"/>
+        <v>40.920081840163661</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126" s="5">
+        <v>30</v>
+      </c>
+      <c r="B126" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C126" s="11">
+        <v>3.8440076880153756E-3</v>
+      </c>
+      <c r="D126">
+        <f t="shared" si="1"/>
+        <v>38.440076880153754</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127" s="5">
+        <v>40</v>
+      </c>
+      <c r="B127" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C127" s="11">
+        <v>4.6190092380184742E-3</v>
+      </c>
+      <c r="D127">
+        <f t="shared" si="1"/>
+        <v>46.190092380184744</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128" s="5">
+        <v>40</v>
+      </c>
+      <c r="B128" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C128" s="11">
+        <v>4.0300080600161195E-3</v>
+      </c>
+      <c r="D128">
+        <f t="shared" si="1"/>
+        <v>40.300080600161195</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A129" s="5">
+        <v>40</v>
+      </c>
+      <c r="B129" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C129" s="11">
+        <v>4.4950089900179782E-3</v>
+      </c>
+      <c r="D129">
+        <f t="shared" si="1"/>
+        <v>44.950089900179783</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130" s="5">
+        <v>40</v>
+      </c>
+      <c r="B130" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C130" s="11">
+        <v>4.2470084940169862E-3</v>
+      </c>
+      <c r="D130">
+        <f t="shared" si="1"/>
+        <v>42.470084940169862</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A131" s="5">
+        <v>40</v>
+      </c>
+      <c r="B131" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C131" s="11">
+        <v>3.9060078120156235E-3</v>
+      </c>
+      <c r="D131">
+        <f t="shared" ref="D131:D194" si="2">C131 * 10000</f>
+        <v>39.060078120156234</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A132" s="5">
+        <v>50</v>
+      </c>
+      <c r="B132" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C132" s="11">
+        <v>4.8980097960195906E-3</v>
+      </c>
+      <c r="D132">
+        <f t="shared" si="2"/>
+        <v>48.980097960195906</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A133" s="5">
+        <v>50</v>
+      </c>
+      <c r="B133" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C133" s="11">
+        <v>4.4020088040176066E-3</v>
+      </c>
+      <c r="D133">
+        <f t="shared" si="2"/>
+        <v>44.020088040176063</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A134" s="5">
+        <v>50</v>
+      </c>
+      <c r="B134" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C134" s="11">
+        <v>4.681009362018723E-3</v>
+      </c>
+      <c r="D134">
+        <f t="shared" si="2"/>
+        <v>46.810093620187232</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135" s="5">
+        <v>50</v>
+      </c>
+      <c r="B135" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C135" s="11">
+        <v>4.3090086180172342E-3</v>
+      </c>
+      <c r="D135">
+        <f t="shared" si="2"/>
+        <v>43.090086180172342</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A136" s="5">
+        <v>50</v>
+      </c>
+      <c r="B136" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C136" s="11">
+        <v>4.061008122016244E-3</v>
+      </c>
+      <c r="D136">
+        <f t="shared" si="2"/>
+        <v>40.610081220162442</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137" s="5">
+        <v>60</v>
+      </c>
+      <c r="B137" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C137" s="11">
+        <v>4.8360096720193426E-3</v>
+      </c>
+      <c r="D137">
+        <f t="shared" si="2"/>
+        <v>48.360096720193425</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" s="5">
+        <v>60</v>
+      </c>
+      <c r="B138" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C138" s="11">
+        <v>4.5880091760183506E-3</v>
+      </c>
+      <c r="D138">
+        <f t="shared" si="2"/>
+        <v>45.880091760183504</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A139" s="5">
+        <v>60</v>
+      </c>
+      <c r="B139" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C139" s="11">
+        <v>4.743009486018971E-3</v>
+      </c>
+      <c r="D139">
+        <f t="shared" si="2"/>
+        <v>47.430094860189712</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140" s="5">
+        <v>60</v>
+      </c>
+      <c r="B140" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C140" s="11">
+        <v>4.3710087420174822E-3</v>
+      </c>
+      <c r="D140">
+        <f t="shared" si="2"/>
+        <v>43.710087420174823</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141" s="5">
+        <v>60</v>
+      </c>
+      <c r="B141" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="C141" s="11">
+        <v>4.0300080600161195E-3</v>
+      </c>
+      <c r="D141">
+        <f t="shared" si="2"/>
+        <v>40.300080600161195</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" s="4">
+        <v>0</v>
+      </c>
+      <c r="B142" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C142" s="11">
+        <v>0</v>
+      </c>
+      <c r="D142">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143" s="4">
+        <v>0</v>
+      </c>
+      <c r="B143" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C143" s="11">
+        <v>0</v>
+      </c>
+      <c r="D143">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" s="4">
+        <v>0</v>
+      </c>
+      <c r="B144" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C144" s="11">
+        <v>0</v>
+      </c>
+      <c r="D144">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145" s="4">
+        <v>0</v>
+      </c>
+      <c r="B145" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C145" s="11">
+        <v>0</v>
+      </c>
+      <c r="D145">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146" s="4">
+        <v>0</v>
+      </c>
+      <c r="B146" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C146" s="11">
+        <v>0</v>
+      </c>
+      <c r="D146">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A147" s="5">
+        <v>10</v>
+      </c>
+      <c r="B147" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C147" s="11">
+        <v>3.2240064480128952E-3</v>
+      </c>
+      <c r="D147">
+        <f t="shared" si="2"/>
+        <v>32.24006448012895</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A148" s="5">
+        <v>10</v>
+      </c>
+      <c r="B148" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C148" s="11">
+        <v>3.4720069440138876E-3</v>
+      </c>
+      <c r="D148">
+        <f t="shared" si="2"/>
+        <v>34.720069440138879</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A149" s="5">
+        <v>10</v>
+      </c>
+      <c r="B149" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C149" s="11">
+        <v>3.4410068820137632E-3</v>
+      </c>
+      <c r="D149">
+        <f t="shared" si="2"/>
+        <v>34.410068820137631</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A150" s="5">
+        <v>10</v>
+      </c>
+      <c r="B150" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C150" s="11">
+        <v>3.2860065720131432E-3</v>
+      </c>
+      <c r="D150">
+        <f t="shared" si="2"/>
+        <v>32.860065720131431</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A151" s="5">
+        <v>10</v>
+      </c>
+      <c r="B151" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C151" s="11">
+        <v>3.4100068200136392E-3</v>
+      </c>
+      <c r="D151">
+        <f t="shared" si="2"/>
+        <v>34.100068200136391</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A152" s="5">
+        <v>20</v>
+      </c>
+      <c r="B152" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C152" s="11">
+        <v>3.5960071920143836E-3</v>
+      </c>
+      <c r="D152">
+        <f t="shared" si="2"/>
+        <v>35.960071920143832</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A153" s="5">
+        <v>20</v>
+      </c>
+      <c r="B153" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C153" s="11">
+        <v>3.5650071300142596E-3</v>
+      </c>
+      <c r="D153">
+        <f t="shared" si="2"/>
+        <v>35.650071300142599</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A154" s="5">
+        <v>20</v>
+      </c>
+      <c r="B154" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C154" s="11">
+        <v>3.5650071300142596E-3</v>
+      </c>
+      <c r="D154">
+        <f t="shared" si="2"/>
+        <v>35.650071300142599</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A155" s="5">
+        <v>20</v>
+      </c>
+      <c r="B155" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C155" s="11">
+        <v>3.4410068820137632E-3</v>
+      </c>
+      <c r="D155">
+        <f t="shared" si="2"/>
+        <v>34.410068820137631</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A156" s="5">
+        <v>20</v>
+      </c>
+      <c r="B156" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C156" s="11">
+        <v>3.7820075640151276E-3</v>
+      </c>
+      <c r="D156">
+        <f t="shared" si="2"/>
+        <v>37.820075640151273</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A157" s="5">
+        <v>30</v>
+      </c>
+      <c r="B157" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C157" s="11">
+        <v>3.5960071920143836E-3</v>
+      </c>
+      <c r="D157">
+        <f t="shared" si="2"/>
+        <v>35.960071920143832</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A158" s="5">
+        <v>30</v>
+      </c>
+      <c r="B158" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C158" s="11">
+        <v>3.6580073160146316E-3</v>
+      </c>
+      <c r="D158">
+        <f t="shared" si="2"/>
+        <v>36.580073160146313</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A159" s="5">
+        <v>30</v>
+      </c>
+      <c r="B159" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C159" s="11">
+        <v>3.8750077500154996E-3</v>
+      </c>
+      <c r="D159">
+        <f t="shared" si="2"/>
+        <v>38.750077500154994</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A160" s="5">
+        <v>30</v>
+      </c>
+      <c r="B160" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C160" s="11">
+        <v>3.7200074400148796E-3</v>
+      </c>
+      <c r="D160">
+        <f t="shared" si="2"/>
+        <v>37.200074400148793</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A161" s="5">
+        <v>30</v>
+      </c>
+      <c r="B161" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C161" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D161">
+        <f t="shared" si="2"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A162" s="5">
+        <v>40</v>
+      </c>
+      <c r="B162" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C162" s="11">
+        <v>3.8130076260152516E-3</v>
+      </c>
+      <c r="D162">
+        <f t="shared" si="2"/>
+        <v>38.130076260152514</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A163" s="5">
+        <v>40</v>
+      </c>
+      <c r="B163" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C163" s="11">
+        <v>3.9680079360158715E-3</v>
+      </c>
+      <c r="D163">
+        <f t="shared" si="2"/>
+        <v>39.680079360158715</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A164" s="5">
+        <v>40</v>
+      </c>
+      <c r="B164" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C164" s="11">
+        <v>3.999007998015996E-3</v>
+      </c>
+      <c r="D164">
+        <f t="shared" si="2"/>
+        <v>39.990079980159962</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A165" s="5">
+        <v>40</v>
+      </c>
+      <c r="B165" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C165" s="11">
+        <v>3.8440076880153756E-3</v>
+      </c>
+      <c r="D165">
+        <f t="shared" si="2"/>
+        <v>38.440076880153754</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A166" s="5">
+        <v>40</v>
+      </c>
+      <c r="B166" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C166" s="11">
+        <v>3.937007874015748E-3</v>
+      </c>
+      <c r="D166">
+        <f t="shared" si="2"/>
+        <v>39.370078740157481</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A167" s="5">
+        <v>50</v>
+      </c>
+      <c r="B167" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C167" s="11">
+        <v>3.8750077500154996E-3</v>
+      </c>
+      <c r="D167">
+        <f t="shared" si="2"/>
+        <v>38.750077500154994</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A168" s="5">
+        <v>50</v>
+      </c>
+      <c r="B168" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C168" s="11">
+        <v>4.0920081840163675E-3</v>
+      </c>
+      <c r="D168">
+        <f t="shared" si="2"/>
+        <v>40.920081840163675</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A169" s="5">
+        <v>50</v>
+      </c>
+      <c r="B169" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C169" s="11">
+        <v>3.937007874015748E-3</v>
+      </c>
+      <c r="D169">
+        <f t="shared" si="2"/>
+        <v>39.370078740157481</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A170" s="5">
+        <v>50</v>
+      </c>
+      <c r="B170" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C170" s="11">
+        <v>3.937007874015748E-3</v>
+      </c>
+      <c r="D170">
+        <f t="shared" si="2"/>
+        <v>39.370078740157481</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A171" s="5">
+        <v>50</v>
+      </c>
+      <c r="B171" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C171" s="11">
+        <v>4.0300080600161195E-3</v>
+      </c>
+      <c r="D171">
+        <f t="shared" si="2"/>
+        <v>40.300080600161195</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A172" s="5">
+        <v>60</v>
+      </c>
+      <c r="B172" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C172" s="11">
+        <v>3.8130076260152516E-3</v>
+      </c>
+      <c r="D172">
+        <f t="shared" si="2"/>
+        <v>38.130076260152514</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A173" s="5">
+        <v>60</v>
+      </c>
+      <c r="B173" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C173" s="11">
+        <v>4.0920081840163675E-3</v>
+      </c>
+      <c r="D173">
+        <f t="shared" si="2"/>
+        <v>40.920081840163675</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A174" s="5">
+        <v>60</v>
+      </c>
+      <c r="B174" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C174" s="11">
+        <v>3.937007874015748E-3</v>
+      </c>
+      <c r="D174">
+        <f t="shared" si="2"/>
+        <v>39.370078740157481</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A175" s="5">
+        <v>60</v>
+      </c>
+      <c r="B175" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C175" s="11">
+        <v>3.9680079360158715E-3</v>
+      </c>
+      <c r="D175">
+        <f t="shared" si="2"/>
+        <v>39.680079360158715</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A176" s="5">
+        <v>60</v>
+      </c>
+      <c r="B176" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C176" s="11">
+        <v>3.937007874015748E-3</v>
+      </c>
+      <c r="D176">
+        <f t="shared" si="2"/>
+        <v>39.370078740157481</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A177" s="4">
+        <v>0</v>
+      </c>
+      <c r="B177" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C177" s="11">
+        <v>0</v>
+      </c>
+      <c r="D177">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A178" s="4">
+        <v>0</v>
+      </c>
+      <c r="B178" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C178" s="11">
+        <v>0</v>
+      </c>
+      <c r="D178">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A179" s="4">
+        <v>0</v>
+      </c>
+      <c r="B179" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C179" s="11">
+        <v>0</v>
+      </c>
+      <c r="D179">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A180" s="4">
+        <v>0</v>
+      </c>
+      <c r="B180" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C180" s="11">
+        <v>0</v>
+      </c>
+      <c r="D180">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A181" s="4">
+        <v>0</v>
+      </c>
+      <c r="B181" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C181" s="11">
+        <v>0</v>
+      </c>
+      <c r="D181">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A182" s="5">
+        <v>10</v>
+      </c>
+      <c r="B182" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C182" s="11">
+        <v>3.4720069440138876E-3</v>
+      </c>
+      <c r="D182">
+        <f t="shared" si="2"/>
+        <v>34.720069440138879</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A183" s="5">
+        <v>10</v>
+      </c>
+      <c r="B183" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C183" s="11">
+        <v>3.6580073160146316E-3</v>
+      </c>
+      <c r="D183">
+        <f t="shared" si="2"/>
+        <v>36.580073160146313</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A184" s="5">
+        <v>10</v>
+      </c>
+      <c r="B184" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C184" s="11">
+        <v>3.2240064480128952E-3</v>
+      </c>
+      <c r="D184">
+        <f t="shared" si="2"/>
+        <v>32.24006448012895</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A185" s="5">
+        <v>10</v>
+      </c>
+      <c r="B185" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C185" s="11">
+        <v>3.4720069440138876E-3</v>
+      </c>
+      <c r="D185">
+        <f t="shared" si="2"/>
+        <v>34.720069440138879</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A186" s="5">
+        <v>10</v>
+      </c>
+      <c r="B186" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C186" s="11">
+        <v>3.2860065720131432E-3</v>
+      </c>
+      <c r="D186">
+        <f t="shared" si="2"/>
+        <v>32.860065720131431</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A187" s="5">
+        <v>20</v>
+      </c>
+      <c r="B187" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C187" s="11">
+        <v>3.7820075640151276E-3</v>
+      </c>
+      <c r="D187">
+        <f t="shared" si="2"/>
+        <v>37.820075640151273</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A188" s="5">
+        <v>20</v>
+      </c>
+      <c r="B188" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C188" s="11">
+        <v>3.8750077500154996E-3</v>
+      </c>
+      <c r="D188">
+        <f t="shared" si="2"/>
+        <v>38.750077500154994</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A189" s="5">
+        <v>20</v>
+      </c>
+      <c r="B189" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C189" s="11">
+        <v>3.5030070060140116E-3</v>
+      </c>
+      <c r="D189">
+        <f t="shared" si="2"/>
+        <v>35.030070060140119</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A190" s="5">
+        <v>20</v>
+      </c>
+      <c r="B190" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C190" s="11">
+        <v>3.8130076260152516E-3</v>
+      </c>
+      <c r="D190">
+        <f t="shared" si="2"/>
+        <v>38.130076260152514</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A191" s="5">
+        <v>20</v>
+      </c>
+      <c r="B191" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C191" s="11">
+        <v>3.3480066960133912E-3</v>
+      </c>
+      <c r="D191">
+        <f t="shared" si="2"/>
+        <v>33.480066960133911</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A192" s="5">
+        <v>30</v>
+      </c>
+      <c r="B192" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C192" s="11">
+        <v>3.999007998015996E-3</v>
+      </c>
+      <c r="D192">
+        <f t="shared" si="2"/>
+        <v>39.990079980159962</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A193" s="5">
+        <v>30</v>
+      </c>
+      <c r="B193" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C193" s="11">
+        <v>3.8750077500154996E-3</v>
+      </c>
+      <c r="D193">
+        <f t="shared" si="2"/>
+        <v>38.750077500154994</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A194" s="5">
+        <v>30</v>
+      </c>
+      <c r="B194" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C194" s="11">
+        <v>3.3480066960133912E-3</v>
+      </c>
+      <c r="D194">
+        <f t="shared" si="2"/>
+        <v>33.480066960133911</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A195" s="5">
+        <v>30</v>
+      </c>
+      <c r="B195" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C195" s="11">
+        <v>3.8440076880153756E-3</v>
+      </c>
+      <c r="D195">
+        <f t="shared" ref="D195:D258" si="3">C195 * 10000</f>
+        <v>38.440076880153754</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A196" s="5">
+        <v>30</v>
+      </c>
+      <c r="B196" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C196" s="11">
+        <v>3.5650071300142596E-3</v>
+      </c>
+      <c r="D196">
+        <f t="shared" si="3"/>
+        <v>35.650071300142599</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A197" s="5">
+        <v>40</v>
+      </c>
+      <c r="B197" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C197" s="11">
+        <v>4.0920081840163675E-3</v>
+      </c>
+      <c r="D197">
+        <f t="shared" si="3"/>
+        <v>40.920081840163675</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A198" s="5">
+        <v>40</v>
+      </c>
+      <c r="B198" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C198" s="11">
+        <v>4.0610081220162422E-3</v>
+      </c>
+      <c r="D198">
+        <f t="shared" si="3"/>
+        <v>40.610081220162421</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A199" s="5">
+        <v>40</v>
+      </c>
+      <c r="B199" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C199" s="11">
+        <v>3.4720069440138876E-3</v>
+      </c>
+      <c r="D199">
+        <f t="shared" si="3"/>
+        <v>34.720069440138879</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A200" s="5">
+        <v>40</v>
+      </c>
+      <c r="B200" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C200" s="11">
+        <v>3.9680079360158715E-3</v>
+      </c>
+      <c r="D200">
+        <f t="shared" si="3"/>
+        <v>39.680079360158715</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A201" s="5">
+        <v>40</v>
+      </c>
+      <c r="B201" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C201" s="11">
+        <v>3.6580073160146316E-3</v>
+      </c>
+      <c r="D201">
+        <f t="shared" si="3"/>
+        <v>36.580073160146313</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A202" s="5">
+        <v>50</v>
+      </c>
+      <c r="B202" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C202" s="11">
+        <v>4.1540083080166155E-3</v>
+      </c>
+      <c r="D202">
+        <f t="shared" si="3"/>
+        <v>41.540083080166156</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A203" s="5">
+        <v>50</v>
+      </c>
+      <c r="B203" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C203" s="11">
+        <v>4.1850083700167382E-3</v>
+      </c>
+      <c r="D203">
+        <f t="shared" si="3"/>
+        <v>41.850083700167382</v>
+      </c>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A204" s="5">
+        <v>50</v>
+      </c>
+      <c r="B204" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C204" s="11">
+        <v>3.6270072540145076E-3</v>
+      </c>
+      <c r="D204">
+        <f t="shared" si="3"/>
+        <v>36.270072540145073</v>
+      </c>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A205" s="5">
+        <v>50</v>
+      </c>
+      <c r="B205" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C205" s="11">
+        <v>4.0920081840163675E-3</v>
+      </c>
+      <c r="D205">
+        <f t="shared" si="3"/>
+        <v>40.920081840163675</v>
+      </c>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A206" s="5">
+        <v>50</v>
+      </c>
+      <c r="B206" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C206" s="11">
+        <v>3.8130076260152516E-3</v>
+      </c>
+      <c r="D206">
+        <f t="shared" si="3"/>
+        <v>38.130076260152514</v>
+      </c>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A207" s="5">
+        <v>60</v>
+      </c>
+      <c r="B207" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C207" s="11">
+        <v>4.2160084320168644E-3</v>
+      </c>
+      <c r="D207">
+        <f t="shared" si="3"/>
+        <v>42.160084320168643</v>
+      </c>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A208" s="5">
+        <v>60</v>
+      </c>
+      <c r="B208" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C208" s="11">
+        <v>4.1850083700167382E-3</v>
+      </c>
+      <c r="D208">
+        <f t="shared" si="3"/>
+        <v>41.850083700167382</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A209" s="5">
+        <v>60</v>
+      </c>
+      <c r="B209" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C209" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D209">
+        <f t="shared" si="3"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A210" s="5">
+        <v>60</v>
+      </c>
+      <c r="B210" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C210" s="11">
+        <v>4.1540083080166155E-3</v>
+      </c>
+      <c r="D210">
+        <f t="shared" si="3"/>
+        <v>41.540083080166156</v>
+      </c>
+    </row>
+    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A211" s="5">
+        <v>60</v>
+      </c>
+      <c r="B211" s="26" t="s">
+        <v>44</v>
+      </c>
+      <c r="C211" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D211">
+        <f t="shared" si="3"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A212" s="4">
+        <v>0</v>
+      </c>
+      <c r="B212" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C212" s="11">
+        <v>0</v>
+      </c>
+      <c r="D212">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A213" s="4">
+        <v>0</v>
+      </c>
+      <c r="B213" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C213" s="11">
+        <v>0</v>
+      </c>
+      <c r="D213">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A214" s="4">
+        <v>0</v>
+      </c>
+      <c r="B214" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C214" s="11">
+        <v>0</v>
+      </c>
+      <c r="D214">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A215" s="4">
+        <v>0</v>
+      </c>
+      <c r="B215" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C215" s="11">
+        <v>0</v>
+      </c>
+      <c r="D215">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A216" s="4">
+        <v>0</v>
+      </c>
+      <c r="B216" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C216" s="11">
+        <v>0</v>
+      </c>
+      <c r="D216">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A217" s="5">
+        <v>10</v>
+      </c>
+      <c r="B217" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C217" s="11">
+        <v>3.2240064480128952E-3</v>
+      </c>
+      <c r="D217">
+        <f t="shared" si="3"/>
+        <v>32.24006448012895</v>
+      </c>
+    </row>
+    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A218" s="5">
+        <v>10</v>
+      </c>
+      <c r="B218" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C218" s="11">
+        <v>3.3790067580135152E-3</v>
+      </c>
+      <c r="D218">
+        <f t="shared" si="3"/>
+        <v>33.790067580135151</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A219" s="5">
+        <v>10</v>
+      </c>
+      <c r="B219" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C219" s="11">
+        <v>3.2550065100130192E-3</v>
+      </c>
+      <c r="D219">
+        <f t="shared" si="3"/>
+        <v>32.55006510013019</v>
+      </c>
+    </row>
+    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A220" s="5">
+        <v>10</v>
+      </c>
+      <c r="B220" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C220" s="11">
+        <v>3.5340070680141356E-3</v>
+      </c>
+      <c r="D220">
+        <f t="shared" si="3"/>
+        <v>35.340070680141359</v>
+      </c>
+    </row>
+    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A221" s="5">
+        <v>10</v>
+      </c>
+      <c r="B221" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C221" s="11">
+        <v>3.5340070680141356E-3</v>
+      </c>
+      <c r="D221">
+        <f t="shared" si="3"/>
+        <v>35.340070680141359</v>
+      </c>
+    </row>
+    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A222" s="5">
+        <v>20</v>
+      </c>
+      <c r="B222" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C222" s="11">
+        <v>3.4720069440138876E-3</v>
+      </c>
+      <c r="D222">
+        <f t="shared" si="3"/>
+        <v>34.720069440138879</v>
+      </c>
+    </row>
+    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A223" s="5">
+        <v>20</v>
+      </c>
+      <c r="B223" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C223" s="11">
+        <v>3.5650071300142596E-3</v>
+      </c>
+      <c r="D223">
+        <f t="shared" si="3"/>
+        <v>35.650071300142599</v>
+      </c>
+    </row>
+    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A224" s="5">
+        <v>20</v>
+      </c>
+      <c r="B224" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C224" s="11">
+        <v>3.5340070680141356E-3</v>
+      </c>
+      <c r="D224">
+        <f t="shared" si="3"/>
+        <v>35.340070680141359</v>
+      </c>
+    </row>
+    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A225" s="5">
+        <v>20</v>
+      </c>
+      <c r="B225" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C225" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D225">
+        <f t="shared" si="3"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A226" s="5">
+        <v>20</v>
+      </c>
+      <c r="B226" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C226" s="11">
+        <v>3.7510075020150036E-3</v>
+      </c>
+      <c r="D226">
+        <f t="shared" si="3"/>
+        <v>37.510075020150033</v>
+      </c>
+    </row>
+    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A227" s="5">
+        <v>30</v>
+      </c>
+      <c r="B227" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C227" s="11">
+        <v>3.7510075020150036E-3</v>
+      </c>
+      <c r="D227">
+        <f t="shared" si="3"/>
+        <v>37.510075020150033</v>
+      </c>
+    </row>
+    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A228" s="5">
+        <v>30</v>
+      </c>
+      <c r="B228" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C228" s="11">
+        <v>3.7200074400148796E-3</v>
+      </c>
+      <c r="D228">
+        <f t="shared" si="3"/>
+        <v>37.200074400148793</v>
+      </c>
+    </row>
+    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A229" s="5">
+        <v>30</v>
+      </c>
+      <c r="B229" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C229" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D229">
+        <f t="shared" si="3"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A230" s="5">
+        <v>30</v>
+      </c>
+      <c r="B230" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C230" s="11">
+        <v>3.8130076260152516E-3</v>
+      </c>
+      <c r="D230">
+        <f t="shared" si="3"/>
+        <v>38.130076260152514</v>
+      </c>
+    </row>
+    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A231" s="5">
+        <v>30</v>
+      </c>
+      <c r="B231" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C231" s="11">
+        <v>3.7820075640151276E-3</v>
+      </c>
+      <c r="D231">
+        <f t="shared" si="3"/>
+        <v>37.820075640151273</v>
+      </c>
+    </row>
+    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A232" s="5">
+        <v>40</v>
+      </c>
+      <c r="B232" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C232" s="11">
+        <v>3.7820075640151276E-3</v>
+      </c>
+      <c r="D232">
+        <f t="shared" si="3"/>
+        <v>37.820075640151273</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A233" s="5">
+        <v>40</v>
+      </c>
+      <c r="B233" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C233" s="11">
+        <v>3.7820075640151276E-3</v>
+      </c>
+      <c r="D233">
+        <f t="shared" si="3"/>
+        <v>37.820075640151273</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A234" s="5">
+        <v>40</v>
+      </c>
+      <c r="B234" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C234" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D234">
+        <f t="shared" si="3"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A235" s="5">
+        <v>40</v>
+      </c>
+      <c r="B235" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C235" s="11">
+        <v>3.9680079360158715E-3</v>
+      </c>
+      <c r="D235">
+        <f t="shared" si="3"/>
+        <v>39.680079360158715</v>
+      </c>
+    </row>
+    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A236" s="5">
+        <v>40</v>
+      </c>
+      <c r="B236" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C236" s="11">
+        <v>3.8130076260152516E-3</v>
+      </c>
+      <c r="D236">
+        <f t="shared" si="3"/>
+        <v>38.130076260152514</v>
+      </c>
+    </row>
+    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A237" s="5">
+        <v>50</v>
+      </c>
+      <c r="B237" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C237" s="11">
+        <v>3.9060078120156235E-3</v>
+      </c>
+      <c r="D237">
+        <f t="shared" si="3"/>
+        <v>39.060078120156234</v>
+      </c>
+    </row>
+    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A238" s="5">
+        <v>50</v>
+      </c>
+      <c r="B238" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C238" s="11">
+        <v>3.937007874015748E-3</v>
+      </c>
+      <c r="D238">
+        <f t="shared" si="3"/>
+        <v>39.370078740157481</v>
+      </c>
+    </row>
+    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A239" s="5">
+        <v>50</v>
+      </c>
+      <c r="B239" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C239" s="11">
+        <v>3.6270072540145076E-3</v>
+      </c>
+      <c r="D239">
+        <f t="shared" si="3"/>
+        <v>36.270072540145073</v>
+      </c>
+    </row>
+    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A240" s="5">
+        <v>50</v>
+      </c>
+      <c r="B240" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C240" s="11">
+        <v>3.9680079360158715E-3</v>
+      </c>
+      <c r="D240">
+        <f t="shared" si="3"/>
+        <v>39.680079360158715</v>
+      </c>
+    </row>
+    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A241" s="5">
+        <v>50</v>
+      </c>
+      <c r="B241" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C241" s="11">
+        <v>3.9060078120156235E-3</v>
+      </c>
+      <c r="D241">
+        <f t="shared" si="3"/>
+        <v>39.060078120156234</v>
+      </c>
+    </row>
+    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A242" s="5">
+        <v>60</v>
+      </c>
+      <c r="B242" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C242" s="11">
+        <v>3.9680079360158715E-3</v>
+      </c>
+      <c r="D242">
+        <f t="shared" si="3"/>
+        <v>39.680079360158715</v>
+      </c>
+    </row>
+    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A243" s="5">
+        <v>60</v>
+      </c>
+      <c r="B243" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C243" s="11">
+        <v>3.937007874015748E-3</v>
+      </c>
+      <c r="D243">
+        <f t="shared" si="3"/>
+        <v>39.370078740157481</v>
+      </c>
+    </row>
+    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A244" s="5">
+        <v>60</v>
+      </c>
+      <c r="B244" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C244" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D244">
+        <f t="shared" si="3"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A245" s="5">
+        <v>60</v>
+      </c>
+      <c r="B245" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C245" s="11">
+        <v>3.937007874015748E-3</v>
+      </c>
+      <c r="D245">
+        <f t="shared" si="3"/>
+        <v>39.370078740157481</v>
+      </c>
+    </row>
+    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A246" s="5">
+        <v>60</v>
+      </c>
+      <c r="B246" s="26" t="s">
+        <v>45</v>
+      </c>
+      <c r="C246" s="11">
+        <v>3.937007874015748E-3</v>
+      </c>
+      <c r="D246">
+        <f t="shared" si="3"/>
+        <v>39.370078740157481</v>
+      </c>
+    </row>
+    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A247" s="4">
+        <v>0</v>
+      </c>
+      <c r="B247" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C247" s="11">
+        <v>0</v>
+      </c>
+      <c r="D247">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A248" s="4">
+        <v>0</v>
+      </c>
+      <c r="B248" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C248" s="11">
+        <v>0</v>
+      </c>
+      <c r="D248">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A249" s="4">
+        <v>0</v>
+      </c>
+      <c r="B249" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C249" s="11">
+        <v>0</v>
+      </c>
+      <c r="D249">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A250" s="4">
+        <v>0</v>
+      </c>
+      <c r="B250" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C250" s="11">
+        <v>0</v>
+      </c>
+      <c r="D250">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A251" s="4">
+        <v>0</v>
+      </c>
+      <c r="B251" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C251" s="11">
+        <v>0</v>
+      </c>
+      <c r="D251">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A252" s="5">
+        <v>10</v>
+      </c>
+      <c r="B252" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C252" s="11">
+        <v>2.9140058280116565E-3</v>
+      </c>
+      <c r="D252">
+        <f t="shared" si="3"/>
+        <v>29.140058280116566</v>
+      </c>
+    </row>
+    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A253" s="5">
+        <v>10</v>
+      </c>
+      <c r="B253" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C253" s="11">
+        <v>2.6040052080104148E-3</v>
+      </c>
+      <c r="D253">
+        <f t="shared" si="3"/>
+        <v>26.040052080104147</v>
+      </c>
+    </row>
+    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A254" s="5">
+        <v>10</v>
+      </c>
+      <c r="B254" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C254" s="11">
+        <v>2.9140058280116548E-3</v>
+      </c>
+      <c r="D254">
+        <f t="shared" si="3"/>
+        <v>29.140058280116548</v>
+      </c>
+    </row>
+    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A255" s="5">
+        <v>10</v>
+      </c>
+      <c r="B255" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C255" s="11">
+        <v>3.1310062620125249E-3</v>
+      </c>
+      <c r="D255">
+        <f t="shared" si="3"/>
+        <v>31.310062620125251</v>
+      </c>
+    </row>
+    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A256" s="5">
+        <v>10</v>
+      </c>
+      <c r="B256" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C256" s="11">
+        <v>2.9760059520119028E-3</v>
+      </c>
+      <c r="D256">
+        <f t="shared" si="3"/>
+        <v>29.760059520119029</v>
+      </c>
+    </row>
+    <row r="257" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A257" s="5">
+        <v>20</v>
+      </c>
+      <c r="B257" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C257" s="11">
+        <v>3.5960071920143853E-3</v>
+      </c>
+      <c r="D257">
+        <f t="shared" si="3"/>
+        <v>35.960071920143854</v>
+      </c>
+    </row>
+    <row r="258" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A258" s="5">
+        <v>20</v>
+      </c>
+      <c r="B258" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C258" s="11">
+        <v>3.5650071300142596E-3</v>
+      </c>
+      <c r="D258">
+        <f t="shared" si="3"/>
+        <v>35.650071300142599</v>
+      </c>
+    </row>
+    <row r="259" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A259" s="5">
+        <v>20</v>
+      </c>
+      <c r="B259" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C259" s="11">
+        <v>3.6580073160146316E-3</v>
+      </c>
+      <c r="D259">
+        <f t="shared" ref="D259:D322" si="4">C259 * 10000</f>
+        <v>36.580073160146313</v>
+      </c>
+    </row>
+    <row r="260" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A260" s="5">
+        <v>20</v>
+      </c>
+      <c r="B260" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C260" s="11">
+        <v>3.7510075020150053E-3</v>
+      </c>
+      <c r="D260">
+        <f t="shared" si="4"/>
+        <v>37.510075020150055</v>
+      </c>
+    </row>
+    <row r="261" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A261" s="5">
+        <v>20</v>
+      </c>
+      <c r="B261" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C261" s="11">
+        <v>4.0920081840163675E-3</v>
+      </c>
+      <c r="D261">
+        <f t="shared" si="4"/>
+        <v>40.920081840163675</v>
+      </c>
+    </row>
+    <row r="262" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A262" s="5">
+        <v>30</v>
+      </c>
+      <c r="B262" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C262" s="11">
+        <v>3.7820075640151276E-3</v>
+      </c>
+      <c r="D262">
+        <f t="shared" si="4"/>
+        <v>37.820075640151273</v>
+      </c>
+    </row>
+    <row r="263" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A263" s="5">
+        <v>30</v>
+      </c>
+      <c r="B263" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C263" s="11">
+        <v>3.4100068200136392E-3</v>
+      </c>
+      <c r="D263">
+        <f t="shared" si="4"/>
+        <v>34.100068200136391</v>
+      </c>
+    </row>
+    <row r="264" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A264" s="5">
+        <v>30</v>
+      </c>
+      <c r="B264" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C264" s="11">
+        <v>3.7510075020150036E-3</v>
+      </c>
+      <c r="D264">
+        <f t="shared" si="4"/>
+        <v>37.510075020150033</v>
+      </c>
+    </row>
+    <row r="265" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A265" s="5">
+        <v>30</v>
+      </c>
+      <c r="B265" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C265" s="11">
+        <v>3.4720069440138889E-3</v>
+      </c>
+      <c r="D265">
+        <f t="shared" si="4"/>
+        <v>34.720069440138886</v>
+      </c>
+    </row>
+    <row r="266" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A266" s="5">
+        <v>30</v>
+      </c>
+      <c r="B266" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C266" s="11">
+        <v>4.2160084320168644E-3</v>
+      </c>
+      <c r="D266">
+        <f t="shared" si="4"/>
+        <v>42.160084320168643</v>
+      </c>
+    </row>
+    <row r="267" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A267" s="5">
+        <v>40</v>
+      </c>
+      <c r="B267" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C267" s="11">
+        <v>4.0300080600161195E-3</v>
+      </c>
+      <c r="D267">
+        <f t="shared" si="4"/>
+        <v>40.300080600161195</v>
+      </c>
+    </row>
+    <row r="268" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A268" s="5">
+        <v>40</v>
+      </c>
+      <c r="B268" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C268" s="11">
+        <v>3.4410068820137632E-3</v>
+      </c>
+      <c r="D268">
+        <f t="shared" si="4"/>
+        <v>34.410068820137631</v>
+      </c>
+    </row>
+    <row r="269" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A269" s="5">
+        <v>40</v>
+      </c>
+      <c r="B269" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C269" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D269">
+        <f t="shared" si="4"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="270" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A270" s="5">
+        <v>40</v>
+      </c>
+      <c r="B270" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C270" s="11">
+        <v>3.6580073160146333E-3</v>
+      </c>
+      <c r="D270">
+        <f t="shared" si="4"/>
+        <v>36.580073160146334</v>
+      </c>
+    </row>
+    <row r="271" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A271" s="5">
+        <v>40</v>
+      </c>
+      <c r="B271" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C271" s="11">
+        <v>4.4640089280178546E-3</v>
+      </c>
+      <c r="D271">
+        <f t="shared" si="4"/>
+        <v>44.640089280178543</v>
+      </c>
+    </row>
+    <row r="272" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A272" s="5">
+        <v>50</v>
+      </c>
+      <c r="B272" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C272" s="11">
+        <v>3.8750077500154996E-3</v>
+      </c>
+      <c r="D272">
+        <f t="shared" si="4"/>
+        <v>38.750077500154994</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A273" s="5">
+        <v>50</v>
+      </c>
+      <c r="B273" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C273" s="11">
+        <v>3.5030070060140116E-3</v>
+      </c>
+      <c r="D273">
+        <f t="shared" si="4"/>
+        <v>35.030070060140119</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A274" s="5">
+        <v>50</v>
+      </c>
+      <c r="B274" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C274" s="11">
+        <v>3.8440076880153756E-3</v>
+      </c>
+      <c r="D274">
+        <f t="shared" si="4"/>
+        <v>38.440076880153754</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A275" s="5">
+        <v>50</v>
+      </c>
+      <c r="B275" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C275" s="11">
+        <v>3.8440076880153773E-3</v>
+      </c>
+      <c r="D275">
+        <f t="shared" si="4"/>
+        <v>38.440076880153775</v>
+      </c>
+    </row>
+    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A276" s="5">
+        <v>50</v>
+      </c>
+      <c r="B276" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C276" s="11">
+        <v>4.7120094240188466E-3</v>
+      </c>
+      <c r="D276">
+        <f t="shared" si="4"/>
+        <v>47.120094240188465</v>
+      </c>
+    </row>
+    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A277" s="5">
+        <v>60</v>
+      </c>
+      <c r="B277" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C277" s="11">
+        <v>3.8130076260152516E-3</v>
+      </c>
+      <c r="D277">
+        <f t="shared" si="4"/>
+        <v>38.130076260152514</v>
+      </c>
+    </row>
+    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A278" s="5">
+        <v>60</v>
+      </c>
+      <c r="B278" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C278" s="11">
+        <v>3.5030070060140116E-3</v>
+      </c>
+      <c r="D278">
+        <f t="shared" si="4"/>
+        <v>35.030070060140119</v>
+      </c>
+    </row>
+    <row r="279" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A279" s="5">
+        <v>60</v>
+      </c>
+      <c r="B279" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C279" s="11">
+        <v>4.061008122016244E-3</v>
+      </c>
+      <c r="D279">
+        <f t="shared" si="4"/>
+        <v>40.610081220162442</v>
+      </c>
+    </row>
+    <row r="280" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A280" s="5">
+        <v>60</v>
+      </c>
+      <c r="B280" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C280" s="11">
+        <v>4.0920081840163675E-3</v>
+      </c>
+      <c r="D280">
+        <f t="shared" si="4"/>
+        <v>40.920081840163675</v>
+      </c>
+    </row>
+    <row r="281" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A281" s="5">
+        <v>60</v>
+      </c>
+      <c r="B281" s="26" t="s">
+        <v>46</v>
+      </c>
+      <c r="C281" s="11">
+        <v>4.7120094240188466E-3</v>
+      </c>
+      <c r="D281">
+        <f t="shared" si="4"/>
+        <v>47.120094240188465</v>
+      </c>
+    </row>
+    <row r="282" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A282" s="4">
+        <v>0</v>
+      </c>
+      <c r="B282" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C282" s="11">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A283" s="4">
+        <v>0</v>
+      </c>
+      <c r="B283" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C283" s="11">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A284" s="4">
+        <v>0</v>
+      </c>
+      <c r="B284" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C284" s="11">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A285" s="4">
+        <v>0</v>
+      </c>
+      <c r="B285" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C285" s="11">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A286" s="4">
+        <v>0</v>
+      </c>
+      <c r="B286" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C286" s="11">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A287" s="5">
+        <v>10</v>
+      </c>
+      <c r="B287" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C287" s="11">
+        <v>2.8830057660115308E-3</v>
+      </c>
+      <c r="D287">
+        <f t="shared" si="4"/>
+        <v>28.830057660115308</v>
+      </c>
+    </row>
+    <row r="288" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A288" s="5">
+        <v>10</v>
+      </c>
+      <c r="B288" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C288" s="11">
+        <v>2.6350052700105406E-3</v>
+      </c>
+      <c r="D288">
+        <f t="shared" si="4"/>
+        <v>26.350052700105405</v>
+      </c>
+    </row>
+    <row r="289" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A289" s="5">
+        <v>10</v>
+      </c>
+      <c r="B289" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C289" s="11">
+        <v>2.6660053320106628E-3</v>
+      </c>
+      <c r="D289">
+        <f t="shared" si="4"/>
+        <v>26.660053320106627</v>
+      </c>
+    </row>
+    <row r="290" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A290" s="5">
+        <v>10</v>
+      </c>
+      <c r="B290" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C290" s="11">
+        <v>2.8520057040114068E-3</v>
+      </c>
+      <c r="D290">
+        <f t="shared" si="4"/>
+        <v>28.520057040114068</v>
+      </c>
+    </row>
+    <row r="291" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A291" s="5">
+        <v>10</v>
+      </c>
+      <c r="B291" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C291" s="11">
+        <v>2.8210056420112828E-3</v>
+      </c>
+      <c r="D291">
+        <f t="shared" si="4"/>
+        <v>28.210056420112828</v>
+      </c>
+    </row>
+    <row r="292" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A292" s="5">
+        <v>20</v>
+      </c>
+      <c r="B292" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C292" s="11">
+        <v>3.0380060760121512E-3</v>
+      </c>
+      <c r="D292">
+        <f t="shared" si="4"/>
+        <v>30.380060760121513</v>
+      </c>
+    </row>
+    <row r="293" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A293" s="5">
+        <v>20</v>
+      </c>
+      <c r="B293" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C293" s="11">
+        <v>3.5650071300142613E-3</v>
+      </c>
+      <c r="D293">
+        <f t="shared" si="4"/>
+        <v>35.650071300142613</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A294" s="5">
+        <v>20</v>
+      </c>
+      <c r="B294" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C294" s="11">
+        <v>3.2550065100130192E-3</v>
+      </c>
+      <c r="D294">
+        <f t="shared" si="4"/>
+        <v>32.55006510013019</v>
+      </c>
+    </row>
+    <row r="295" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A295" s="5">
+        <v>20</v>
+      </c>
+      <c r="B295" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C295" s="11">
+        <v>3.1620063240126472E-3</v>
+      </c>
+      <c r="D295">
+        <f t="shared" si="4"/>
+        <v>31.620063240126473</v>
+      </c>
+    </row>
+    <row r="296" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A296" s="5">
+        <v>20</v>
+      </c>
+      <c r="B296" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C296" s="11">
+        <v>3.5030070060140116E-3</v>
+      </c>
+      <c r="D296">
+        <f t="shared" si="4"/>
+        <v>35.030070060140119</v>
+      </c>
+    </row>
+    <row r="297" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A297" s="5">
+        <v>30</v>
+      </c>
+      <c r="B297" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C297" s="11">
+        <v>3.3170066340132672E-3</v>
+      </c>
+      <c r="D297">
+        <f t="shared" si="4"/>
+        <v>33.170066340132671</v>
+      </c>
+    </row>
+    <row r="298" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A298" s="5">
+        <v>30</v>
+      </c>
+      <c r="B298" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C298" s="11">
+        <v>3.5960071920143853E-3</v>
+      </c>
+      <c r="D298">
+        <f t="shared" si="4"/>
+        <v>35.960071920143854</v>
+      </c>
+    </row>
+    <row r="299" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A299" s="5">
+        <v>30</v>
+      </c>
+      <c r="B299" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C299" s="11">
+        <v>3.5650071300142596E-3</v>
+      </c>
+      <c r="D299">
+        <f t="shared" si="4"/>
+        <v>35.650071300142599</v>
+      </c>
+    </row>
+    <row r="300" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A300" s="5">
+        <v>30</v>
+      </c>
+      <c r="B300" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C300" s="11">
+        <v>3.4410068820137632E-3</v>
+      </c>
+      <c r="D300">
+        <f t="shared" si="4"/>
+        <v>34.410068820137631</v>
+      </c>
+    </row>
+    <row r="301" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A301" s="5">
+        <v>30</v>
+      </c>
+      <c r="B301" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C301" s="11">
+        <v>3.8130076260152516E-3</v>
+      </c>
+      <c r="D301">
+        <f t="shared" si="4"/>
+        <v>38.130076260152514</v>
+      </c>
+    </row>
+    <row r="302" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A302" s="5">
+        <v>40</v>
+      </c>
+      <c r="B302" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C302" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D302">
+        <f t="shared" si="4"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A303" s="5">
+        <v>40</v>
+      </c>
+      <c r="B303" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C303" s="11">
+        <v>3.937007874015748E-3</v>
+      </c>
+      <c r="D303">
+        <f t="shared" si="4"/>
+        <v>39.370078740157481</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A304" s="5">
+        <v>40</v>
+      </c>
+      <c r="B304" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C304" s="11">
+        <v>3.7200074400148796E-3</v>
+      </c>
+      <c r="D304">
+        <f t="shared" si="4"/>
+        <v>37.200074400148793</v>
+      </c>
+    </row>
+    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A305" s="5">
+        <v>40</v>
+      </c>
+      <c r="B305" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C305" s="11">
+        <v>3.6580073160146316E-3</v>
+      </c>
+      <c r="D305">
+        <f t="shared" si="4"/>
+        <v>36.580073160146313</v>
+      </c>
+    </row>
+    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A306" s="5">
+        <v>40</v>
+      </c>
+      <c r="B306" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C306" s="11">
+        <v>3.6580073160146316E-3</v>
+      </c>
+      <c r="D306">
+        <f t="shared" si="4"/>
+        <v>36.580073160146313</v>
+      </c>
+    </row>
+    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A307" s="5">
+        <v>50</v>
+      </c>
+      <c r="B307" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C307" s="11">
+        <v>3.6580073160146316E-3</v>
+      </c>
+      <c r="D307">
+        <f t="shared" si="4"/>
+        <v>36.580073160146313</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A308" s="5">
+        <v>50</v>
+      </c>
+      <c r="B308" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C308" s="11">
+        <v>3.8750077500154996E-3</v>
+      </c>
+      <c r="D308">
+        <f t="shared" si="4"/>
+        <v>38.750077500154994</v>
+      </c>
+    </row>
+    <row r="309" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A309" s="5">
+        <v>50</v>
+      </c>
+      <c r="B309" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C309" s="11">
+        <v>3.5650071300142596E-3</v>
+      </c>
+      <c r="D309">
+        <f t="shared" si="4"/>
+        <v>35.650071300142599</v>
+      </c>
+    </row>
+    <row r="310" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A310" s="5">
+        <v>50</v>
+      </c>
+      <c r="B310" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C310" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D310">
+        <f t="shared" si="4"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="311" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A311" s="5">
+        <v>50</v>
+      </c>
+      <c r="B311" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C311" s="11">
+        <v>3.8440076880153756E-3</v>
+      </c>
+      <c r="D311">
+        <f t="shared" si="4"/>
+        <v>38.440076880153754</v>
+      </c>
+    </row>
+    <row r="312" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A312" s="5">
+        <v>60</v>
+      </c>
+      <c r="B312" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C312" s="11">
+        <v>3.6270072540145076E-3</v>
+      </c>
+      <c r="D312">
+        <f t="shared" si="4"/>
+        <v>36.270072540145073</v>
+      </c>
+    </row>
+    <row r="313" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A313" s="5">
+        <v>60</v>
+      </c>
+      <c r="B313" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C313" s="11">
+        <v>3.937007874015748E-3</v>
+      </c>
+      <c r="D313">
+        <f t="shared" si="4"/>
+        <v>39.370078740157481</v>
+      </c>
+    </row>
+    <row r="314" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A314" s="5">
+        <v>60</v>
+      </c>
+      <c r="B314" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C314" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D314">
+        <f t="shared" si="4"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A315" s="5">
+        <v>60</v>
+      </c>
+      <c r="B315" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C315" s="11">
+        <v>3.7820075640151276E-3</v>
+      </c>
+      <c r="D315">
+        <f t="shared" si="4"/>
+        <v>37.820075640151273</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A316" s="5">
+        <v>60</v>
+      </c>
+      <c r="B316" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C316" s="11">
+        <v>3.9060078120156218E-3</v>
+      </c>
+      <c r="D316">
+        <f t="shared" si="4"/>
+        <v>39.06007812015622</v>
+      </c>
+    </row>
+    <row r="317" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A317" s="4">
+        <v>0</v>
+      </c>
+      <c r="B317" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C317" s="11">
+        <v>0</v>
+      </c>
+      <c r="D317">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="318" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A318" s="4">
+        <v>0</v>
+      </c>
+      <c r="B318" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C318" s="11">
+        <v>0</v>
+      </c>
+      <c r="D318">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="319" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A319" s="4">
+        <v>0</v>
+      </c>
+      <c r="B319" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C319" s="11">
+        <v>0</v>
+      </c>
+      <c r="D319">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A320" s="4">
+        <v>0</v>
+      </c>
+      <c r="B320" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C320" s="11">
+        <v>0</v>
+      </c>
+      <c r="D320">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A321" s="4">
+        <v>0</v>
+      </c>
+      <c r="B321" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C321" s="11">
+        <v>0</v>
+      </c>
+      <c r="D321">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A322" s="5">
+        <v>10</v>
+      </c>
+      <c r="B322" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C322" s="11">
+        <v>2.5420050840101681E-3</v>
+      </c>
+      <c r="D322">
+        <f t="shared" si="4"/>
+        <v>25.42005084010168</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A323" s="5">
+        <v>10</v>
+      </c>
+      <c r="B323" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C323" s="11">
+        <v>2.7280054560109126E-3</v>
+      </c>
+      <c r="D323">
+        <f t="shared" ref="D323:D386" si="5">C323 * 10000</f>
+        <v>27.280054560109125</v>
+      </c>
+    </row>
+    <row r="324" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A324" s="5">
+        <v>10</v>
+      </c>
+      <c r="B324" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C324" s="11">
+        <v>2.6040052080104166E-3</v>
+      </c>
+      <c r="D324">
+        <f t="shared" si="5"/>
+        <v>26.040052080104164</v>
+      </c>
+    </row>
+    <row r="325" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A325" s="5">
+        <v>10</v>
+      </c>
+      <c r="B325" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C325" s="11">
+        <v>2.5420050840101681E-3</v>
+      </c>
+      <c r="D325">
+        <f t="shared" si="5"/>
+        <v>25.42005084010168</v>
+      </c>
+    </row>
+    <row r="326" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A326" s="5">
+        <v>10</v>
+      </c>
+      <c r="B326" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C326" s="11">
+        <v>2.6660053320106646E-3</v>
+      </c>
+      <c r="D326">
+        <f t="shared" si="5"/>
+        <v>26.660053320106645</v>
+      </c>
+    </row>
+    <row r="327" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A327" s="5">
+        <v>20</v>
+      </c>
+      <c r="B327" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C327" s="11">
+        <v>3.2550065100130209E-3</v>
+      </c>
+      <c r="D327">
+        <f t="shared" si="5"/>
+        <v>32.550065100130212</v>
+      </c>
+    </row>
+    <row r="328" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A328" s="5">
+        <v>20</v>
+      </c>
+      <c r="B328" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C328" s="11">
+        <v>3.1930063860127729E-3</v>
+      </c>
+      <c r="D328">
+        <f t="shared" si="5"/>
+        <v>31.930063860127728</v>
+      </c>
+    </row>
+    <row r="329" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A329" s="5">
+        <v>20</v>
+      </c>
+      <c r="B329" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C329" s="11">
+        <v>3.1310062620125249E-3</v>
+      </c>
+      <c r="D329">
+        <f t="shared" si="5"/>
+        <v>31.310062620125251</v>
+      </c>
+    </row>
+    <row r="330" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A330" s="5">
+        <v>20</v>
+      </c>
+      <c r="B330" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C330" s="11">
+        <v>2.7900055800111605E-3</v>
+      </c>
+      <c r="D330">
+        <f t="shared" si="5"/>
+        <v>27.900055800111605</v>
+      </c>
+    </row>
+    <row r="331" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A331" s="5">
+        <v>20</v>
+      </c>
+      <c r="B331" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C331" s="11">
+        <v>3.1620063240126472E-3</v>
+      </c>
+      <c r="D331">
+        <f t="shared" si="5"/>
+        <v>31.620063240126473</v>
+      </c>
+    </row>
+    <row r="332" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A332" s="5">
+        <v>30</v>
+      </c>
+      <c r="B332" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C332" s="11">
+        <v>3.5340070680141356E-3</v>
+      </c>
+      <c r="D332">
+        <f t="shared" si="5"/>
+        <v>35.340070680141359</v>
+      </c>
+    </row>
+    <row r="333" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A333" s="5">
+        <v>30</v>
+      </c>
+      <c r="B333" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C333" s="11">
+        <v>3.2860065720131449E-3</v>
+      </c>
+      <c r="D333">
+        <f t="shared" si="5"/>
+        <v>32.860065720131452</v>
+      </c>
+    </row>
+    <row r="334" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A334" s="5">
+        <v>30</v>
+      </c>
+      <c r="B334" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C334" s="11">
+        <v>3.0070060140120285E-3</v>
+      </c>
+      <c r="D334">
+        <f t="shared" si="5"/>
+        <v>30.070060140120287</v>
+      </c>
+    </row>
+    <row r="335" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A335" s="5">
+        <v>30</v>
+      </c>
+      <c r="B335" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C335" s="11">
+        <v>2.8830057660115325E-3</v>
+      </c>
+      <c r="D335">
+        <f t="shared" si="5"/>
+        <v>28.830057660115326</v>
+      </c>
+    </row>
+    <row r="336" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A336" s="5">
+        <v>30</v>
+      </c>
+      <c r="B336" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C336" s="11">
+        <v>3.0380060760121529E-3</v>
+      </c>
+      <c r="D336">
+        <f t="shared" si="5"/>
+        <v>30.38006076012153</v>
+      </c>
+    </row>
+    <row r="337" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A337" s="5">
+        <v>40</v>
+      </c>
+      <c r="B337" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C337" s="11">
+        <v>3.3480066960133912E-3</v>
+      </c>
+      <c r="D337">
+        <f t="shared" si="5"/>
+        <v>33.480066960133911</v>
+      </c>
+    </row>
+    <row r="338" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A338" s="5">
+        <v>40</v>
+      </c>
+      <c r="B338" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C338" s="11">
+        <v>3.1000062000124009E-3</v>
+      </c>
+      <c r="D338">
+        <f t="shared" si="5"/>
+        <v>31.000062000124011</v>
+      </c>
+    </row>
+    <row r="339" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A339" s="5">
+        <v>40</v>
+      </c>
+      <c r="B339" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C339" s="11">
+        <v>3.1620063240126489E-3</v>
+      </c>
+      <c r="D339">
+        <f t="shared" si="5"/>
+        <v>31.620063240126488</v>
+      </c>
+    </row>
+    <row r="340" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A340" s="5">
+        <v>40</v>
+      </c>
+      <c r="B340" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C340" s="11">
+        <v>3.1310062620125249E-3</v>
+      </c>
+      <c r="D340">
+        <f t="shared" si="5"/>
+        <v>31.310062620125251</v>
+      </c>
+    </row>
+    <row r="341" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A341" s="5">
+        <v>40</v>
+      </c>
+      <c r="B341" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C341" s="11">
+        <v>3.2860065720131432E-3</v>
+      </c>
+      <c r="D341">
+        <f t="shared" si="5"/>
+        <v>32.860065720131431</v>
+      </c>
+    </row>
+    <row r="342" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A342" s="5">
+        <v>50</v>
+      </c>
+      <c r="B342" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C342" s="11">
+        <v>3.5340070680141356E-3</v>
+      </c>
+      <c r="D342">
+        <f t="shared" si="5"/>
+        <v>35.340070680141359</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A343" s="5">
+        <v>50</v>
+      </c>
+      <c r="B343" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C343" s="11">
+        <v>3.1000062000124009E-3</v>
+      </c>
+      <c r="D343">
+        <f t="shared" si="5"/>
+        <v>31.000062000124011</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A344" s="5">
+        <v>50</v>
+      </c>
+      <c r="B344" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C344" s="11">
+        <v>3.0690061380122769E-3</v>
+      </c>
+      <c r="D344">
+        <f t="shared" si="5"/>
+        <v>30.690061380122771</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A345" s="5">
+        <v>50</v>
+      </c>
+      <c r="B345" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C345" s="11">
+        <v>3.2860065720131449E-3</v>
+      </c>
+      <c r="D345">
+        <f t="shared" si="5"/>
+        <v>32.860065720131452</v>
+      </c>
+    </row>
+    <row r="346" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A346" s="5">
+        <v>50</v>
+      </c>
+      <c r="B346" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C346" s="11">
+        <v>3.1000062000124009E-3</v>
+      </c>
+      <c r="D346">
+        <f t="shared" si="5"/>
+        <v>31.000062000124011</v>
+      </c>
+    </row>
+    <row r="347" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A347" s="5">
+        <v>60</v>
+      </c>
+      <c r="B347" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C347" s="11">
+        <v>3.5030070060140116E-3</v>
+      </c>
+      <c r="D347">
+        <f t="shared" si="5"/>
+        <v>35.030070060140119</v>
+      </c>
+    </row>
+    <row r="348" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A348" s="5">
+        <v>60</v>
+      </c>
+      <c r="B348" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C348" s="11">
+        <v>3.1620063240126489E-3</v>
+      </c>
+      <c r="D348">
+        <f t="shared" si="5"/>
+        <v>31.620063240126488</v>
+      </c>
+    </row>
+    <row r="349" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A349" s="5">
+        <v>60</v>
+      </c>
+      <c r="B349" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C349" s="11">
+        <v>3.1620063240126489E-3</v>
+      </c>
+      <c r="D349">
+        <f t="shared" si="5"/>
+        <v>31.620063240126488</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A350" s="5">
+        <v>60</v>
+      </c>
+      <c r="B350" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C350" s="11">
+        <v>3.1620063240126489E-3</v>
+      </c>
+      <c r="D350">
+        <f t="shared" si="5"/>
+        <v>31.620063240126488</v>
+      </c>
+    </row>
+    <row r="351" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A351" s="5">
+        <v>60</v>
+      </c>
+      <c r="B351" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C351" s="11">
+        <v>3.2860065720131432E-3</v>
+      </c>
+      <c r="D351">
+        <f t="shared" si="5"/>
+        <v>32.860065720131431</v>
+      </c>
+    </row>
+    <row r="352" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A352" s="4">
+        <v>0</v>
+      </c>
+      <c r="B352" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C352" s="11">
+        <v>0</v>
+      </c>
+      <c r="D352">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A353" s="4">
+        <v>0</v>
+      </c>
+      <c r="B353" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C353" s="11">
+        <v>0</v>
+      </c>
+      <c r="D353">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A354" s="4">
+        <v>0</v>
+      </c>
+      <c r="B354" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C354" s="11">
+        <v>0</v>
+      </c>
+      <c r="D354">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A355" s="4">
+        <v>0</v>
+      </c>
+      <c r="B355" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C355" s="11">
+        <v>0</v>
+      </c>
+      <c r="D355">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A356" s="4">
+        <v>0</v>
+      </c>
+      <c r="B356" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C356" s="11">
+        <v>0</v>
+      </c>
+      <c r="D356">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A357" s="5">
+        <v>10</v>
+      </c>
+      <c r="B357" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C357" s="11">
+        <v>1.9530039060078118E-3</v>
+      </c>
+      <c r="D357">
+        <f t="shared" si="5"/>
+        <v>19.530039060078117</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A358" s="5">
+        <v>10</v>
+      </c>
+      <c r="B358" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C358" s="11">
+        <v>2.0770041540083078E-3</v>
+      </c>
+      <c r="D358">
+        <f t="shared" si="5"/>
+        <v>20.770041540083078</v>
+      </c>
+    </row>
+    <row r="359" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A359" s="5">
+        <v>10</v>
+      </c>
+      <c r="B359" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C359" s="11">
+        <v>2.2010044020088042E-3</v>
+      </c>
+      <c r="D359">
+        <f t="shared" si="5"/>
+        <v>22.010044020088042</v>
+      </c>
+    </row>
+    <row r="360" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A360" s="5">
+        <v>10</v>
+      </c>
+      <c r="B360" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C360" s="11">
+        <v>2.1700043400086802E-3</v>
+      </c>
+      <c r="D360">
+        <f t="shared" si="5"/>
+        <v>21.700043400086802</v>
+      </c>
+    </row>
+    <row r="361" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A361" s="5">
+        <v>10</v>
+      </c>
+      <c r="B361" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C361" s="11">
+        <v>2.0460040920081838E-3</v>
+      </c>
+      <c r="D361">
+        <f t="shared" si="5"/>
+        <v>20.460040920081838</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A362" s="5">
+        <v>20</v>
+      </c>
+      <c r="B362" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C362" s="11">
+        <v>3.0690061380122752E-3</v>
+      </c>
+      <c r="D362">
+        <f t="shared" si="5"/>
+        <v>30.690061380122753</v>
+      </c>
+    </row>
+    <row r="363" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A363" s="5">
+        <v>20</v>
+      </c>
+      <c r="B363" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C363" s="11">
+        <v>2.9140058280116548E-3</v>
+      </c>
+      <c r="D363">
+        <f t="shared" si="5"/>
+        <v>29.140058280116548</v>
+      </c>
+    </row>
+    <row r="364" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A364" s="5">
+        <v>20</v>
+      </c>
+      <c r="B364" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C364" s="11">
+        <v>3.3170066340132672E-3</v>
+      </c>
+      <c r="D364">
+        <f t="shared" si="5"/>
+        <v>33.170066340132671</v>
+      </c>
+    </row>
+    <row r="365" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A365" s="5">
+        <v>20</v>
+      </c>
+      <c r="B365" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C365" s="11">
+        <v>3.3790067580135152E-3</v>
+      </c>
+      <c r="D365">
+        <f t="shared" si="5"/>
+        <v>33.790067580135151</v>
+      </c>
+    </row>
+    <row r="366" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A366" s="5">
+        <v>20</v>
+      </c>
+      <c r="B366" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C366" s="11">
+        <v>3.2550065100130192E-3</v>
+      </c>
+      <c r="D366">
+        <f t="shared" si="5"/>
+        <v>32.55006510013019</v>
+      </c>
+    </row>
+    <row r="367" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A367" s="5">
+        <v>30</v>
+      </c>
+      <c r="B367" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C367" s="11">
+        <v>3.4410068820137632E-3</v>
+      </c>
+      <c r="D367">
+        <f t="shared" si="5"/>
+        <v>34.410068820137631</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A368" s="5">
+        <v>30</v>
+      </c>
+      <c r="B368" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C368" s="11">
+        <v>3.4410068820137632E-3</v>
+      </c>
+      <c r="D368">
+        <f t="shared" si="5"/>
+        <v>34.410068820137631</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A369" s="5">
+        <v>30</v>
+      </c>
+      <c r="B369" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C369" s="11">
+        <v>3.7820075640151276E-3</v>
+      </c>
+      <c r="D369">
+        <f t="shared" si="5"/>
+        <v>37.820075640151273</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A370" s="5">
+        <v>30</v>
+      </c>
+      <c r="B370" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C370" s="11">
+        <v>3.7200074400148796E-3</v>
+      </c>
+      <c r="D370">
+        <f t="shared" si="5"/>
+        <v>37.200074400148793</v>
+      </c>
+    </row>
+    <row r="371" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A371" s="5">
+        <v>30</v>
+      </c>
+      <c r="B371" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C371" s="11">
+        <v>3.5340070680141356E-3</v>
+      </c>
+      <c r="D371">
+        <f t="shared" si="5"/>
+        <v>35.340070680141359</v>
+      </c>
+    </row>
+    <row r="372" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A372" s="5">
+        <v>40</v>
+      </c>
+      <c r="B372" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C372" s="11">
+        <v>3.6270072540145076E-3</v>
+      </c>
+      <c r="D372">
+        <f t="shared" si="5"/>
+        <v>36.270072540145073</v>
+      </c>
+    </row>
+    <row r="373" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A373" s="5">
+        <v>40</v>
+      </c>
+      <c r="B373" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C373" s="11">
+        <v>3.5650071300142596E-3</v>
+      </c>
+      <c r="D373">
+        <f t="shared" si="5"/>
+        <v>35.650071300142599</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A374" s="5">
+        <v>40</v>
+      </c>
+      <c r="B374" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C374" s="11">
+        <v>3.7820075640151276E-3</v>
+      </c>
+      <c r="D374">
+        <f t="shared" si="5"/>
+        <v>37.820075640151273</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A375" s="5">
+        <v>40</v>
+      </c>
+      <c r="B375" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C375" s="11">
+        <v>3.8130076260152516E-3</v>
+      </c>
+      <c r="D375">
+        <f t="shared" si="5"/>
+        <v>38.130076260152514</v>
+      </c>
+    </row>
+    <row r="376" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A376" s="5">
+        <v>40</v>
+      </c>
+      <c r="B376" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C376" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D376">
+        <f t="shared" si="5"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="377" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A377" s="5">
+        <v>50</v>
+      </c>
+      <c r="B377" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C377" s="11">
+        <v>3.6580073160146316E-3</v>
+      </c>
+      <c r="D377">
+        <f t="shared" si="5"/>
+        <v>36.580073160146313</v>
+      </c>
+    </row>
+    <row r="378" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A378" s="5">
+        <v>50</v>
+      </c>
+      <c r="B378" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C378" s="11">
+        <v>3.6890073780147556E-3</v>
+      </c>
+      <c r="D378">
+        <f t="shared" si="5"/>
+        <v>36.890073780147553</v>
+      </c>
+    </row>
+    <row r="379" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A379" s="5">
+        <v>50</v>
+      </c>
+      <c r="B379" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C379" s="11">
+        <v>3.9060078120156235E-3</v>
+      </c>
+      <c r="D379">
+        <f t="shared" si="5"/>
+        <v>39.060078120156234</v>
+      </c>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A380" s="5">
+        <v>50</v>
+      </c>
+      <c r="B380" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C380" s="11">
+        <v>3.937007874015748E-3</v>
+      </c>
+      <c r="D380">
+        <f t="shared" si="5"/>
+        <v>39.370078740157481</v>
+      </c>
+    </row>
+    <row r="381" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A381" s="5">
+        <v>50</v>
+      </c>
+      <c r="B381" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C381" s="11">
+        <v>3.7510075020150036E-3</v>
+      </c>
+      <c r="D381">
+        <f t="shared" si="5"/>
+        <v>37.510075020150033</v>
+      </c>
+    </row>
+    <row r="382" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A382" s="5">
+        <v>60</v>
+      </c>
+      <c r="B382" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C382" s="11">
+        <v>3.7820075640151276E-3</v>
+      </c>
+      <c r="D382">
+        <f t="shared" si="5"/>
+        <v>37.820075640151273</v>
+      </c>
+    </row>
+    <row r="383" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A383" s="5">
+        <v>60</v>
+      </c>
+      <c r="B383" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C383" s="11">
+        <v>3.7510075020150036E-3</v>
+      </c>
+      <c r="D383">
+        <f t="shared" si="5"/>
+        <v>37.510075020150033</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A384" s="5">
+        <v>60</v>
+      </c>
+      <c r="B384" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C384" s="11">
+        <v>3.9060078120156235E-3</v>
+      </c>
+      <c r="D384">
+        <f t="shared" si="5"/>
+        <v>39.060078120156234</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A385" s="5">
+        <v>60</v>
+      </c>
+      <c r="B385" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C385" s="11">
+        <v>3.8750077500154996E-3</v>
+      </c>
+      <c r="D385">
+        <f t="shared" si="5"/>
+        <v>38.750077500154994</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A386" s="5">
+        <v>60</v>
+      </c>
+      <c r="B386" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C386" s="11">
+        <v>3.7510075020150036E-3</v>
+      </c>
+      <c r="D386">
+        <f t="shared" si="5"/>
+        <v>37.510075020150033</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A387" s="4">
+        <v>0</v>
+      </c>
+      <c r="B387" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C387" s="11">
+        <v>0</v>
+      </c>
+      <c r="D387">
+        <f t="shared" ref="D387:D421" si="6">C387 * 10000</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A388" s="4">
+        <v>0</v>
+      </c>
+      <c r="B388" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C388" s="11">
+        <v>0</v>
+      </c>
+      <c r="D388">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A389" s="4">
+        <v>0</v>
+      </c>
+      <c r="B389" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C389" s="11">
+        <v>0</v>
+      </c>
+      <c r="D389">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A390" s="4">
+        <v>0</v>
+      </c>
+      <c r="B390" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C390" s="11">
+        <v>0</v>
+      </c>
+      <c r="D390">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A391" s="4">
+        <v>0</v>
+      </c>
+      <c r="B391" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C391" s="11">
+        <v>0</v>
+      </c>
+      <c r="D391">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A392" s="5">
+        <v>10</v>
+      </c>
+      <c r="B392" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C392" s="11">
+        <v>2.4180048360096704E-3</v>
+      </c>
+      <c r="D392">
+        <f t="shared" si="6"/>
+        <v>24.180048360096706</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A393" s="5">
+        <v>10</v>
+      </c>
+      <c r="B393" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C393" s="11">
+        <v>2.2940045880091762E-3</v>
+      </c>
+      <c r="D393">
+        <f t="shared" si="6"/>
+        <v>22.940045880091763</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A394" s="5">
+        <v>10</v>
+      </c>
+      <c r="B394" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C394" s="11">
+        <v>2.2010044020088042E-3</v>
+      </c>
+      <c r="D394">
+        <f t="shared" si="6"/>
+        <v>22.010044020088042</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A395" s="5">
+        <v>10</v>
+      </c>
+      <c r="B395" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C395" s="11">
+        <v>1.7360034720069438E-3</v>
+      </c>
+      <c r="D395">
+        <f t="shared" si="6"/>
+        <v>17.360034720069439</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A396" s="5">
+        <v>10</v>
+      </c>
+      <c r="B396" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C396" s="11">
+        <v>1.7050034100068196E-3</v>
+      </c>
+      <c r="D396">
+        <f t="shared" si="6"/>
+        <v>17.050034100068196</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A397" s="5">
+        <v>20</v>
+      </c>
+      <c r="B397" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C397" s="11">
+        <v>3.3480066960133912E-3</v>
+      </c>
+      <c r="D397">
+        <f t="shared" si="6"/>
+        <v>33.480066960133911</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A398" s="5">
+        <v>20</v>
+      </c>
+      <c r="B398" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C398" s="11">
+        <v>3.1620063240126472E-3</v>
+      </c>
+      <c r="D398">
+        <f t="shared" si="6"/>
+        <v>31.620063240126473</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A399" s="5">
+        <v>20</v>
+      </c>
+      <c r="B399" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C399" s="11">
+        <v>3.2240064480128969E-3</v>
+      </c>
+      <c r="D399">
+        <f t="shared" si="6"/>
+        <v>32.240064480128972</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A400" s="5">
+        <v>20</v>
+      </c>
+      <c r="B400" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C400" s="11">
+        <v>2.5110050220100424E-3</v>
+      </c>
+      <c r="D400">
+        <f t="shared" si="6"/>
+        <v>25.110050220100423</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A401" s="5">
+        <v>20</v>
+      </c>
+      <c r="B401" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C401" s="11">
+        <v>2.8210056420112828E-3</v>
+      </c>
+      <c r="D401">
+        <f t="shared" si="6"/>
+        <v>28.210056420112828</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A402" s="5">
+        <v>30</v>
+      </c>
+      <c r="B402" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C402" s="11">
+        <v>3.5960071920143836E-3</v>
+      </c>
+      <c r="D402">
+        <f t="shared" si="6"/>
+        <v>35.960071920143832</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A403" s="5">
+        <v>30</v>
+      </c>
+      <c r="B403" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C403" s="11">
+        <v>3.5340070680141356E-3</v>
+      </c>
+      <c r="D403">
+        <f t="shared" si="6"/>
+        <v>35.340070680141359</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A404" s="5">
+        <v>30</v>
+      </c>
+      <c r="B404" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C404" s="11">
+        <v>3.5650071300142613E-3</v>
+      </c>
+      <c r="D404">
+        <f t="shared" si="6"/>
+        <v>35.650071300142613</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A405" s="5">
+        <v>30</v>
+      </c>
+      <c r="B405" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C405" s="11">
+        <v>2.9760059520119028E-3</v>
+      </c>
+      <c r="D405">
+        <f t="shared" si="6"/>
+        <v>29.760059520119029</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A406" s="5">
+        <v>30</v>
+      </c>
+      <c r="B406" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C406" s="11">
+        <v>3.0690061380122752E-3</v>
+      </c>
+      <c r="D406">
+        <f t="shared" si="6"/>
+        <v>30.690061380122753</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A407" s="5">
+        <v>40</v>
+      </c>
+      <c r="B407" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C407" s="11">
+        <v>3.8440076880153756E-3</v>
+      </c>
+      <c r="D407">
+        <f t="shared" si="6"/>
+        <v>38.440076880153754</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A408" s="5">
+        <v>40</v>
+      </c>
+      <c r="B408" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C408" s="11">
+        <v>3.8130076260152516E-3</v>
+      </c>
+      <c r="D408">
+        <f t="shared" si="6"/>
+        <v>38.130076260152514</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A409" s="5">
+        <v>40</v>
+      </c>
+      <c r="B409" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C409" s="11">
+        <v>3.7820075640151293E-3</v>
+      </c>
+      <c r="D409">
+        <f t="shared" si="6"/>
+        <v>37.820075640151295</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A410" s="5">
+        <v>40</v>
+      </c>
+      <c r="B410" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C410" s="11">
+        <v>3.1620063240126472E-3</v>
+      </c>
+      <c r="D410">
+        <f t="shared" si="6"/>
+        <v>31.620063240126473</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A411" s="5">
+        <v>40</v>
+      </c>
+      <c r="B411" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C411" s="11">
+        <v>3.3480066960133912E-3</v>
+      </c>
+      <c r="D411">
+        <f t="shared" si="6"/>
+        <v>33.480066960133911</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A412" s="5">
+        <v>50</v>
+      </c>
+      <c r="B412" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C412" s="11">
+        <v>3.9680079360158715E-3</v>
+      </c>
+      <c r="D412">
+        <f t="shared" si="6"/>
+        <v>39.680079360158715</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A413" s="5">
+        <v>50</v>
+      </c>
+      <c r="B413" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C413" s="11">
+        <v>3.7820075640151276E-3</v>
+      </c>
+      <c r="D413">
+        <f t="shared" si="6"/>
+        <v>37.820075640151273</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A414" s="5">
+        <v>50</v>
+      </c>
+      <c r="B414" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C414" s="11">
+        <v>3.8750077500155013E-3</v>
+      </c>
+      <c r="D414">
+        <f t="shared" si="6"/>
+        <v>38.750077500155015</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A415" s="5">
+        <v>50</v>
+      </c>
+      <c r="B415" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C415" s="11">
+        <v>3.1930063860127712E-3</v>
+      </c>
+      <c r="D415">
+        <f t="shared" si="6"/>
+        <v>31.930063860127714</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A416" s="5">
+        <v>50</v>
+      </c>
+      <c r="B416" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C416" s="11">
+        <v>3.3790067580135152E-3</v>
+      </c>
+      <c r="D416">
+        <f t="shared" si="6"/>
+        <v>33.790067580135151</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A417" s="5">
+        <v>60</v>
+      </c>
+      <c r="B417" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C417">
+        <v>4.061008122016244E-3</v>
+      </c>
+      <c r="D417">
+        <f t="shared" si="6"/>
+        <v>40.610081220162442</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A418" s="5">
+        <v>60</v>
+      </c>
+      <c r="B418" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C418">
+        <v>3.9680079360158715E-3</v>
+      </c>
+      <c r="D418">
+        <f t="shared" si="6"/>
+        <v>39.680079360158715</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A419" s="5">
+        <v>60</v>
+      </c>
+      <c r="B419" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C419">
+        <v>3.9680079360158733E-3</v>
+      </c>
+      <c r="D419">
+        <f t="shared" si="6"/>
+        <v>39.680079360158736</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A420" s="5">
+        <v>60</v>
+      </c>
+      <c r="B420" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C420">
+        <v>3.3170066340132672E-3</v>
+      </c>
+      <c r="D420">
+        <f t="shared" si="6"/>
+        <v>33.170066340132671</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A421" s="5">
+        <v>60</v>
+      </c>
+      <c r="B421" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C421">
+        <v>3.5960071920143836E-3</v>
+      </c>
+      <c r="D421">
+        <f t="shared" si="6"/>
+        <v>35.960071920143832</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52EC2250-5D34-B040-9FCC-DF20636C09BE}">
   <dimension ref="A1:H421"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -55598,7 +64824,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B91D78A-59F5-754B-92FA-07DC9469041F}">
   <dimension ref="A1:D421"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>

--- a/HelloFresh_Absorption_Fall2025.xlsx
+++ b/HelloFresh_Absorption_Fall2025.xlsx
@@ -8,18 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://nuwildcat-my.sharepoint.com/personal/stn424_ads_northwestern_edu/Documents/Collaborations/Proposals/GO-Barrier, TFMI Proposals with Tim Wei/URAP_2023-10/Shared/Lanning, Mackenzie/Absorption Data/Fall 2025/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2119" documentId="13_ncr:1_{F2E763B4-4DB6-894B-B240-8188D6068E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EB26540-F5B1-1341-95D7-B9E92C4367C1}"/>
+  <xr:revisionPtr revIDLastSave="1712" documentId="13_ncr:1_{F2E763B4-4DB6-894B-B240-8188D6068E1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8CEF8C6-F78E-8742-AFFB-1CA691E0992F}"/>
   <bookViews>
-    <workbookView xWindow="13980" yWindow="740" windowWidth="15420" windowHeight="17180" firstSheet="1" activeTab="4" xr2:uid="{304DC28A-0BB6-064B-B35E-217EA1A1C90F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17180" activeTab="5" xr2:uid="{304DC28A-0BB6-064B-B35E-217EA1A1C90F}"/>
   </bookViews>
   <sheets>
     <sheet name="Crayola Method" sheetId="1" r:id="rId1"/>
     <sheet name="Boat Method" sheetId="2" r:id="rId2"/>
     <sheet name="Boat Method (Retest)" sheetId="4" r:id="rId3"/>
     <sheet name="Metsä EB" sheetId="3" r:id="rId4"/>
-    <sheet name="Absorption for R" sheetId="7" r:id="rId5"/>
-    <sheet name="Formatting for R" sheetId="5" r:id="rId6"/>
-    <sheet name="Figures for R" sheetId="6" r:id="rId7"/>
+    <sheet name="Formatting for R" sheetId="5" r:id="rId5"/>
+    <sheet name="Figures for R" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1238" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="814" uniqueCount="56">
   <si>
     <t>Raw Weights (gms)</t>
   </si>
@@ -210,12 +209,6 @@
   </si>
   <si>
     <t>0.2% GO</t>
-  </si>
-  <si>
-    <t>Absorption Raw</t>
-  </si>
-  <si>
-    <t>Absorption Large</t>
   </si>
 </sst>
 </file>
@@ -9558,1705 +9551,6 @@
 </file>
 
 <file path=xl/charts/chart16.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200" i="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>HelloFresh</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="1"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Boat Method (Retest)'!$D$141</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>DI Water @ 100°C</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:prstDash val="sysDot"/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:errBars>
-            <c:errDir val="y"/>
-            <c:errBarType val="both"/>
-            <c:errValType val="cust"/>
-            <c:noEndCap val="0"/>
-            <c:plus>
-              <c:numRef>
-                <c:f>'Boat Method (Retest)'!$D$142:$D$148</c:f>
-                <c:numCache>
-                  <c:formatCode>General</c:formatCode>
-                  <c:ptCount val="7"/>
-                  <c:pt idx="0">
-                    <c:v>0</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>0.12723213842582981</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>0.13136292466267202</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>0.134284860746891</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>0.12517170131277844</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>0.109941473521196</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>0.10419045694508391</c:v>
-                  </c:pt>
-                </c:numCache>
-              </c:numRef>
-            </c:plus>
-            <c:minus>
-              <c:numRef>
-                <c:f>'Boat Method (Retest)'!$D$142:$D$148</c:f>
-                <c:numCache>
-                  <c:formatCode>General</c:formatCode>
-                  <c:ptCount val="7"/>
-                  <c:pt idx="0">
-                    <c:v>0</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>0.12723213842582981</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>0.13136292466267202</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>0.134284860746891</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>0.12517170131277844</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>0.109941473521196</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>0.10419045694508391</c:v>
-                  </c:pt>
-                </c:numCache>
-              </c:numRef>
-            </c:minus>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:errBars>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Boat Method (Retest)'!$B$130:$B$136</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>60</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Boat Method (Retest)'!$D$130:$D$136</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.4364713004960451</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.51531160069446025</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.53478420496033385</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.57372941349208095</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.59462684246033559</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.62169851180557445</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8742-6A45-8E5C-190D3C5459B4}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Boat Method (Retest)'!$I$129</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0.1% GO @ 100°C </c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Boat Method (Retest)'!$B$130:$B$136</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>60</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Boat Method (Retest)'!$I$130:$I$136</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.29257448220778787</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.3111973135710977</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.32736977238660353</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.34550252924035252</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.34746282727859573</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.35677424296025051</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000008-8742-6A45-8E5C-190D3C5459B4}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Boat Method (Retest)'!$R$129</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>25% WBBC @ 100°C</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Boat Method (Retest)'!$B$130:$B$136</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>60</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Boat Method (Retest)'!$R$130:$R$136</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.13836403442827419</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.21103594568585438</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.23731279495413199</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.24470315881083501</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.25086179535808761</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.25250409843735494</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000009-8742-6A45-8E5C-190D3C5459B4}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="35411248"/>
-        <c:axId val="9409920"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="35411248"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="60"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1200" i="1">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:rPr>
-                  <a:t>time (min)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="in"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="9409920"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="9409920"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="1"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1200" i="1">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:rPr>
-                  <a:t>absorbed water weight / unit dry paper weight (gm/gm)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="0"/>
-        <c:majorTickMark val="in"/>
-        <c:minorTickMark val="in"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="35411248"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.8038751991516695"/>
-          <c:y val="0.17533106156733624"/>
-          <c:w val="0.17693780588355021"/>
-          <c:h val="0.11296035888095081"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart17.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US" sz="1200" i="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:rPr>
-              <a:t>HelloFresh</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="1"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:scatterChart>
-        <c:scatterStyle val="lineMarker"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Boat Method (Retest)'!$D$141</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>DI Water @ 100°C</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:prstDash val="sysDot"/>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:errBars>
-            <c:errDir val="y"/>
-            <c:errBarType val="both"/>
-            <c:errValType val="cust"/>
-            <c:noEndCap val="0"/>
-            <c:plus>
-              <c:numRef>
-                <c:f>'Boat Method (Retest)'!$D$142:$D$148</c:f>
-                <c:numCache>
-                  <c:formatCode>General</c:formatCode>
-                  <c:ptCount val="7"/>
-                  <c:pt idx="0">
-                    <c:v>0</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>0.12723213842582981</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>0.13136292466267202</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>0.134284860746891</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>0.12517170131277844</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>0.109941473521196</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>0.10419045694508391</c:v>
-                  </c:pt>
-                </c:numCache>
-              </c:numRef>
-            </c:plus>
-            <c:minus>
-              <c:numRef>
-                <c:f>'Boat Method (Retest)'!$D$142:$D$148</c:f>
-                <c:numCache>
-                  <c:formatCode>General</c:formatCode>
-                  <c:ptCount val="7"/>
-                  <c:pt idx="0">
-                    <c:v>0</c:v>
-                  </c:pt>
-                  <c:pt idx="1">
-                    <c:v>0.12723213842582981</c:v>
-                  </c:pt>
-                  <c:pt idx="2">
-                    <c:v>0.13136292466267202</c:v>
-                  </c:pt>
-                  <c:pt idx="3">
-                    <c:v>0.134284860746891</c:v>
-                  </c:pt>
-                  <c:pt idx="4">
-                    <c:v>0.12517170131277844</c:v>
-                  </c:pt>
-                  <c:pt idx="5">
-                    <c:v>0.109941473521196</c:v>
-                  </c:pt>
-                  <c:pt idx="6">
-                    <c:v>0.10419045694508391</c:v>
-                  </c:pt>
-                </c:numCache>
-              </c:numRef>
-            </c:minus>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:round/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:errBars>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Boat Method (Retest)'!$B$130:$B$136</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>60</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Boat Method (Retest)'!$D$130:$D$136</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.4364713004960451</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.51531160069446025</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.53478420496033385</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.57372941349208095</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.59462684246033559</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.62169851180557445</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-6117-724C-AB49-EC257783BEDE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Boat Method (Retest)'!$M$129</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0.5 wt% GO @ 100°C</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="6"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-                <a:prstDash val="sysDot"/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Boat Method (Retest)'!$B$130:$B$136</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>60</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Boat Method (Retest)'!$M$130:$M$136</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.26322584290738199</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.28009929437580394</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.29166966109700754</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.2960085486174589</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.3008295347512937</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.30275792920482769</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-6117-724C-AB49-EC257783BEDE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="2"/>
-          <c:order val="2"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Boat Method (Retest)'!$Q$129</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>15% WBBC @ 100°C</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent3"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent3"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Boat Method (Retest)'!$B$130:$B$136</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>60</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Boat Method (Retest)'!$Q$130:$Q$136</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.18855657823047495</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.2238550845816776</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.22698280033431581</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.23100414915913636</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.23189778223131868</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.23457868144786573</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-6117-724C-AB49-EC257783BEDE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="3"/>
-          <c:order val="3"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Boat Method (Retest)'!$K$129</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>0.2 wt% GO @ 100°C</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="19050" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent4"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent4"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:xVal>
-            <c:numRef>
-              <c:f>'Boat Method (Retest)'!$B$130:$B$136</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>10</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>20</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>30</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>40</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>50</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>60</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:xVal>
-          <c:yVal>
-            <c:numRef>
-              <c:f>'Boat Method (Retest)'!$K$130:$K$136</c:f>
-              <c:numCache>
-                <c:formatCode>0.0000</c:formatCode>
-                <c:ptCount val="7"/>
-                <c:pt idx="0">
-                  <c:v>0</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>0.26497392836152356</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>0.28254126062858592</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>0.29181290821397998</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>0.30791629612545385</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>0.31279611064408219</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>0.31084418483663079</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:yVal>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-6117-724C-AB49-EC257783BEDE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:axId val="35411248"/>
-        <c:axId val="9409920"/>
-      </c:scatterChart>
-      <c:valAx>
-        <c:axId val="35411248"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="60"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1200" i="1">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:rPr>
-                  <a:t>time (min)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="in"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="9409920"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:valAx>
-        <c:axId val="9409920"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-          <c:max val="1"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US" sz="1200" i="1">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1"/>
-                    </a:solidFill>
-                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  </a:rPr>
-                  <a:t>absorbed water weight / unit dry paper weight (gm/gm)</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1200" b="0" i="1" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1"/>
-                  </a:solidFill>
-                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="0.0" sourceLinked="0"/>
-        <c:majorTickMark val="in"/>
-        <c:minorTickMark val="in"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1"/>
-                </a:solidFill>
-                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="35411248"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="midCat"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="r"/>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.8038751991516695"/>
-          <c:y val="0.17533106156733624"/>
-          <c:w val="0.17693780588355021"/>
-          <c:h val="0.15061381184126774"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart18.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -21530,86 +19824,6 @@
 </file>
 
 <file path=xl/charts/colors16.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors17.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors18.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -25582,1038 +23796,6 @@
 </file>
 
 <file path=xl/charts/style16.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style17.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style18.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -31839,82 +29021,6 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>216</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>178931</xdr:colOff>
-      <xdr:row>244</xdr:row>
-      <xdr:rowOff>14625</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="4" name="Chart 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9CBA7F87-0856-434F-A5AC-3CBD2D74C179}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>172469</xdr:colOff>
-      <xdr:row>217</xdr:row>
-      <xdr:rowOff>141112</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>194610</xdr:colOff>
-      <xdr:row>245</xdr:row>
-      <xdr:rowOff>155737</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="5" name="Chart 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D128520D-850E-574E-9D2D-6B60E4E7BE08}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -32658,10 +29764,7 @@
     <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A9" s="4"/>
       <c r="B9" s="5"/>
-      <c r="C9" s="5">
-        <f>AVERAGE(C4:C8)</f>
-        <v>0.33939999999999998</v>
-      </c>
+      <c r="C9" s="5"/>
       <c r="D9" s="5"/>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
@@ -34350,11 +31453,11 @@
         <v>0</v>
       </c>
       <c r="C49" s="7">
-        <f xml:space="preserve"> (C4-C4)/14.52</f>
+        <f t="shared" ref="C49:F53" si="0" xml:space="preserve"> (C4-C4)/14.52</f>
         <v>0</v>
       </c>
       <c r="D49" s="7">
-        <f t="shared" ref="C49:F53" si="0" xml:space="preserve"> (D4-D4)/14.52</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E49" s="7">
@@ -35502,7 +32605,7 @@
         <v>30</v>
       </c>
       <c r="C70" s="7">
-        <f xml:space="preserve"> (C25-C7)/14.52</f>
+        <f t="shared" si="44"/>
         <v>5.2341597796143223E-3</v>
       </c>
       <c r="D70" s="7">
@@ -35825,7 +32928,7 @@
         <v>40</v>
       </c>
       <c r="C76" s="7">
-        <f xml:space="preserve"> (C31-C7)/14.52</f>
+        <f t="shared" si="61"/>
         <v>5.9228650137741028E-3</v>
       </c>
       <c r="D76" s="7">
@@ -37385,11 +34488,11 @@
         <v>30</v>
       </c>
       <c r="C108" s="7">
-        <f xml:space="preserve"> STDEV(C67:C71)*32.258/AVERAGE(C4:C8)</f>
+        <f t="shared" ref="C108:K108" si="139" xml:space="preserve"> STDEV(C67:C71)*32.258/AVERAGE(C4:C8)</f>
         <v>5.1207632133280175E-2</v>
       </c>
       <c r="D108" s="7">
-        <f t="shared" ref="D108:K108" si="139" xml:space="preserve"> STDEV(D67:D71)*32.258/AVERAGE(D4:D8)</f>
+        <f t="shared" si="139"/>
         <v>0.53417540201550062</v>
       </c>
       <c r="E108" s="7">
@@ -37444,11 +34547,11 @@
         <v>40</v>
       </c>
       <c r="C109" s="7">
-        <f xml:space="preserve"> STDEV(C73:C77)*32.258/AVERAGE(C4:C8)</f>
+        <f t="shared" ref="C109:K109" si="142" xml:space="preserve"> STDEV(C73:C77)*32.258/AVERAGE(C4:C8)</f>
         <v>6.902578857180762E-2</v>
       </c>
       <c r="D109" s="7">
-        <f t="shared" ref="D109:K109" si="142" xml:space="preserve"> STDEV(D73:D77)*32.258/AVERAGE(D4:D8)</f>
+        <f t="shared" si="142"/>
         <v>0.47029695344489003</v>
       </c>
       <c r="E109" s="7">
@@ -43285,7 +40388,6 @@
       <c r="G8" s="11">
         <v>0.32100000000000001</v>
       </c>
-      <c r="H8" s="24"/>
       <c r="I8" s="11">
         <v>0.32800000000000001</v>
       </c>
@@ -45750,7 +42852,7 @@
         <v>20</v>
       </c>
       <c r="C68" s="7">
-        <f xml:space="preserve"> (C17-C5)/32.258</f>
+        <f t="shared" si="42"/>
         <v>4.061008122016244E-3</v>
       </c>
       <c r="D68" s="7">
@@ -47598,11 +44700,11 @@
         <v>10</v>
       </c>
       <c r="C107" s="12">
-        <f xml:space="preserve"> AVERAGE(C61:C65)*10000</f>
+        <f t="shared" ref="C107:G107" si="151" xml:space="preserve"> AVERAGE(C61:C65)*10000</f>
         <v>37.634075268150532</v>
       </c>
       <c r="D107" s="12">
-        <f t="shared" ref="C107:G107" si="151" xml:space="preserve"> AVERAGE(D61:D65)*10000</f>
+        <f t="shared" si="151"/>
         <v>56.978113956227901</v>
       </c>
       <c r="E107" s="12">
@@ -48670,11 +45772,11 @@
         <v>10</v>
       </c>
       <c r="C131" s="7">
-        <f>AVERAGE(C61:C65)*25.8/AVERAGE(C4:C8)</f>
+        <f t="shared" ref="C131:E131" si="214">AVERAGE(C61:C65)*25.8/AVERAGE(C4:C8)</f>
         <v>0.2944084723827422</v>
       </c>
       <c r="D131" s="7">
-        <f t="shared" ref="C131:E131" si="214">AVERAGE(D61:D65)*25.8/AVERAGE(D4:D8)</f>
+        <f t="shared" si="214"/>
         <v>0.4364713004960451</v>
       </c>
       <c r="E131" s="7">
@@ -48733,11 +45835,11 @@
         <v>20</v>
       </c>
       <c r="C132" s="7">
-        <f>AVERAGE(C67:C71)*25.8/AVERAGE(C4:C8)</f>
+        <f t="shared" ref="C132:E132" si="218">AVERAGE(C67:C71)*25.8/AVERAGE(C4:C8)</f>
         <v>0.32496487066958368</v>
       </c>
       <c r="D132" s="7">
-        <f t="shared" ref="C132:E132" si="218">AVERAGE(D67:D71)*25.8/AVERAGE(D4:D8)</f>
+        <f t="shared" si="218"/>
         <v>0.51531160069446025</v>
       </c>
       <c r="E132" s="7">
@@ -49010,7 +46112,7 @@
         <v>0.35677424296025051</v>
       </c>
       <c r="J136" s="7">
-        <f t="shared" ref="J136:M136" si="236">AVERAGE(J91:J95)*25.8/AVERAGE(J4:J8)</f>
+        <f t="shared" ref="I136:M136" si="236">AVERAGE(J91:J95)*25.8/AVERAGE(J4:J8)</f>
         <v>0.35096779054317595</v>
       </c>
       <c r="K136" s="7">
@@ -49213,7 +46315,7 @@
         <v>0.12723213842582981</v>
       </c>
       <c r="E143" s="7">
-        <f t="shared" ref="E143" si="243" xml:space="preserve"> STDEV(E61:E65)*22.58/AVERAGE(E4:E8)</f>
+        <f t="shared" ref="C143:E143" si="243" xml:space="preserve"> STDEV(E61:E65)*22.58/AVERAGE(E4:E8)</f>
         <v>0.10299723685496648</v>
       </c>
       <c r="F143" s="7">
@@ -49293,7 +46395,7 @@
         <v>9.9438732493841893E-3</v>
       </c>
       <c r="J144" s="7">
-        <f t="shared" ref="J144:M144" si="250" xml:space="preserve"> STDEV(J67:J71)*22.58/AVERAGE(J4:J8)</f>
+        <f t="shared" ref="I144:M144" si="250" xml:space="preserve"> STDEV(J67:J71)*22.58/AVERAGE(J4:J8)</f>
         <v>1.5473952385165919E-2</v>
       </c>
       <c r="K144" s="7">
@@ -53624,6334 +50726,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A43CB27B-6453-3E45-8189-F45331D133AA}">
-  <dimension ref="A1:D421"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="2" max="2" width="21.5" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="25" t="s">
-        <v>38</v>
-      </c>
-      <c r="B1" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C1" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="25" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="4">
-        <v>0</v>
-      </c>
-      <c r="B2" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="27">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <f>C2 * 10000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="4">
-        <v>0</v>
-      </c>
-      <c r="B3" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="27">
-        <v>0</v>
-      </c>
-      <c r="D3">
-        <f t="shared" ref="D3:D66" si="0">C3 * 10000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="4">
-        <v>0</v>
-      </c>
-      <c r="B4" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="27">
-        <v>0</v>
-      </c>
-      <c r="D4">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="4">
-        <v>0</v>
-      </c>
-      <c r="B5" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="27">
-        <v>0</v>
-      </c>
-      <c r="D5">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="4">
-        <v>0</v>
-      </c>
-      <c r="B6" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C6" s="27">
-        <v>0</v>
-      </c>
-      <c r="D6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="5">
-        <v>10</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="27">
-        <v>3.7510075020150036E-3</v>
-      </c>
-      <c r="D7">
-        <f t="shared" si="0"/>
-        <v>37.510075020150033</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="5">
-        <v>10</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="27">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D8">
-        <f t="shared" si="0"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="5">
-        <v>10</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C9" s="27">
-        <v>3.9680079360158715E-3</v>
-      </c>
-      <c r="D9">
-        <f t="shared" si="0"/>
-        <v>39.680079360158715</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A10" s="5">
-        <v>10</v>
-      </c>
-      <c r="B10" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C10" s="27">
-        <v>3.5960071920143836E-3</v>
-      </c>
-      <c r="D10">
-        <f t="shared" si="0"/>
-        <v>35.960071920143832</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="5">
-        <v>10</v>
-      </c>
-      <c r="B11" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="27">
-        <v>3.8130076260152516E-3</v>
-      </c>
-      <c r="D11">
-        <f t="shared" si="0"/>
-        <v>38.130076260152514</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="5">
-        <v>20</v>
-      </c>
-      <c r="B12" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" s="27">
-        <v>4.2470084940169879E-3</v>
-      </c>
-      <c r="D12">
-        <f t="shared" si="0"/>
-        <v>42.470084940169876</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="5">
-        <v>20</v>
-      </c>
-      <c r="B13" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="27">
-        <v>4.061008122016244E-3</v>
-      </c>
-      <c r="D13">
-        <f t="shared" si="0"/>
-        <v>40.610081220162442</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="5">
-        <v>20</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="27">
-        <v>4.123008246016492E-3</v>
-      </c>
-      <c r="D14">
-        <f t="shared" si="0"/>
-        <v>41.230082460164923</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A15" s="5">
-        <v>20</v>
-      </c>
-      <c r="B15" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C15" s="27">
-        <v>3.9060078120156235E-3</v>
-      </c>
-      <c r="D15">
-        <f t="shared" si="0"/>
-        <v>39.060078120156234</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="5">
-        <v>20</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="27">
-        <v>4.4330088660177302E-3</v>
-      </c>
-      <c r="D16">
-        <f t="shared" si="0"/>
-        <v>44.330088660177303</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="5">
-        <v>30</v>
-      </c>
-      <c r="B17" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="27">
-        <v>4.5260090520181026E-3</v>
-      </c>
-      <c r="D17">
-        <f t="shared" si="0"/>
-        <v>45.260090520181024</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="5">
-        <v>30</v>
-      </c>
-      <c r="B18" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="27">
-        <v>4.3400086800173586E-3</v>
-      </c>
-      <c r="D18">
-        <f t="shared" si="0"/>
-        <v>43.40008680017359</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="5">
-        <v>30</v>
-      </c>
-      <c r="B19" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="27">
-        <v>4.5880091760183506E-3</v>
-      </c>
-      <c r="D19">
-        <f t="shared" si="0"/>
-        <v>45.880091760183504</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="5">
-        <v>30</v>
-      </c>
-      <c r="B20" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="27">
-        <v>4.4020088040176084E-3</v>
-      </c>
-      <c r="D20">
-        <f t="shared" si="0"/>
-        <v>44.020088040176084</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="5">
-        <v>30</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="27">
-        <v>4.929009858019715E-3</v>
-      </c>
-      <c r="D21">
-        <f t="shared" si="0"/>
-        <v>49.290098580197153</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="5">
-        <v>40</v>
-      </c>
-      <c r="B22" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="10">
-        <v>4.6190092380184742E-3</v>
-      </c>
-      <c r="D22">
-        <f t="shared" si="0"/>
-        <v>46.190092380184744</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="5">
-        <v>40</v>
-      </c>
-      <c r="B23" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" s="10">
-        <v>4.4020088040176066E-3</v>
-      </c>
-      <c r="D23">
-        <f t="shared" si="0"/>
-        <v>44.020088040176063</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="5">
-        <v>40</v>
-      </c>
-      <c r="B24" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C24" s="10">
-        <v>4.867009734019467E-3</v>
-      </c>
-      <c r="D24">
-        <f t="shared" si="0"/>
-        <v>48.670097340194673</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="5">
-        <v>40</v>
-      </c>
-      <c r="B25" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="10">
-        <v>4.4640089280178563E-3</v>
-      </c>
-      <c r="D25">
-        <f t="shared" si="0"/>
-        <v>44.640089280178564</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="5">
-        <v>40</v>
-      </c>
-      <c r="B26" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C26" s="10">
-        <v>5.0840101680203345E-3</v>
-      </c>
-      <c r="D26">
-        <f t="shared" si="0"/>
-        <v>50.840101680203347</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="5">
-        <v>50</v>
-      </c>
-      <c r="B27" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C27" s="10">
-        <v>4.9600099200198386E-3</v>
-      </c>
-      <c r="D27">
-        <f t="shared" si="0"/>
-        <v>49.600099200198386</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="5">
-        <v>50</v>
-      </c>
-      <c r="B28" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="10">
-        <v>4.743009486018971E-3</v>
-      </c>
-      <c r="D28">
-        <f t="shared" si="0"/>
-        <v>47.430094860189712</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="5">
-        <v>50</v>
-      </c>
-      <c r="B29" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" s="10">
-        <v>5.301010602021203E-3</v>
-      </c>
-      <c r="D29">
-        <f t="shared" si="0"/>
-        <v>53.010106020212028</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="5">
-        <v>50</v>
-      </c>
-      <c r="B30" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="10">
-        <v>4.6190092380184742E-3</v>
-      </c>
-      <c r="D30">
-        <f t="shared" si="0"/>
-        <v>46.190092380184744</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="5">
-        <v>50</v>
-      </c>
-      <c r="B31" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C31" s="10">
-        <v>5.2080104160208314E-3</v>
-      </c>
-      <c r="D31">
-        <f t="shared" si="0"/>
-        <v>52.080104160208315</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="5">
-        <v>60</v>
-      </c>
-      <c r="B32" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C32" s="10">
-        <v>5.2080104160208314E-3</v>
-      </c>
-      <c r="D32">
-        <f t="shared" si="0"/>
-        <v>52.080104160208315</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A33" s="5">
-        <v>60</v>
-      </c>
-      <c r="B33" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C33" s="10">
-        <v>4.8980097960195906E-3</v>
-      </c>
-      <c r="D33">
-        <f t="shared" si="0"/>
-        <v>48.980097960195906</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A34" s="5">
-        <v>60</v>
-      </c>
-      <c r="B34" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C34" s="10">
-        <v>5.4250108500216989E-3</v>
-      </c>
-      <c r="D34">
-        <f t="shared" si="0"/>
-        <v>54.250108500216989</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A35" s="5">
-        <v>60</v>
-      </c>
-      <c r="B35" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C35" s="10">
-        <v>4.8360096720193426E-3</v>
-      </c>
-      <c r="D35">
-        <f t="shared" si="0"/>
-        <v>48.360096720193425</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A36" s="5">
-        <v>60</v>
-      </c>
-      <c r="B36" s="26" t="s">
-        <v>40</v>
-      </c>
-      <c r="C36" s="10">
-        <v>5.5180110360220714E-3</v>
-      </c>
-      <c r="D36">
-        <f t="shared" si="0"/>
-        <v>55.180110360220716</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A37" s="4">
-        <v>0</v>
-      </c>
-      <c r="B37" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="10">
-        <v>0</v>
-      </c>
-      <c r="D37">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="4">
-        <v>0</v>
-      </c>
-      <c r="B38" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C38" s="10">
-        <v>0</v>
-      </c>
-      <c r="D38">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="4">
-        <v>0</v>
-      </c>
-      <c r="B39" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="10">
-        <v>0</v>
-      </c>
-      <c r="D39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A40" s="4">
-        <v>0</v>
-      </c>
-      <c r="B40" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="10">
-        <v>0</v>
-      </c>
-      <c r="D40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A41" s="4">
-        <v>0</v>
-      </c>
-      <c r="B41" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="10">
-        <v>0</v>
-      </c>
-      <c r="D41">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A42" s="5">
-        <v>10</v>
-      </c>
-      <c r="B42" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="10">
-        <v>4.2780085560171106E-3</v>
-      </c>
-      <c r="D42">
-        <f t="shared" si="0"/>
-        <v>42.780085560171109</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A43" s="5">
-        <v>10</v>
-      </c>
-      <c r="B43" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C43" s="10">
-        <v>6.2310124620249237E-3</v>
-      </c>
-      <c r="D43">
-        <f t="shared" si="0"/>
-        <v>62.31012462024924</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A44" s="5">
-        <v>10</v>
-      </c>
-      <c r="B44" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C44" s="10">
-        <v>8.680017360034719E-3</v>
-      </c>
-      <c r="D44">
-        <f t="shared" si="0"/>
-        <v>86.800173600347193</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A45" s="5">
-        <v>10</v>
-      </c>
-      <c r="B45" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C45" s="10">
-        <v>3.937007874015748E-3</v>
-      </c>
-      <c r="D45">
-        <f t="shared" si="0"/>
-        <v>39.370078740157481</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A46" s="5">
-        <v>10</v>
-      </c>
-      <c r="B46" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C46" s="10">
-        <v>5.3630107260214509E-3</v>
-      </c>
-      <c r="D46">
-        <f t="shared" si="0"/>
-        <v>53.630107260214508</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A47" s="5">
-        <v>20</v>
-      </c>
-      <c r="B47" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C47" s="10">
-        <v>5.5180110360220714E-3</v>
-      </c>
-      <c r="D47">
-        <f t="shared" si="0"/>
-        <v>55.180110360220716</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A48" s="5">
-        <v>20</v>
-      </c>
-      <c r="B48" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C48" s="10">
-        <v>8.0600161200322373E-3</v>
-      </c>
-      <c r="D48">
-        <f t="shared" si="0"/>
-        <v>80.600161200322376</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A49" s="5">
-        <v>20</v>
-      </c>
-      <c r="B49" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C49" s="10">
-        <v>9.3310186620373225E-3</v>
-      </c>
-      <c r="D49">
-        <f t="shared" si="0"/>
-        <v>93.31018662037323</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A50" s="5">
-        <v>20</v>
-      </c>
-      <c r="B50" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C50" s="10">
-        <v>4.4640089280178546E-3</v>
-      </c>
-      <c r="D50">
-        <f t="shared" si="0"/>
-        <v>44.640089280178543</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="5">
-        <v>20</v>
-      </c>
-      <c r="B51" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C51" s="10">
-        <v>6.2620125240250481E-3</v>
-      </c>
-      <c r="D51">
-        <f t="shared" si="0"/>
-        <v>62.620125240250481</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="5">
-        <v>30</v>
-      </c>
-      <c r="B52" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C52" s="10">
-        <v>5.4870109740219469E-3</v>
-      </c>
-      <c r="D52">
-        <f t="shared" si="0"/>
-        <v>54.870109740219469</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="5">
-        <v>30</v>
-      </c>
-      <c r="B53" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C53" s="10">
-        <v>8.432016864033727E-3</v>
-      </c>
-      <c r="D53">
-        <f t="shared" si="0"/>
-        <v>84.320168640337272</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="5">
-        <v>30</v>
-      </c>
-      <c r="B54" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C54" s="10">
-        <v>9.3620187240374478E-3</v>
-      </c>
-      <c r="D54">
-        <f t="shared" si="0"/>
-        <v>93.620187240374477</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="5">
-        <v>30</v>
-      </c>
-      <c r="B55" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C55" s="10">
-        <v>4.5260090520181026E-3</v>
-      </c>
-      <c r="D55">
-        <f t="shared" si="0"/>
-        <v>45.260090520181024</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="5">
-        <v>30</v>
-      </c>
-      <c r="B56" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C56" s="10">
-        <v>7.0990141980283965E-3</v>
-      </c>
-      <c r="D56">
-        <f t="shared" si="0"/>
-        <v>70.990141980283965</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="5">
-        <v>40</v>
-      </c>
-      <c r="B57" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C57" s="10">
-        <v>5.9830119660239317E-3</v>
-      </c>
-      <c r="D57">
-        <f t="shared" si="0"/>
-        <v>59.830119660239319</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="5">
-        <v>40</v>
-      </c>
-      <c r="B58" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C58" s="10">
-        <v>8.8970177940355874E-3</v>
-      </c>
-      <c r="D58">
-        <f t="shared" si="0"/>
-        <v>88.970177940355867</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="5">
-        <v>40</v>
-      </c>
-      <c r="B59" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C59" s="10">
-        <v>9.7340194680389357E-3</v>
-      </c>
-      <c r="D59">
-        <f t="shared" si="0"/>
-        <v>97.340194680389359</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A60" s="5">
-        <v>40</v>
-      </c>
-      <c r="B60" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C60" s="10">
-        <v>5.3320106640213274E-3</v>
-      </c>
-      <c r="D60">
-        <f t="shared" si="0"/>
-        <v>53.320106640213275</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A61" s="5">
-        <v>40</v>
-      </c>
-      <c r="B61" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C61" s="10">
-        <v>7.5020150040300054E-3</v>
-      </c>
-      <c r="D61">
-        <f t="shared" si="0"/>
-        <v>75.020150040300052</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A62" s="5">
-        <v>50</v>
-      </c>
-      <c r="B62" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C62" s="10">
-        <v>6.5410130820261645E-3</v>
-      </c>
-      <c r="D62">
-        <f t="shared" si="0"/>
-        <v>65.410130820261642</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A63" s="5">
-        <v>50</v>
-      </c>
-      <c r="B63" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C63" s="10">
-        <v>9.0210180420360834E-3</v>
-      </c>
-      <c r="D63">
-        <f t="shared" si="0"/>
-        <v>90.210180420360828</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A64" s="5">
-        <v>50</v>
-      </c>
-      <c r="B64" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C64" s="10">
-        <v>9.6100192200384398E-3</v>
-      </c>
-      <c r="D64">
-        <f t="shared" si="0"/>
-        <v>96.100192200384399</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A65" s="5">
-        <v>50</v>
-      </c>
-      <c r="B65" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C65" s="10">
-        <v>5.7040114080228153E-3</v>
-      </c>
-      <c r="D65">
-        <f t="shared" si="0"/>
-        <v>57.04011408022815</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A66" s="5">
-        <v>50</v>
-      </c>
-      <c r="B66" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C66" s="10">
-        <v>7.9360158720317413E-3</v>
-      </c>
-      <c r="D66">
-        <f t="shared" si="0"/>
-        <v>79.360158720317415</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A67" s="5">
-        <v>60</v>
-      </c>
-      <c r="B67" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C67" s="10">
-        <v>7.0680141360282694E-3</v>
-      </c>
-      <c r="D67">
-        <f t="shared" ref="D67:D130" si="1">C67 * 10000</f>
-        <v>70.68014136028269</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A68" s="5">
-        <v>60</v>
-      </c>
-      <c r="B68" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C68" s="10">
-        <v>9.0520181040362069E-3</v>
-      </c>
-      <c r="D68">
-        <f t="shared" si="1"/>
-        <v>90.520181040362075</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A69" s="5">
-        <v>60</v>
-      </c>
-      <c r="B69" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C69" s="10">
-        <v>9.9200198400396788E-3</v>
-      </c>
-      <c r="D69">
-        <f t="shared" si="1"/>
-        <v>99.200198400396786</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A70" s="5">
-        <v>60</v>
-      </c>
-      <c r="B70" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C70" s="10">
-        <v>6.0450120900241797E-3</v>
-      </c>
-      <c r="D70">
-        <f t="shared" si="1"/>
-        <v>60.450120900241799</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A71" s="5">
-        <v>60</v>
-      </c>
-      <c r="B71" s="26" t="s">
-        <v>41</v>
-      </c>
-      <c r="C71" s="10">
-        <v>8.4940169880339741E-3</v>
-      </c>
-      <c r="D71">
-        <f t="shared" si="1"/>
-        <v>84.940169880339738</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A72" s="4">
-        <v>0</v>
-      </c>
-      <c r="B72" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C72" s="11">
-        <v>0</v>
-      </c>
-      <c r="D72">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A73" s="4">
-        <v>0</v>
-      </c>
-      <c r="B73" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C73" s="11">
-        <v>0</v>
-      </c>
-      <c r="D73">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A74" s="4">
-        <v>0</v>
-      </c>
-      <c r="B74" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C74" s="11">
-        <v>0</v>
-      </c>
-      <c r="D74">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A75" s="4">
-        <v>0</v>
-      </c>
-      <c r="B75" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C75" s="11">
-        <v>0</v>
-      </c>
-      <c r="D75">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A76" s="4">
-        <v>0</v>
-      </c>
-      <c r="B76" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C76" s="11">
-        <v>0</v>
-      </c>
-      <c r="D76">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A77" s="5">
-        <v>10</v>
-      </c>
-      <c r="B77" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C77" s="11">
-        <v>3.5960071920143836E-3</v>
-      </c>
-      <c r="D77">
-        <f t="shared" si="1"/>
-        <v>35.960071920143832</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A78" s="5">
-        <v>10</v>
-      </c>
-      <c r="B78" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C78" s="11">
-        <v>3.6580073160146316E-3</v>
-      </c>
-      <c r="D78">
-        <f t="shared" si="1"/>
-        <v>36.580073160146313</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A79" s="5">
-        <v>10</v>
-      </c>
-      <c r="B79" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C79" s="11">
-        <v>3.9060078120156235E-3</v>
-      </c>
-      <c r="D79">
-        <f t="shared" si="1"/>
-        <v>39.060078120156234</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A80" s="5">
-        <v>10</v>
-      </c>
-      <c r="B80" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C80" s="11">
-        <v>3.7820075640151276E-3</v>
-      </c>
-      <c r="D80">
-        <f t="shared" si="1"/>
-        <v>37.820075640151273</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A81" s="5">
-        <v>10</v>
-      </c>
-      <c r="B81" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C81" s="11">
-        <v>3.5650071300142596E-3</v>
-      </c>
-      <c r="D81">
-        <f t="shared" si="1"/>
-        <v>35.650071300142599</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A82" s="5">
-        <v>20</v>
-      </c>
-      <c r="B82" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C82" s="11">
-        <v>3.8130076260152516E-3</v>
-      </c>
-      <c r="D82">
-        <f t="shared" si="1"/>
-        <v>38.130076260152514</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A83" s="5">
-        <v>20</v>
-      </c>
-      <c r="B83" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C83" s="11">
-        <v>3.8130076260152516E-3</v>
-      </c>
-      <c r="D83">
-        <f t="shared" si="1"/>
-        <v>38.130076260152514</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A84" s="5">
-        <v>20</v>
-      </c>
-      <c r="B84" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C84" s="11">
-        <v>3.999007998015996E-3</v>
-      </c>
-      <c r="D84">
-        <f t="shared" si="1"/>
-        <v>39.990079980159962</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A85" s="5">
-        <v>20</v>
-      </c>
-      <c r="B85" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C85" s="11">
-        <v>4.1540083080166155E-3</v>
-      </c>
-      <c r="D85">
-        <f t="shared" si="1"/>
-        <v>41.540083080166156</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A86" s="5">
-        <v>20</v>
-      </c>
-      <c r="B86" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C86" s="11">
-        <v>3.9060078120156235E-3</v>
-      </c>
-      <c r="D86">
-        <f t="shared" si="1"/>
-        <v>39.060078120156234</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A87" s="5">
-        <v>30</v>
-      </c>
-      <c r="B87" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C87" s="11">
-        <v>4.061008122016244E-3</v>
-      </c>
-      <c r="D87">
-        <f t="shared" si="1"/>
-        <v>40.610081220162442</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A88" s="5">
-        <v>30</v>
-      </c>
-      <c r="B88" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C88" s="11">
-        <v>4.061008122016244E-3</v>
-      </c>
-      <c r="D88">
-        <f t="shared" si="1"/>
-        <v>40.610081220162442</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A89" s="5">
-        <v>30</v>
-      </c>
-      <c r="B89" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C89" s="11">
-        <v>4.2470084940169879E-3</v>
-      </c>
-      <c r="D89">
-        <f t="shared" si="1"/>
-        <v>42.470084940169876</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A90" s="5">
-        <v>30</v>
-      </c>
-      <c r="B90" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C90" s="11">
-        <v>4.3090086180172359E-3</v>
-      </c>
-      <c r="D90">
-        <f t="shared" si="1"/>
-        <v>43.090086180172356</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A91" s="5">
-        <v>30</v>
-      </c>
-      <c r="B91" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C91" s="11">
-        <v>4.0300080600161195E-3</v>
-      </c>
-      <c r="D91">
-        <f t="shared" si="1"/>
-        <v>40.300080600161195</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A92" s="5">
-        <v>40</v>
-      </c>
-      <c r="B92" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C92" s="11">
-        <v>4.2780085560171124E-3</v>
-      </c>
-      <c r="D92">
-        <f t="shared" si="1"/>
-        <v>42.780085560171123</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A93" s="5">
-        <v>40</v>
-      </c>
-      <c r="B93" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C93" s="11">
-        <v>4.1850083700167399E-3</v>
-      </c>
-      <c r="D93">
-        <f t="shared" si="1"/>
-        <v>41.850083700167403</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A94" s="5">
-        <v>40</v>
-      </c>
-      <c r="B94" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C94" s="11">
-        <v>4.681009362018723E-3</v>
-      </c>
-      <c r="D94">
-        <f t="shared" si="1"/>
-        <v>46.810093620187232</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A95" s="5">
-        <v>40</v>
-      </c>
-      <c r="B95" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C95" s="11">
-        <v>4.4950089900179782E-3</v>
-      </c>
-      <c r="D95">
-        <f t="shared" si="1"/>
-        <v>44.950089900179783</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A96" s="5">
-        <v>40</v>
-      </c>
-      <c r="B96" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C96" s="11">
-        <v>4.2160084320168644E-3</v>
-      </c>
-      <c r="D96">
-        <f t="shared" si="1"/>
-        <v>42.160084320168643</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A97" s="5">
-        <v>50</v>
-      </c>
-      <c r="B97" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C97" s="11">
-        <v>4.4950089900179782E-3</v>
-      </c>
-      <c r="D97">
-        <f t="shared" si="1"/>
-        <v>44.950089900179783</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A98" s="5">
-        <v>50</v>
-      </c>
-      <c r="B98" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C98" s="11">
-        <v>4.4020088040176084E-3</v>
-      </c>
-      <c r="D98">
-        <f t="shared" si="1"/>
-        <v>44.020088040176084</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A99" s="5">
-        <v>50</v>
-      </c>
-      <c r="B99" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C99" s="11">
-        <v>4.4640089280178563E-3</v>
-      </c>
-      <c r="D99">
-        <f t="shared" si="1"/>
-        <v>44.640089280178564</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A100" s="5">
-        <v>50</v>
-      </c>
-      <c r="B100" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C100" s="11">
-        <v>4.4330088660177302E-3</v>
-      </c>
-      <c r="D100">
-        <f t="shared" si="1"/>
-        <v>44.330088660177303</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A101" s="5">
-        <v>50</v>
-      </c>
-      <c r="B101" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C101" s="11">
-        <v>4.1850083700167399E-3</v>
-      </c>
-      <c r="D101">
-        <f t="shared" si="1"/>
-        <v>41.850083700167403</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A102" s="5">
-        <v>60</v>
-      </c>
-      <c r="B102" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C102" s="11">
-        <v>4.2780085560171124E-3</v>
-      </c>
-      <c r="D102">
-        <f t="shared" si="1"/>
-        <v>42.780085560171123</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A103" s="5">
-        <v>60</v>
-      </c>
-      <c r="B103" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C103" s="11">
-        <v>4.5570091140182262E-3</v>
-      </c>
-      <c r="D103">
-        <f t="shared" si="1"/>
-        <v>45.570091140182264</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A104" s="5">
-        <v>60</v>
-      </c>
-      <c r="B104" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C104" s="11">
-        <v>4.681009362018723E-3</v>
-      </c>
-      <c r="D104">
-        <f t="shared" si="1"/>
-        <v>46.810093620187232</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A105" s="5">
-        <v>60</v>
-      </c>
-      <c r="B105" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C105" s="11">
-        <v>4.681009362018723E-3</v>
-      </c>
-      <c r="D105">
-        <f t="shared" si="1"/>
-        <v>46.810093620187232</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A106" s="5">
-        <v>60</v>
-      </c>
-      <c r="B106" s="26" t="s">
-        <v>42</v>
-      </c>
-      <c r="C106" s="11">
-        <v>4.3710087420174822E-3</v>
-      </c>
-      <c r="D106">
-        <f t="shared" si="1"/>
-        <v>43.710087420174823</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A107" s="4">
-        <v>0</v>
-      </c>
-      <c r="B107" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C107" s="11">
-        <v>0</v>
-      </c>
-      <c r="D107">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A108" s="4">
-        <v>0</v>
-      </c>
-      <c r="B108" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C108" s="11">
-        <v>0</v>
-      </c>
-      <c r="D108">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A109" s="4">
-        <v>0</v>
-      </c>
-      <c r="B109" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C109" s="11">
-        <v>0</v>
-      </c>
-      <c r="D109">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A110" s="4">
-        <v>0</v>
-      </c>
-      <c r="B110" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C110" s="11">
-        <v>0</v>
-      </c>
-      <c r="D110">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A111" s="4">
-        <v>0</v>
-      </c>
-      <c r="B111" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C111" s="11">
-        <v>0</v>
-      </c>
-      <c r="D111">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A112" s="5">
-        <v>10</v>
-      </c>
-      <c r="B112" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C112" s="11">
-        <v>4.0920081840163675E-3</v>
-      </c>
-      <c r="D112">
-        <f t="shared" si="1"/>
-        <v>40.920081840163675</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A113" s="5">
-        <v>10</v>
-      </c>
-      <c r="B113" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C113" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D113">
-        <f t="shared" si="1"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A114" s="5">
-        <v>10</v>
-      </c>
-      <c r="B114" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C114" s="11">
-        <v>3.8130076260152516E-3</v>
-      </c>
-      <c r="D114">
-        <f t="shared" si="1"/>
-        <v>38.130076260152514</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A115" s="5">
-        <v>10</v>
-      </c>
-      <c r="B115" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C115" s="11">
-        <v>3.7510075020150036E-3</v>
-      </c>
-      <c r="D115">
-        <f t="shared" si="1"/>
-        <v>37.510075020150033</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A116" s="5">
-        <v>10</v>
-      </c>
-      <c r="B116" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C116" s="11">
-        <v>3.6270072540145076E-3</v>
-      </c>
-      <c r="D116">
-        <f t="shared" si="1"/>
-        <v>36.270072540145073</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A117" s="5">
-        <v>20</v>
-      </c>
-      <c r="B117" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C117" s="11">
-        <v>4.2160084320168626E-3</v>
-      </c>
-      <c r="D117">
-        <f t="shared" si="1"/>
-        <v>42.160084320168629</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A118" s="5">
-        <v>20</v>
-      </c>
-      <c r="B118" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C118" s="11">
-        <v>3.937007874015748E-3</v>
-      </c>
-      <c r="D118">
-        <f t="shared" si="1"/>
-        <v>39.370078740157481</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A119" s="5">
-        <v>20</v>
-      </c>
-      <c r="B119" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C119" s="11">
-        <v>4.2470084940169862E-3</v>
-      </c>
-      <c r="D119">
-        <f t="shared" si="1"/>
-        <v>42.470084940169862</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A120" s="5">
-        <v>20</v>
-      </c>
-      <c r="B120" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C120" s="11">
-        <v>3.9990079980159942E-3</v>
-      </c>
-      <c r="D120">
-        <f t="shared" si="1"/>
-        <v>39.99007998015994</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A121" s="5">
-        <v>20</v>
-      </c>
-      <c r="B121" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C121" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D121">
-        <f t="shared" si="1"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A122" s="5">
-        <v>30</v>
-      </c>
-      <c r="B122" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C122" s="11">
-        <v>4.4640089280178546E-3</v>
-      </c>
-      <c r="D122">
-        <f t="shared" si="1"/>
-        <v>44.640089280178543</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A123" s="5">
-        <v>30</v>
-      </c>
-      <c r="B123" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C123" s="11">
-        <v>3.999007998015996E-3</v>
-      </c>
-      <c r="D123">
-        <f t="shared" si="1"/>
-        <v>39.990079980159962</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A124" s="5">
-        <v>30</v>
-      </c>
-      <c r="B124" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C124" s="11">
-        <v>4.3710087420174822E-3</v>
-      </c>
-      <c r="D124">
-        <f t="shared" si="1"/>
-        <v>43.710087420174823</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A125" s="5">
-        <v>30</v>
-      </c>
-      <c r="B125" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C125" s="11">
-        <v>4.0920081840163658E-3</v>
-      </c>
-      <c r="D125">
-        <f t="shared" si="1"/>
-        <v>40.920081840163661</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A126" s="5">
-        <v>30</v>
-      </c>
-      <c r="B126" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C126" s="11">
-        <v>3.8440076880153756E-3</v>
-      </c>
-      <c r="D126">
-        <f t="shared" si="1"/>
-        <v>38.440076880153754</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A127" s="5">
-        <v>40</v>
-      </c>
-      <c r="B127" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C127" s="11">
-        <v>4.6190092380184742E-3</v>
-      </c>
-      <c r="D127">
-        <f t="shared" si="1"/>
-        <v>46.190092380184744</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A128" s="5">
-        <v>40</v>
-      </c>
-      <c r="B128" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C128" s="11">
-        <v>4.0300080600161195E-3</v>
-      </c>
-      <c r="D128">
-        <f t="shared" si="1"/>
-        <v>40.300080600161195</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A129" s="5">
-        <v>40</v>
-      </c>
-      <c r="B129" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C129" s="11">
-        <v>4.4950089900179782E-3</v>
-      </c>
-      <c r="D129">
-        <f t="shared" si="1"/>
-        <v>44.950089900179783</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A130" s="5">
-        <v>40</v>
-      </c>
-      <c r="B130" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C130" s="11">
-        <v>4.2470084940169862E-3</v>
-      </c>
-      <c r="D130">
-        <f t="shared" si="1"/>
-        <v>42.470084940169862</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A131" s="5">
-        <v>40</v>
-      </c>
-      <c r="B131" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C131" s="11">
-        <v>3.9060078120156235E-3</v>
-      </c>
-      <c r="D131">
-        <f t="shared" ref="D131:D194" si="2">C131 * 10000</f>
-        <v>39.060078120156234</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A132" s="5">
-        <v>50</v>
-      </c>
-      <c r="B132" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C132" s="11">
-        <v>4.8980097960195906E-3</v>
-      </c>
-      <c r="D132">
-        <f t="shared" si="2"/>
-        <v>48.980097960195906</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A133" s="5">
-        <v>50</v>
-      </c>
-      <c r="B133" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C133" s="11">
-        <v>4.4020088040176066E-3</v>
-      </c>
-      <c r="D133">
-        <f t="shared" si="2"/>
-        <v>44.020088040176063</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A134" s="5">
-        <v>50</v>
-      </c>
-      <c r="B134" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C134" s="11">
-        <v>4.681009362018723E-3</v>
-      </c>
-      <c r="D134">
-        <f t="shared" si="2"/>
-        <v>46.810093620187232</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A135" s="5">
-        <v>50</v>
-      </c>
-      <c r="B135" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C135" s="11">
-        <v>4.3090086180172342E-3</v>
-      </c>
-      <c r="D135">
-        <f t="shared" si="2"/>
-        <v>43.090086180172342</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A136" s="5">
-        <v>50</v>
-      </c>
-      <c r="B136" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C136" s="11">
-        <v>4.061008122016244E-3</v>
-      </c>
-      <c r="D136">
-        <f t="shared" si="2"/>
-        <v>40.610081220162442</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A137" s="5">
-        <v>60</v>
-      </c>
-      <c r="B137" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C137" s="11">
-        <v>4.8360096720193426E-3</v>
-      </c>
-      <c r="D137">
-        <f t="shared" si="2"/>
-        <v>48.360096720193425</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A138" s="5">
-        <v>60</v>
-      </c>
-      <c r="B138" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C138" s="11">
-        <v>4.5880091760183506E-3</v>
-      </c>
-      <c r="D138">
-        <f t="shared" si="2"/>
-        <v>45.880091760183504</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A139" s="5">
-        <v>60</v>
-      </c>
-      <c r="B139" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C139" s="11">
-        <v>4.743009486018971E-3</v>
-      </c>
-      <c r="D139">
-        <f t="shared" si="2"/>
-        <v>47.430094860189712</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A140" s="5">
-        <v>60</v>
-      </c>
-      <c r="B140" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C140" s="11">
-        <v>4.3710087420174822E-3</v>
-      </c>
-      <c r="D140">
-        <f t="shared" si="2"/>
-        <v>43.710087420174823</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A141" s="5">
-        <v>60</v>
-      </c>
-      <c r="B141" s="26" t="s">
-        <v>43</v>
-      </c>
-      <c r="C141" s="11">
-        <v>4.0300080600161195E-3</v>
-      </c>
-      <c r="D141">
-        <f t="shared" si="2"/>
-        <v>40.300080600161195</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A142" s="4">
-        <v>0</v>
-      </c>
-      <c r="B142" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C142" s="11">
-        <v>0</v>
-      </c>
-      <c r="D142">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A143" s="4">
-        <v>0</v>
-      </c>
-      <c r="B143" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C143" s="11">
-        <v>0</v>
-      </c>
-      <c r="D143">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A144" s="4">
-        <v>0</v>
-      </c>
-      <c r="B144" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C144" s="11">
-        <v>0</v>
-      </c>
-      <c r="D144">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A145" s="4">
-        <v>0</v>
-      </c>
-      <c r="B145" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C145" s="11">
-        <v>0</v>
-      </c>
-      <c r="D145">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A146" s="4">
-        <v>0</v>
-      </c>
-      <c r="B146" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C146" s="11">
-        <v>0</v>
-      </c>
-      <c r="D146">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A147" s="5">
-        <v>10</v>
-      </c>
-      <c r="B147" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C147" s="11">
-        <v>3.2240064480128952E-3</v>
-      </c>
-      <c r="D147">
-        <f t="shared" si="2"/>
-        <v>32.24006448012895</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A148" s="5">
-        <v>10</v>
-      </c>
-      <c r="B148" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C148" s="11">
-        <v>3.4720069440138876E-3</v>
-      </c>
-      <c r="D148">
-        <f t="shared" si="2"/>
-        <v>34.720069440138879</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A149" s="5">
-        <v>10</v>
-      </c>
-      <c r="B149" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C149" s="11">
-        <v>3.4410068820137632E-3</v>
-      </c>
-      <c r="D149">
-        <f t="shared" si="2"/>
-        <v>34.410068820137631</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A150" s="5">
-        <v>10</v>
-      </c>
-      <c r="B150" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C150" s="11">
-        <v>3.2860065720131432E-3</v>
-      </c>
-      <c r="D150">
-        <f t="shared" si="2"/>
-        <v>32.860065720131431</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A151" s="5">
-        <v>10</v>
-      </c>
-      <c r="B151" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C151" s="11">
-        <v>3.4100068200136392E-3</v>
-      </c>
-      <c r="D151">
-        <f t="shared" si="2"/>
-        <v>34.100068200136391</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A152" s="5">
-        <v>20</v>
-      </c>
-      <c r="B152" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C152" s="11">
-        <v>3.5960071920143836E-3</v>
-      </c>
-      <c r="D152">
-        <f t="shared" si="2"/>
-        <v>35.960071920143832</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A153" s="5">
-        <v>20</v>
-      </c>
-      <c r="B153" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C153" s="11">
-        <v>3.5650071300142596E-3</v>
-      </c>
-      <c r="D153">
-        <f t="shared" si="2"/>
-        <v>35.650071300142599</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A154" s="5">
-        <v>20</v>
-      </c>
-      <c r="B154" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C154" s="11">
-        <v>3.5650071300142596E-3</v>
-      </c>
-      <c r="D154">
-        <f t="shared" si="2"/>
-        <v>35.650071300142599</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A155" s="5">
-        <v>20</v>
-      </c>
-      <c r="B155" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C155" s="11">
-        <v>3.4410068820137632E-3</v>
-      </c>
-      <c r="D155">
-        <f t="shared" si="2"/>
-        <v>34.410068820137631</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A156" s="5">
-        <v>20</v>
-      </c>
-      <c r="B156" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C156" s="11">
-        <v>3.7820075640151276E-3</v>
-      </c>
-      <c r="D156">
-        <f t="shared" si="2"/>
-        <v>37.820075640151273</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A157" s="5">
-        <v>30</v>
-      </c>
-      <c r="B157" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C157" s="11">
-        <v>3.5960071920143836E-3</v>
-      </c>
-      <c r="D157">
-        <f t="shared" si="2"/>
-        <v>35.960071920143832</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A158" s="5">
-        <v>30</v>
-      </c>
-      <c r="B158" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C158" s="11">
-        <v>3.6580073160146316E-3</v>
-      </c>
-      <c r="D158">
-        <f t="shared" si="2"/>
-        <v>36.580073160146313</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A159" s="5">
-        <v>30</v>
-      </c>
-      <c r="B159" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C159" s="11">
-        <v>3.8750077500154996E-3</v>
-      </c>
-      <c r="D159">
-        <f t="shared" si="2"/>
-        <v>38.750077500154994</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A160" s="5">
-        <v>30</v>
-      </c>
-      <c r="B160" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C160" s="11">
-        <v>3.7200074400148796E-3</v>
-      </c>
-      <c r="D160">
-        <f t="shared" si="2"/>
-        <v>37.200074400148793</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A161" s="5">
-        <v>30</v>
-      </c>
-      <c r="B161" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C161" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D161">
-        <f t="shared" si="2"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A162" s="5">
-        <v>40</v>
-      </c>
-      <c r="B162" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C162" s="11">
-        <v>3.8130076260152516E-3</v>
-      </c>
-      <c r="D162">
-        <f t="shared" si="2"/>
-        <v>38.130076260152514</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A163" s="5">
-        <v>40</v>
-      </c>
-      <c r="B163" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C163" s="11">
-        <v>3.9680079360158715E-3</v>
-      </c>
-      <c r="D163">
-        <f t="shared" si="2"/>
-        <v>39.680079360158715</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A164" s="5">
-        <v>40</v>
-      </c>
-      <c r="B164" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C164" s="11">
-        <v>3.999007998015996E-3</v>
-      </c>
-      <c r="D164">
-        <f t="shared" si="2"/>
-        <v>39.990079980159962</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A165" s="5">
-        <v>40</v>
-      </c>
-      <c r="B165" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C165" s="11">
-        <v>3.8440076880153756E-3</v>
-      </c>
-      <c r="D165">
-        <f t="shared" si="2"/>
-        <v>38.440076880153754</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A166" s="5">
-        <v>40</v>
-      </c>
-      <c r="B166" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C166" s="11">
-        <v>3.937007874015748E-3</v>
-      </c>
-      <c r="D166">
-        <f t="shared" si="2"/>
-        <v>39.370078740157481</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A167" s="5">
-        <v>50</v>
-      </c>
-      <c r="B167" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C167" s="11">
-        <v>3.8750077500154996E-3</v>
-      </c>
-      <c r="D167">
-        <f t="shared" si="2"/>
-        <v>38.750077500154994</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A168" s="5">
-        <v>50</v>
-      </c>
-      <c r="B168" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C168" s="11">
-        <v>4.0920081840163675E-3</v>
-      </c>
-      <c r="D168">
-        <f t="shared" si="2"/>
-        <v>40.920081840163675</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A169" s="5">
-        <v>50</v>
-      </c>
-      <c r="B169" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C169" s="11">
-        <v>3.937007874015748E-3</v>
-      </c>
-      <c r="D169">
-        <f t="shared" si="2"/>
-        <v>39.370078740157481</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A170" s="5">
-        <v>50</v>
-      </c>
-      <c r="B170" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C170" s="11">
-        <v>3.937007874015748E-3</v>
-      </c>
-      <c r="D170">
-        <f t="shared" si="2"/>
-        <v>39.370078740157481</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A171" s="5">
-        <v>50</v>
-      </c>
-      <c r="B171" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C171" s="11">
-        <v>4.0300080600161195E-3</v>
-      </c>
-      <c r="D171">
-        <f t="shared" si="2"/>
-        <v>40.300080600161195</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A172" s="5">
-        <v>60</v>
-      </c>
-      <c r="B172" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C172" s="11">
-        <v>3.8130076260152516E-3</v>
-      </c>
-      <c r="D172">
-        <f t="shared" si="2"/>
-        <v>38.130076260152514</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A173" s="5">
-        <v>60</v>
-      </c>
-      <c r="B173" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C173" s="11">
-        <v>4.0920081840163675E-3</v>
-      </c>
-      <c r="D173">
-        <f t="shared" si="2"/>
-        <v>40.920081840163675</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A174" s="5">
-        <v>60</v>
-      </c>
-      <c r="B174" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C174" s="11">
-        <v>3.937007874015748E-3</v>
-      </c>
-      <c r="D174">
-        <f t="shared" si="2"/>
-        <v>39.370078740157481</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A175" s="5">
-        <v>60</v>
-      </c>
-      <c r="B175" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C175" s="11">
-        <v>3.9680079360158715E-3</v>
-      </c>
-      <c r="D175">
-        <f t="shared" si="2"/>
-        <v>39.680079360158715</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A176" s="5">
-        <v>60</v>
-      </c>
-      <c r="B176" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C176" s="11">
-        <v>3.937007874015748E-3</v>
-      </c>
-      <c r="D176">
-        <f t="shared" si="2"/>
-        <v>39.370078740157481</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A177" s="4">
-        <v>0</v>
-      </c>
-      <c r="B177" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C177" s="11">
-        <v>0</v>
-      </c>
-      <c r="D177">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A178" s="4">
-        <v>0</v>
-      </c>
-      <c r="B178" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C178" s="11">
-        <v>0</v>
-      </c>
-      <c r="D178">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A179" s="4">
-        <v>0</v>
-      </c>
-      <c r="B179" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C179" s="11">
-        <v>0</v>
-      </c>
-      <c r="D179">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A180" s="4">
-        <v>0</v>
-      </c>
-      <c r="B180" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C180" s="11">
-        <v>0</v>
-      </c>
-      <c r="D180">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A181" s="4">
-        <v>0</v>
-      </c>
-      <c r="B181" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C181" s="11">
-        <v>0</v>
-      </c>
-      <c r="D181">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A182" s="5">
-        <v>10</v>
-      </c>
-      <c r="B182" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C182" s="11">
-        <v>3.4720069440138876E-3</v>
-      </c>
-      <c r="D182">
-        <f t="shared" si="2"/>
-        <v>34.720069440138879</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A183" s="5">
-        <v>10</v>
-      </c>
-      <c r="B183" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C183" s="11">
-        <v>3.6580073160146316E-3</v>
-      </c>
-      <c r="D183">
-        <f t="shared" si="2"/>
-        <v>36.580073160146313</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A184" s="5">
-        <v>10</v>
-      </c>
-      <c r="B184" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C184" s="11">
-        <v>3.2240064480128952E-3</v>
-      </c>
-      <c r="D184">
-        <f t="shared" si="2"/>
-        <v>32.24006448012895</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A185" s="5">
-        <v>10</v>
-      </c>
-      <c r="B185" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C185" s="11">
-        <v>3.4720069440138876E-3</v>
-      </c>
-      <c r="D185">
-        <f t="shared" si="2"/>
-        <v>34.720069440138879</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A186" s="5">
-        <v>10</v>
-      </c>
-      <c r="B186" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C186" s="11">
-        <v>3.2860065720131432E-3</v>
-      </c>
-      <c r="D186">
-        <f t="shared" si="2"/>
-        <v>32.860065720131431</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A187" s="5">
-        <v>20</v>
-      </c>
-      <c r="B187" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C187" s="11">
-        <v>3.7820075640151276E-3</v>
-      </c>
-      <c r="D187">
-        <f t="shared" si="2"/>
-        <v>37.820075640151273</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A188" s="5">
-        <v>20</v>
-      </c>
-      <c r="B188" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C188" s="11">
-        <v>3.8750077500154996E-3</v>
-      </c>
-      <c r="D188">
-        <f t="shared" si="2"/>
-        <v>38.750077500154994</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A189" s="5">
-        <v>20</v>
-      </c>
-      <c r="B189" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C189" s="11">
-        <v>3.5030070060140116E-3</v>
-      </c>
-      <c r="D189">
-        <f t="shared" si="2"/>
-        <v>35.030070060140119</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A190" s="5">
-        <v>20</v>
-      </c>
-      <c r="B190" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C190" s="11">
-        <v>3.8130076260152516E-3</v>
-      </c>
-      <c r="D190">
-        <f t="shared" si="2"/>
-        <v>38.130076260152514</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A191" s="5">
-        <v>20</v>
-      </c>
-      <c r="B191" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C191" s="11">
-        <v>3.3480066960133912E-3</v>
-      </c>
-      <c r="D191">
-        <f t="shared" si="2"/>
-        <v>33.480066960133911</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A192" s="5">
-        <v>30</v>
-      </c>
-      <c r="B192" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C192" s="11">
-        <v>3.999007998015996E-3</v>
-      </c>
-      <c r="D192">
-        <f t="shared" si="2"/>
-        <v>39.990079980159962</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A193" s="5">
-        <v>30</v>
-      </c>
-      <c r="B193" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C193" s="11">
-        <v>3.8750077500154996E-3</v>
-      </c>
-      <c r="D193">
-        <f t="shared" si="2"/>
-        <v>38.750077500154994</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A194" s="5">
-        <v>30</v>
-      </c>
-      <c r="B194" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C194" s="11">
-        <v>3.3480066960133912E-3</v>
-      </c>
-      <c r="D194">
-        <f t="shared" si="2"/>
-        <v>33.480066960133911</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A195" s="5">
-        <v>30</v>
-      </c>
-      <c r="B195" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C195" s="11">
-        <v>3.8440076880153756E-3</v>
-      </c>
-      <c r="D195">
-        <f t="shared" ref="D195:D258" si="3">C195 * 10000</f>
-        <v>38.440076880153754</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A196" s="5">
-        <v>30</v>
-      </c>
-      <c r="B196" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C196" s="11">
-        <v>3.5650071300142596E-3</v>
-      </c>
-      <c r="D196">
-        <f t="shared" si="3"/>
-        <v>35.650071300142599</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A197" s="5">
-        <v>40</v>
-      </c>
-      <c r="B197" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C197" s="11">
-        <v>4.0920081840163675E-3</v>
-      </c>
-      <c r="D197">
-        <f t="shared" si="3"/>
-        <v>40.920081840163675</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A198" s="5">
-        <v>40</v>
-      </c>
-      <c r="B198" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C198" s="11">
-        <v>4.0610081220162422E-3</v>
-      </c>
-      <c r="D198">
-        <f t="shared" si="3"/>
-        <v>40.610081220162421</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A199" s="5">
-        <v>40</v>
-      </c>
-      <c r="B199" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C199" s="11">
-        <v>3.4720069440138876E-3</v>
-      </c>
-      <c r="D199">
-        <f t="shared" si="3"/>
-        <v>34.720069440138879</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A200" s="5">
-        <v>40</v>
-      </c>
-      <c r="B200" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C200" s="11">
-        <v>3.9680079360158715E-3</v>
-      </c>
-      <c r="D200">
-        <f t="shared" si="3"/>
-        <v>39.680079360158715</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A201" s="5">
-        <v>40</v>
-      </c>
-      <c r="B201" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C201" s="11">
-        <v>3.6580073160146316E-3</v>
-      </c>
-      <c r="D201">
-        <f t="shared" si="3"/>
-        <v>36.580073160146313</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A202" s="5">
-        <v>50</v>
-      </c>
-      <c r="B202" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C202" s="11">
-        <v>4.1540083080166155E-3</v>
-      </c>
-      <c r="D202">
-        <f t="shared" si="3"/>
-        <v>41.540083080166156</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A203" s="5">
-        <v>50</v>
-      </c>
-      <c r="B203" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C203" s="11">
-        <v>4.1850083700167382E-3</v>
-      </c>
-      <c r="D203">
-        <f t="shared" si="3"/>
-        <v>41.850083700167382</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A204" s="5">
-        <v>50</v>
-      </c>
-      <c r="B204" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C204" s="11">
-        <v>3.6270072540145076E-3</v>
-      </c>
-      <c r="D204">
-        <f t="shared" si="3"/>
-        <v>36.270072540145073</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A205" s="5">
-        <v>50</v>
-      </c>
-      <c r="B205" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C205" s="11">
-        <v>4.0920081840163675E-3</v>
-      </c>
-      <c r="D205">
-        <f t="shared" si="3"/>
-        <v>40.920081840163675</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A206" s="5">
-        <v>50</v>
-      </c>
-      <c r="B206" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C206" s="11">
-        <v>3.8130076260152516E-3</v>
-      </c>
-      <c r="D206">
-        <f t="shared" si="3"/>
-        <v>38.130076260152514</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A207" s="5">
-        <v>60</v>
-      </c>
-      <c r="B207" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C207" s="11">
-        <v>4.2160084320168644E-3</v>
-      </c>
-      <c r="D207">
-        <f t="shared" si="3"/>
-        <v>42.160084320168643</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A208" s="5">
-        <v>60</v>
-      </c>
-      <c r="B208" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C208" s="11">
-        <v>4.1850083700167382E-3</v>
-      </c>
-      <c r="D208">
-        <f t="shared" si="3"/>
-        <v>41.850083700167382</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A209" s="5">
-        <v>60</v>
-      </c>
-      <c r="B209" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C209" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D209">
-        <f t="shared" si="3"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A210" s="5">
-        <v>60</v>
-      </c>
-      <c r="B210" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C210" s="11">
-        <v>4.1540083080166155E-3</v>
-      </c>
-      <c r="D210">
-        <f t="shared" si="3"/>
-        <v>41.540083080166156</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A211" s="5">
-        <v>60</v>
-      </c>
-      <c r="B211" s="26" t="s">
-        <v>44</v>
-      </c>
-      <c r="C211" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D211">
-        <f t="shared" si="3"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A212" s="4">
-        <v>0</v>
-      </c>
-      <c r="B212" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C212" s="11">
-        <v>0</v>
-      </c>
-      <c r="D212">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A213" s="4">
-        <v>0</v>
-      </c>
-      <c r="B213" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C213" s="11">
-        <v>0</v>
-      </c>
-      <c r="D213">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A214" s="4">
-        <v>0</v>
-      </c>
-      <c r="B214" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C214" s="11">
-        <v>0</v>
-      </c>
-      <c r="D214">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A215" s="4">
-        <v>0</v>
-      </c>
-      <c r="B215" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C215" s="11">
-        <v>0</v>
-      </c>
-      <c r="D215">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A216" s="4">
-        <v>0</v>
-      </c>
-      <c r="B216" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C216" s="11">
-        <v>0</v>
-      </c>
-      <c r="D216">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A217" s="5">
-        <v>10</v>
-      </c>
-      <c r="B217" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C217" s="11">
-        <v>3.2240064480128952E-3</v>
-      </c>
-      <c r="D217">
-        <f t="shared" si="3"/>
-        <v>32.24006448012895</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A218" s="5">
-        <v>10</v>
-      </c>
-      <c r="B218" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C218" s="11">
-        <v>3.3790067580135152E-3</v>
-      </c>
-      <c r="D218">
-        <f t="shared" si="3"/>
-        <v>33.790067580135151</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A219" s="5">
-        <v>10</v>
-      </c>
-      <c r="B219" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C219" s="11">
-        <v>3.2550065100130192E-3</v>
-      </c>
-      <c r="D219">
-        <f t="shared" si="3"/>
-        <v>32.55006510013019</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A220" s="5">
-        <v>10</v>
-      </c>
-      <c r="B220" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C220" s="11">
-        <v>3.5340070680141356E-3</v>
-      </c>
-      <c r="D220">
-        <f t="shared" si="3"/>
-        <v>35.340070680141359</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A221" s="5">
-        <v>10</v>
-      </c>
-      <c r="B221" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C221" s="11">
-        <v>3.5340070680141356E-3</v>
-      </c>
-      <c r="D221">
-        <f t="shared" si="3"/>
-        <v>35.340070680141359</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A222" s="5">
-        <v>20</v>
-      </c>
-      <c r="B222" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C222" s="11">
-        <v>3.4720069440138876E-3</v>
-      </c>
-      <c r="D222">
-        <f t="shared" si="3"/>
-        <v>34.720069440138879</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A223" s="5">
-        <v>20</v>
-      </c>
-      <c r="B223" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C223" s="11">
-        <v>3.5650071300142596E-3</v>
-      </c>
-      <c r="D223">
-        <f t="shared" si="3"/>
-        <v>35.650071300142599</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A224" s="5">
-        <v>20</v>
-      </c>
-      <c r="B224" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C224" s="11">
-        <v>3.5340070680141356E-3</v>
-      </c>
-      <c r="D224">
-        <f t="shared" si="3"/>
-        <v>35.340070680141359</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A225" s="5">
-        <v>20</v>
-      </c>
-      <c r="B225" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C225" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D225">
-        <f t="shared" si="3"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A226" s="5">
-        <v>20</v>
-      </c>
-      <c r="B226" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C226" s="11">
-        <v>3.7510075020150036E-3</v>
-      </c>
-      <c r="D226">
-        <f t="shared" si="3"/>
-        <v>37.510075020150033</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A227" s="5">
-        <v>30</v>
-      </c>
-      <c r="B227" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C227" s="11">
-        <v>3.7510075020150036E-3</v>
-      </c>
-      <c r="D227">
-        <f t="shared" si="3"/>
-        <v>37.510075020150033</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A228" s="5">
-        <v>30</v>
-      </c>
-      <c r="B228" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C228" s="11">
-        <v>3.7200074400148796E-3</v>
-      </c>
-      <c r="D228">
-        <f t="shared" si="3"/>
-        <v>37.200074400148793</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A229" s="5">
-        <v>30</v>
-      </c>
-      <c r="B229" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C229" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D229">
-        <f t="shared" si="3"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A230" s="5">
-        <v>30</v>
-      </c>
-      <c r="B230" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C230" s="11">
-        <v>3.8130076260152516E-3</v>
-      </c>
-      <c r="D230">
-        <f t="shared" si="3"/>
-        <v>38.130076260152514</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A231" s="5">
-        <v>30</v>
-      </c>
-      <c r="B231" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C231" s="11">
-        <v>3.7820075640151276E-3</v>
-      </c>
-      <c r="D231">
-        <f t="shared" si="3"/>
-        <v>37.820075640151273</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A232" s="5">
-        <v>40</v>
-      </c>
-      <c r="B232" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C232" s="11">
-        <v>3.7820075640151276E-3</v>
-      </c>
-      <c r="D232">
-        <f t="shared" si="3"/>
-        <v>37.820075640151273</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A233" s="5">
-        <v>40</v>
-      </c>
-      <c r="B233" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C233" s="11">
-        <v>3.7820075640151276E-3</v>
-      </c>
-      <c r="D233">
-        <f t="shared" si="3"/>
-        <v>37.820075640151273</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A234" s="5">
-        <v>40</v>
-      </c>
-      <c r="B234" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C234" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D234">
-        <f t="shared" si="3"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A235" s="5">
-        <v>40</v>
-      </c>
-      <c r="B235" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C235" s="11">
-        <v>3.9680079360158715E-3</v>
-      </c>
-      <c r="D235">
-        <f t="shared" si="3"/>
-        <v>39.680079360158715</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A236" s="5">
-        <v>40</v>
-      </c>
-      <c r="B236" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C236" s="11">
-        <v>3.8130076260152516E-3</v>
-      </c>
-      <c r="D236">
-        <f t="shared" si="3"/>
-        <v>38.130076260152514</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A237" s="5">
-        <v>50</v>
-      </c>
-      <c r="B237" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C237" s="11">
-        <v>3.9060078120156235E-3</v>
-      </c>
-      <c r="D237">
-        <f t="shared" si="3"/>
-        <v>39.060078120156234</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A238" s="5">
-        <v>50</v>
-      </c>
-      <c r="B238" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C238" s="11">
-        <v>3.937007874015748E-3</v>
-      </c>
-      <c r="D238">
-        <f t="shared" si="3"/>
-        <v>39.370078740157481</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A239" s="5">
-        <v>50</v>
-      </c>
-      <c r="B239" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C239" s="11">
-        <v>3.6270072540145076E-3</v>
-      </c>
-      <c r="D239">
-        <f t="shared" si="3"/>
-        <v>36.270072540145073</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A240" s="5">
-        <v>50</v>
-      </c>
-      <c r="B240" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C240" s="11">
-        <v>3.9680079360158715E-3</v>
-      </c>
-      <c r="D240">
-        <f t="shared" si="3"/>
-        <v>39.680079360158715</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A241" s="5">
-        <v>50</v>
-      </c>
-      <c r="B241" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C241" s="11">
-        <v>3.9060078120156235E-3</v>
-      </c>
-      <c r="D241">
-        <f t="shared" si="3"/>
-        <v>39.060078120156234</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A242" s="5">
-        <v>60</v>
-      </c>
-      <c r="B242" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C242" s="11">
-        <v>3.9680079360158715E-3</v>
-      </c>
-      <c r="D242">
-        <f t="shared" si="3"/>
-        <v>39.680079360158715</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A243" s="5">
-        <v>60</v>
-      </c>
-      <c r="B243" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C243" s="11">
-        <v>3.937007874015748E-3</v>
-      </c>
-      <c r="D243">
-        <f t="shared" si="3"/>
-        <v>39.370078740157481</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A244" s="5">
-        <v>60</v>
-      </c>
-      <c r="B244" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C244" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D244">
-        <f t="shared" si="3"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A245" s="5">
-        <v>60</v>
-      </c>
-      <c r="B245" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C245" s="11">
-        <v>3.937007874015748E-3</v>
-      </c>
-      <c r="D245">
-        <f t="shared" si="3"/>
-        <v>39.370078740157481</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A246" s="5">
-        <v>60</v>
-      </c>
-      <c r="B246" s="26" t="s">
-        <v>45</v>
-      </c>
-      <c r="C246" s="11">
-        <v>3.937007874015748E-3</v>
-      </c>
-      <c r="D246">
-        <f t="shared" si="3"/>
-        <v>39.370078740157481</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A247" s="4">
-        <v>0</v>
-      </c>
-      <c r="B247" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C247" s="11">
-        <v>0</v>
-      </c>
-      <c r="D247">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A248" s="4">
-        <v>0</v>
-      </c>
-      <c r="B248" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C248" s="11">
-        <v>0</v>
-      </c>
-      <c r="D248">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A249" s="4">
-        <v>0</v>
-      </c>
-      <c r="B249" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C249" s="11">
-        <v>0</v>
-      </c>
-      <c r="D249">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A250" s="4">
-        <v>0</v>
-      </c>
-      <c r="B250" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C250" s="11">
-        <v>0</v>
-      </c>
-      <c r="D250">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A251" s="4">
-        <v>0</v>
-      </c>
-      <c r="B251" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C251" s="11">
-        <v>0</v>
-      </c>
-      <c r="D251">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A252" s="5">
-        <v>10</v>
-      </c>
-      <c r="B252" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C252" s="11">
-        <v>2.9140058280116565E-3</v>
-      </c>
-      <c r="D252">
-        <f t="shared" si="3"/>
-        <v>29.140058280116566</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A253" s="5">
-        <v>10</v>
-      </c>
-      <c r="B253" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C253" s="11">
-        <v>2.6040052080104148E-3</v>
-      </c>
-      <c r="D253">
-        <f t="shared" si="3"/>
-        <v>26.040052080104147</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A254" s="5">
-        <v>10</v>
-      </c>
-      <c r="B254" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C254" s="11">
-        <v>2.9140058280116548E-3</v>
-      </c>
-      <c r="D254">
-        <f t="shared" si="3"/>
-        <v>29.140058280116548</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A255" s="5">
-        <v>10</v>
-      </c>
-      <c r="B255" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C255" s="11">
-        <v>3.1310062620125249E-3</v>
-      </c>
-      <c r="D255">
-        <f t="shared" si="3"/>
-        <v>31.310062620125251</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A256" s="5">
-        <v>10</v>
-      </c>
-      <c r="B256" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C256" s="11">
-        <v>2.9760059520119028E-3</v>
-      </c>
-      <c r="D256">
-        <f t="shared" si="3"/>
-        <v>29.760059520119029</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A257" s="5">
-        <v>20</v>
-      </c>
-      <c r="B257" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C257" s="11">
-        <v>3.5960071920143853E-3</v>
-      </c>
-      <c r="D257">
-        <f t="shared" si="3"/>
-        <v>35.960071920143854</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A258" s="5">
-        <v>20</v>
-      </c>
-      <c r="B258" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C258" s="11">
-        <v>3.5650071300142596E-3</v>
-      </c>
-      <c r="D258">
-        <f t="shared" si="3"/>
-        <v>35.650071300142599</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A259" s="5">
-        <v>20</v>
-      </c>
-      <c r="B259" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C259" s="11">
-        <v>3.6580073160146316E-3</v>
-      </c>
-      <c r="D259">
-        <f t="shared" ref="D259:D322" si="4">C259 * 10000</f>
-        <v>36.580073160146313</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A260" s="5">
-        <v>20</v>
-      </c>
-      <c r="B260" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C260" s="11">
-        <v>3.7510075020150053E-3</v>
-      </c>
-      <c r="D260">
-        <f t="shared" si="4"/>
-        <v>37.510075020150055</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A261" s="5">
-        <v>20</v>
-      </c>
-      <c r="B261" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C261" s="11">
-        <v>4.0920081840163675E-3</v>
-      </c>
-      <c r="D261">
-        <f t="shared" si="4"/>
-        <v>40.920081840163675</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A262" s="5">
-        <v>30</v>
-      </c>
-      <c r="B262" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C262" s="11">
-        <v>3.7820075640151276E-3</v>
-      </c>
-      <c r="D262">
-        <f t="shared" si="4"/>
-        <v>37.820075640151273</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A263" s="5">
-        <v>30</v>
-      </c>
-      <c r="B263" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C263" s="11">
-        <v>3.4100068200136392E-3</v>
-      </c>
-      <c r="D263">
-        <f t="shared" si="4"/>
-        <v>34.100068200136391</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A264" s="5">
-        <v>30</v>
-      </c>
-      <c r="B264" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C264" s="11">
-        <v>3.7510075020150036E-3</v>
-      </c>
-      <c r="D264">
-        <f t="shared" si="4"/>
-        <v>37.510075020150033</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A265" s="5">
-        <v>30</v>
-      </c>
-      <c r="B265" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C265" s="11">
-        <v>3.4720069440138889E-3</v>
-      </c>
-      <c r="D265">
-        <f t="shared" si="4"/>
-        <v>34.720069440138886</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A266" s="5">
-        <v>30</v>
-      </c>
-      <c r="B266" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C266" s="11">
-        <v>4.2160084320168644E-3</v>
-      </c>
-      <c r="D266">
-        <f t="shared" si="4"/>
-        <v>42.160084320168643</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A267" s="5">
-        <v>40</v>
-      </c>
-      <c r="B267" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C267" s="11">
-        <v>4.0300080600161195E-3</v>
-      </c>
-      <c r="D267">
-        <f t="shared" si="4"/>
-        <v>40.300080600161195</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A268" s="5">
-        <v>40</v>
-      </c>
-      <c r="B268" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C268" s="11">
-        <v>3.4410068820137632E-3</v>
-      </c>
-      <c r="D268">
-        <f t="shared" si="4"/>
-        <v>34.410068820137631</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A269" s="5">
-        <v>40</v>
-      </c>
-      <c r="B269" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C269" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D269">
-        <f t="shared" si="4"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A270" s="5">
-        <v>40</v>
-      </c>
-      <c r="B270" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C270" s="11">
-        <v>3.6580073160146333E-3</v>
-      </c>
-      <c r="D270">
-        <f t="shared" si="4"/>
-        <v>36.580073160146334</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A271" s="5">
-        <v>40</v>
-      </c>
-      <c r="B271" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C271" s="11">
-        <v>4.4640089280178546E-3</v>
-      </c>
-      <c r="D271">
-        <f t="shared" si="4"/>
-        <v>44.640089280178543</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A272" s="5">
-        <v>50</v>
-      </c>
-      <c r="B272" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C272" s="11">
-        <v>3.8750077500154996E-3</v>
-      </c>
-      <c r="D272">
-        <f t="shared" si="4"/>
-        <v>38.750077500154994</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A273" s="5">
-        <v>50</v>
-      </c>
-      <c r="B273" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C273" s="11">
-        <v>3.5030070060140116E-3</v>
-      </c>
-      <c r="D273">
-        <f t="shared" si="4"/>
-        <v>35.030070060140119</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A274" s="5">
-        <v>50</v>
-      </c>
-      <c r="B274" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C274" s="11">
-        <v>3.8440076880153756E-3</v>
-      </c>
-      <c r="D274">
-        <f t="shared" si="4"/>
-        <v>38.440076880153754</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A275" s="5">
-        <v>50</v>
-      </c>
-      <c r="B275" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C275" s="11">
-        <v>3.8440076880153773E-3</v>
-      </c>
-      <c r="D275">
-        <f t="shared" si="4"/>
-        <v>38.440076880153775</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A276" s="5">
-        <v>50</v>
-      </c>
-      <c r="B276" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C276" s="11">
-        <v>4.7120094240188466E-3</v>
-      </c>
-      <c r="D276">
-        <f t="shared" si="4"/>
-        <v>47.120094240188465</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A277" s="5">
-        <v>60</v>
-      </c>
-      <c r="B277" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C277" s="11">
-        <v>3.8130076260152516E-3</v>
-      </c>
-      <c r="D277">
-        <f t="shared" si="4"/>
-        <v>38.130076260152514</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A278" s="5">
-        <v>60</v>
-      </c>
-      <c r="B278" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C278" s="11">
-        <v>3.5030070060140116E-3</v>
-      </c>
-      <c r="D278">
-        <f t="shared" si="4"/>
-        <v>35.030070060140119</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A279" s="5">
-        <v>60</v>
-      </c>
-      <c r="B279" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C279" s="11">
-        <v>4.061008122016244E-3</v>
-      </c>
-      <c r="D279">
-        <f t="shared" si="4"/>
-        <v>40.610081220162442</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A280" s="5">
-        <v>60</v>
-      </c>
-      <c r="B280" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C280" s="11">
-        <v>4.0920081840163675E-3</v>
-      </c>
-      <c r="D280">
-        <f t="shared" si="4"/>
-        <v>40.920081840163675</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A281" s="5">
-        <v>60</v>
-      </c>
-      <c r="B281" s="26" t="s">
-        <v>46</v>
-      </c>
-      <c r="C281" s="11">
-        <v>4.7120094240188466E-3</v>
-      </c>
-      <c r="D281">
-        <f t="shared" si="4"/>
-        <v>47.120094240188465</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A282" s="4">
-        <v>0</v>
-      </c>
-      <c r="B282" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C282" s="11">
-        <v>0</v>
-      </c>
-      <c r="D282">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A283" s="4">
-        <v>0</v>
-      </c>
-      <c r="B283" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C283" s="11">
-        <v>0</v>
-      </c>
-      <c r="D283">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A284" s="4">
-        <v>0</v>
-      </c>
-      <c r="B284" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C284" s="11">
-        <v>0</v>
-      </c>
-      <c r="D284">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A285" s="4">
-        <v>0</v>
-      </c>
-      <c r="B285" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C285" s="11">
-        <v>0</v>
-      </c>
-      <c r="D285">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A286" s="4">
-        <v>0</v>
-      </c>
-      <c r="B286" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C286" s="11">
-        <v>0</v>
-      </c>
-      <c r="D286">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A287" s="5">
-        <v>10</v>
-      </c>
-      <c r="B287" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C287" s="11">
-        <v>2.8830057660115308E-3</v>
-      </c>
-      <c r="D287">
-        <f t="shared" si="4"/>
-        <v>28.830057660115308</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A288" s="5">
-        <v>10</v>
-      </c>
-      <c r="B288" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C288" s="11">
-        <v>2.6350052700105406E-3</v>
-      </c>
-      <c r="D288">
-        <f t="shared" si="4"/>
-        <v>26.350052700105405</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A289" s="5">
-        <v>10</v>
-      </c>
-      <c r="B289" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C289" s="11">
-        <v>2.6660053320106628E-3</v>
-      </c>
-      <c r="D289">
-        <f t="shared" si="4"/>
-        <v>26.660053320106627</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A290" s="5">
-        <v>10</v>
-      </c>
-      <c r="B290" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C290" s="11">
-        <v>2.8520057040114068E-3</v>
-      </c>
-      <c r="D290">
-        <f t="shared" si="4"/>
-        <v>28.520057040114068</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A291" s="5">
-        <v>10</v>
-      </c>
-      <c r="B291" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C291" s="11">
-        <v>2.8210056420112828E-3</v>
-      </c>
-      <c r="D291">
-        <f t="shared" si="4"/>
-        <v>28.210056420112828</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A292" s="5">
-        <v>20</v>
-      </c>
-      <c r="B292" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C292" s="11">
-        <v>3.0380060760121512E-3</v>
-      </c>
-      <c r="D292">
-        <f t="shared" si="4"/>
-        <v>30.380060760121513</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A293" s="5">
-        <v>20</v>
-      </c>
-      <c r="B293" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C293" s="11">
-        <v>3.5650071300142613E-3</v>
-      </c>
-      <c r="D293">
-        <f t="shared" si="4"/>
-        <v>35.650071300142613</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A294" s="5">
-        <v>20</v>
-      </c>
-      <c r="B294" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C294" s="11">
-        <v>3.2550065100130192E-3</v>
-      </c>
-      <c r="D294">
-        <f t="shared" si="4"/>
-        <v>32.55006510013019</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A295" s="5">
-        <v>20</v>
-      </c>
-      <c r="B295" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C295" s="11">
-        <v>3.1620063240126472E-3</v>
-      </c>
-      <c r="D295">
-        <f t="shared" si="4"/>
-        <v>31.620063240126473</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A296" s="5">
-        <v>20</v>
-      </c>
-      <c r="B296" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C296" s="11">
-        <v>3.5030070060140116E-3</v>
-      </c>
-      <c r="D296">
-        <f t="shared" si="4"/>
-        <v>35.030070060140119</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A297" s="5">
-        <v>30</v>
-      </c>
-      <c r="B297" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C297" s="11">
-        <v>3.3170066340132672E-3</v>
-      </c>
-      <c r="D297">
-        <f t="shared" si="4"/>
-        <v>33.170066340132671</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A298" s="5">
-        <v>30</v>
-      </c>
-      <c r="B298" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C298" s="11">
-        <v>3.5960071920143853E-3</v>
-      </c>
-      <c r="D298">
-        <f t="shared" si="4"/>
-        <v>35.960071920143854</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A299" s="5">
-        <v>30</v>
-      </c>
-      <c r="B299" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C299" s="11">
-        <v>3.5650071300142596E-3</v>
-      </c>
-      <c r="D299">
-        <f t="shared" si="4"/>
-        <v>35.650071300142599</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A300" s="5">
-        <v>30</v>
-      </c>
-      <c r="B300" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C300" s="11">
-        <v>3.4410068820137632E-3</v>
-      </c>
-      <c r="D300">
-        <f t="shared" si="4"/>
-        <v>34.410068820137631</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A301" s="5">
-        <v>30</v>
-      </c>
-      <c r="B301" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C301" s="11">
-        <v>3.8130076260152516E-3</v>
-      </c>
-      <c r="D301">
-        <f t="shared" si="4"/>
-        <v>38.130076260152514</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A302" s="5">
-        <v>40</v>
-      </c>
-      <c r="B302" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C302" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D302">
-        <f t="shared" si="4"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A303" s="5">
-        <v>40</v>
-      </c>
-      <c r="B303" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C303" s="11">
-        <v>3.937007874015748E-3</v>
-      </c>
-      <c r="D303">
-        <f t="shared" si="4"/>
-        <v>39.370078740157481</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A304" s="5">
-        <v>40</v>
-      </c>
-      <c r="B304" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C304" s="11">
-        <v>3.7200074400148796E-3</v>
-      </c>
-      <c r="D304">
-        <f t="shared" si="4"/>
-        <v>37.200074400148793</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A305" s="5">
-        <v>40</v>
-      </c>
-      <c r="B305" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C305" s="11">
-        <v>3.6580073160146316E-3</v>
-      </c>
-      <c r="D305">
-        <f t="shared" si="4"/>
-        <v>36.580073160146313</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A306" s="5">
-        <v>40</v>
-      </c>
-      <c r="B306" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C306" s="11">
-        <v>3.6580073160146316E-3</v>
-      </c>
-      <c r="D306">
-        <f t="shared" si="4"/>
-        <v>36.580073160146313</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A307" s="5">
-        <v>50</v>
-      </c>
-      <c r="B307" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C307" s="11">
-        <v>3.6580073160146316E-3</v>
-      </c>
-      <c r="D307">
-        <f t="shared" si="4"/>
-        <v>36.580073160146313</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A308" s="5">
-        <v>50</v>
-      </c>
-      <c r="B308" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C308" s="11">
-        <v>3.8750077500154996E-3</v>
-      </c>
-      <c r="D308">
-        <f t="shared" si="4"/>
-        <v>38.750077500154994</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A309" s="5">
-        <v>50</v>
-      </c>
-      <c r="B309" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C309" s="11">
-        <v>3.5650071300142596E-3</v>
-      </c>
-      <c r="D309">
-        <f t="shared" si="4"/>
-        <v>35.650071300142599</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A310" s="5">
-        <v>50</v>
-      </c>
-      <c r="B310" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C310" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D310">
-        <f t="shared" si="4"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A311" s="5">
-        <v>50</v>
-      </c>
-      <c r="B311" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C311" s="11">
-        <v>3.8440076880153756E-3</v>
-      </c>
-      <c r="D311">
-        <f t="shared" si="4"/>
-        <v>38.440076880153754</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A312" s="5">
-        <v>60</v>
-      </c>
-      <c r="B312" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C312" s="11">
-        <v>3.6270072540145076E-3</v>
-      </c>
-      <c r="D312">
-        <f t="shared" si="4"/>
-        <v>36.270072540145073</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A313" s="5">
-        <v>60</v>
-      </c>
-      <c r="B313" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C313" s="11">
-        <v>3.937007874015748E-3</v>
-      </c>
-      <c r="D313">
-        <f t="shared" si="4"/>
-        <v>39.370078740157481</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A314" s="5">
-        <v>60</v>
-      </c>
-      <c r="B314" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C314" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D314">
-        <f t="shared" si="4"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="315" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A315" s="5">
-        <v>60</v>
-      </c>
-      <c r="B315" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C315" s="11">
-        <v>3.7820075640151276E-3</v>
-      </c>
-      <c r="D315">
-        <f t="shared" si="4"/>
-        <v>37.820075640151273</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A316" s="5">
-        <v>60</v>
-      </c>
-      <c r="B316" s="26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C316" s="11">
-        <v>3.9060078120156218E-3</v>
-      </c>
-      <c r="D316">
-        <f t="shared" si="4"/>
-        <v>39.06007812015622</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A317" s="4">
-        <v>0</v>
-      </c>
-      <c r="B317" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C317" s="11">
-        <v>0</v>
-      </c>
-      <c r="D317">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A318" s="4">
-        <v>0</v>
-      </c>
-      <c r="B318" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C318" s="11">
-        <v>0</v>
-      </c>
-      <c r="D318">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A319" s="4">
-        <v>0</v>
-      </c>
-      <c r="B319" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C319" s="11">
-        <v>0</v>
-      </c>
-      <c r="D319">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A320" s="4">
-        <v>0</v>
-      </c>
-      <c r="B320" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C320" s="11">
-        <v>0</v>
-      </c>
-      <c r="D320">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A321" s="4">
-        <v>0</v>
-      </c>
-      <c r="B321" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C321" s="11">
-        <v>0</v>
-      </c>
-      <c r="D321">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A322" s="5">
-        <v>10</v>
-      </c>
-      <c r="B322" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C322" s="11">
-        <v>2.5420050840101681E-3</v>
-      </c>
-      <c r="D322">
-        <f t="shared" si="4"/>
-        <v>25.42005084010168</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A323" s="5">
-        <v>10</v>
-      </c>
-      <c r="B323" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C323" s="11">
-        <v>2.7280054560109126E-3</v>
-      </c>
-      <c r="D323">
-        <f t="shared" ref="D323:D386" si="5">C323 * 10000</f>
-        <v>27.280054560109125</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A324" s="5">
-        <v>10</v>
-      </c>
-      <c r="B324" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C324" s="11">
-        <v>2.6040052080104166E-3</v>
-      </c>
-      <c r="D324">
-        <f t="shared" si="5"/>
-        <v>26.040052080104164</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A325" s="5">
-        <v>10</v>
-      </c>
-      <c r="B325" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C325" s="11">
-        <v>2.5420050840101681E-3</v>
-      </c>
-      <c r="D325">
-        <f t="shared" si="5"/>
-        <v>25.42005084010168</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A326" s="5">
-        <v>10</v>
-      </c>
-      <c r="B326" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C326" s="11">
-        <v>2.6660053320106646E-3</v>
-      </c>
-      <c r="D326">
-        <f t="shared" si="5"/>
-        <v>26.660053320106645</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A327" s="5">
-        <v>20</v>
-      </c>
-      <c r="B327" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C327" s="11">
-        <v>3.2550065100130209E-3</v>
-      </c>
-      <c r="D327">
-        <f t="shared" si="5"/>
-        <v>32.550065100130212</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A328" s="5">
-        <v>20</v>
-      </c>
-      <c r="B328" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C328" s="11">
-        <v>3.1930063860127729E-3</v>
-      </c>
-      <c r="D328">
-        <f t="shared" si="5"/>
-        <v>31.930063860127728</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A329" s="5">
-        <v>20</v>
-      </c>
-      <c r="B329" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C329" s="11">
-        <v>3.1310062620125249E-3</v>
-      </c>
-      <c r="D329">
-        <f t="shared" si="5"/>
-        <v>31.310062620125251</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A330" s="5">
-        <v>20</v>
-      </c>
-      <c r="B330" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C330" s="11">
-        <v>2.7900055800111605E-3</v>
-      </c>
-      <c r="D330">
-        <f t="shared" si="5"/>
-        <v>27.900055800111605</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A331" s="5">
-        <v>20</v>
-      </c>
-      <c r="B331" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C331" s="11">
-        <v>3.1620063240126472E-3</v>
-      </c>
-      <c r="D331">
-        <f t="shared" si="5"/>
-        <v>31.620063240126473</v>
-      </c>
-    </row>
-    <row r="332" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A332" s="5">
-        <v>30</v>
-      </c>
-      <c r="B332" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C332" s="11">
-        <v>3.5340070680141356E-3</v>
-      </c>
-      <c r="D332">
-        <f t="shared" si="5"/>
-        <v>35.340070680141359</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A333" s="5">
-        <v>30</v>
-      </c>
-      <c r="B333" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C333" s="11">
-        <v>3.2860065720131449E-3</v>
-      </c>
-      <c r="D333">
-        <f t="shared" si="5"/>
-        <v>32.860065720131452</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A334" s="5">
-        <v>30</v>
-      </c>
-      <c r="B334" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C334" s="11">
-        <v>3.0070060140120285E-3</v>
-      </c>
-      <c r="D334">
-        <f t="shared" si="5"/>
-        <v>30.070060140120287</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A335" s="5">
-        <v>30</v>
-      </c>
-      <c r="B335" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C335" s="11">
-        <v>2.8830057660115325E-3</v>
-      </c>
-      <c r="D335">
-        <f t="shared" si="5"/>
-        <v>28.830057660115326</v>
-      </c>
-    </row>
-    <row r="336" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A336" s="5">
-        <v>30</v>
-      </c>
-      <c r="B336" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C336" s="11">
-        <v>3.0380060760121529E-3</v>
-      </c>
-      <c r="D336">
-        <f t="shared" si="5"/>
-        <v>30.38006076012153</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A337" s="5">
-        <v>40</v>
-      </c>
-      <c r="B337" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C337" s="11">
-        <v>3.3480066960133912E-3</v>
-      </c>
-      <c r="D337">
-        <f t="shared" si="5"/>
-        <v>33.480066960133911</v>
-      </c>
-    </row>
-    <row r="338" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A338" s="5">
-        <v>40</v>
-      </c>
-      <c r="B338" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C338" s="11">
-        <v>3.1000062000124009E-3</v>
-      </c>
-      <c r="D338">
-        <f t="shared" si="5"/>
-        <v>31.000062000124011</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A339" s="5">
-        <v>40</v>
-      </c>
-      <c r="B339" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C339" s="11">
-        <v>3.1620063240126489E-3</v>
-      </c>
-      <c r="D339">
-        <f t="shared" si="5"/>
-        <v>31.620063240126488</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A340" s="5">
-        <v>40</v>
-      </c>
-      <c r="B340" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C340" s="11">
-        <v>3.1310062620125249E-3</v>
-      </c>
-      <c r="D340">
-        <f t="shared" si="5"/>
-        <v>31.310062620125251</v>
-      </c>
-    </row>
-    <row r="341" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A341" s="5">
-        <v>40</v>
-      </c>
-      <c r="B341" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C341" s="11">
-        <v>3.2860065720131432E-3</v>
-      </c>
-      <c r="D341">
-        <f t="shared" si="5"/>
-        <v>32.860065720131431</v>
-      </c>
-    </row>
-    <row r="342" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A342" s="5">
-        <v>50</v>
-      </c>
-      <c r="B342" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C342" s="11">
-        <v>3.5340070680141356E-3</v>
-      </c>
-      <c r="D342">
-        <f t="shared" si="5"/>
-        <v>35.340070680141359</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A343" s="5">
-        <v>50</v>
-      </c>
-      <c r="B343" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C343" s="11">
-        <v>3.1000062000124009E-3</v>
-      </c>
-      <c r="D343">
-        <f t="shared" si="5"/>
-        <v>31.000062000124011</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A344" s="5">
-        <v>50</v>
-      </c>
-      <c r="B344" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C344" s="11">
-        <v>3.0690061380122769E-3</v>
-      </c>
-      <c r="D344">
-        <f t="shared" si="5"/>
-        <v>30.690061380122771</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A345" s="5">
-        <v>50</v>
-      </c>
-      <c r="B345" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C345" s="11">
-        <v>3.2860065720131449E-3</v>
-      </c>
-      <c r="D345">
-        <f t="shared" si="5"/>
-        <v>32.860065720131452</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A346" s="5">
-        <v>50</v>
-      </c>
-      <c r="B346" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C346" s="11">
-        <v>3.1000062000124009E-3</v>
-      </c>
-      <c r="D346">
-        <f t="shared" si="5"/>
-        <v>31.000062000124011</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A347" s="5">
-        <v>60</v>
-      </c>
-      <c r="B347" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C347" s="11">
-        <v>3.5030070060140116E-3</v>
-      </c>
-      <c r="D347">
-        <f t="shared" si="5"/>
-        <v>35.030070060140119</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A348" s="5">
-        <v>60</v>
-      </c>
-      <c r="B348" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C348" s="11">
-        <v>3.1620063240126489E-3</v>
-      </c>
-      <c r="D348">
-        <f t="shared" si="5"/>
-        <v>31.620063240126488</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A349" s="5">
-        <v>60</v>
-      </c>
-      <c r="B349" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C349" s="11">
-        <v>3.1620063240126489E-3</v>
-      </c>
-      <c r="D349">
-        <f t="shared" si="5"/>
-        <v>31.620063240126488</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A350" s="5">
-        <v>60</v>
-      </c>
-      <c r="B350" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C350" s="11">
-        <v>3.1620063240126489E-3</v>
-      </c>
-      <c r="D350">
-        <f t="shared" si="5"/>
-        <v>31.620063240126488</v>
-      </c>
-    </row>
-    <row r="351" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A351" s="5">
-        <v>60</v>
-      </c>
-      <c r="B351" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C351" s="11">
-        <v>3.2860065720131432E-3</v>
-      </c>
-      <c r="D351">
-        <f t="shared" si="5"/>
-        <v>32.860065720131431</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A352" s="4">
-        <v>0</v>
-      </c>
-      <c r="B352" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C352" s="11">
-        <v>0</v>
-      </c>
-      <c r="D352">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A353" s="4">
-        <v>0</v>
-      </c>
-      <c r="B353" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C353" s="11">
-        <v>0</v>
-      </c>
-      <c r="D353">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A354" s="4">
-        <v>0</v>
-      </c>
-      <c r="B354" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C354" s="11">
-        <v>0</v>
-      </c>
-      <c r="D354">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A355" s="4">
-        <v>0</v>
-      </c>
-      <c r="B355" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C355" s="11">
-        <v>0</v>
-      </c>
-      <c r="D355">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A356" s="4">
-        <v>0</v>
-      </c>
-      <c r="B356" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C356" s="11">
-        <v>0</v>
-      </c>
-      <c r="D356">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A357" s="5">
-        <v>10</v>
-      </c>
-      <c r="B357" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C357" s="11">
-        <v>1.9530039060078118E-3</v>
-      </c>
-      <c r="D357">
-        <f t="shared" si="5"/>
-        <v>19.530039060078117</v>
-      </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A358" s="5">
-        <v>10</v>
-      </c>
-      <c r="B358" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C358" s="11">
-        <v>2.0770041540083078E-3</v>
-      </c>
-      <c r="D358">
-        <f t="shared" si="5"/>
-        <v>20.770041540083078</v>
-      </c>
-    </row>
-    <row r="359" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A359" s="5">
-        <v>10</v>
-      </c>
-      <c r="B359" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C359" s="11">
-        <v>2.2010044020088042E-3</v>
-      </c>
-      <c r="D359">
-        <f t="shared" si="5"/>
-        <v>22.010044020088042</v>
-      </c>
-    </row>
-    <row r="360" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A360" s="5">
-        <v>10</v>
-      </c>
-      <c r="B360" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C360" s="11">
-        <v>2.1700043400086802E-3</v>
-      </c>
-      <c r="D360">
-        <f t="shared" si="5"/>
-        <v>21.700043400086802</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A361" s="5">
-        <v>10</v>
-      </c>
-      <c r="B361" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C361" s="11">
-        <v>2.0460040920081838E-3</v>
-      </c>
-      <c r="D361">
-        <f t="shared" si="5"/>
-        <v>20.460040920081838</v>
-      </c>
-    </row>
-    <row r="362" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A362" s="5">
-        <v>20</v>
-      </c>
-      <c r="B362" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C362" s="11">
-        <v>3.0690061380122752E-3</v>
-      </c>
-      <c r="D362">
-        <f t="shared" si="5"/>
-        <v>30.690061380122753</v>
-      </c>
-    </row>
-    <row r="363" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A363" s="5">
-        <v>20</v>
-      </c>
-      <c r="B363" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C363" s="11">
-        <v>2.9140058280116548E-3</v>
-      </c>
-      <c r="D363">
-        <f t="shared" si="5"/>
-        <v>29.140058280116548</v>
-      </c>
-    </row>
-    <row r="364" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A364" s="5">
-        <v>20</v>
-      </c>
-      <c r="B364" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C364" s="11">
-        <v>3.3170066340132672E-3</v>
-      </c>
-      <c r="D364">
-        <f t="shared" si="5"/>
-        <v>33.170066340132671</v>
-      </c>
-    </row>
-    <row r="365" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A365" s="5">
-        <v>20</v>
-      </c>
-      <c r="B365" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C365" s="11">
-        <v>3.3790067580135152E-3</v>
-      </c>
-      <c r="D365">
-        <f t="shared" si="5"/>
-        <v>33.790067580135151</v>
-      </c>
-    </row>
-    <row r="366" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A366" s="5">
-        <v>20</v>
-      </c>
-      <c r="B366" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C366" s="11">
-        <v>3.2550065100130192E-3</v>
-      </c>
-      <c r="D366">
-        <f t="shared" si="5"/>
-        <v>32.55006510013019</v>
-      </c>
-    </row>
-    <row r="367" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A367" s="5">
-        <v>30</v>
-      </c>
-      <c r="B367" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C367" s="11">
-        <v>3.4410068820137632E-3</v>
-      </c>
-      <c r="D367">
-        <f t="shared" si="5"/>
-        <v>34.410068820137631</v>
-      </c>
-    </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A368" s="5">
-        <v>30</v>
-      </c>
-      <c r="B368" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C368" s="11">
-        <v>3.4410068820137632E-3</v>
-      </c>
-      <c r="D368">
-        <f t="shared" si="5"/>
-        <v>34.410068820137631</v>
-      </c>
-    </row>
-    <row r="369" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A369" s="5">
-        <v>30</v>
-      </c>
-      <c r="B369" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C369" s="11">
-        <v>3.7820075640151276E-3</v>
-      </c>
-      <c r="D369">
-        <f t="shared" si="5"/>
-        <v>37.820075640151273</v>
-      </c>
-    </row>
-    <row r="370" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A370" s="5">
-        <v>30</v>
-      </c>
-      <c r="B370" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C370" s="11">
-        <v>3.7200074400148796E-3</v>
-      </c>
-      <c r="D370">
-        <f t="shared" si="5"/>
-        <v>37.200074400148793</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A371" s="5">
-        <v>30</v>
-      </c>
-      <c r="B371" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C371" s="11">
-        <v>3.5340070680141356E-3</v>
-      </c>
-      <c r="D371">
-        <f t="shared" si="5"/>
-        <v>35.340070680141359</v>
-      </c>
-    </row>
-    <row r="372" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A372" s="5">
-        <v>40</v>
-      </c>
-      <c r="B372" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C372" s="11">
-        <v>3.6270072540145076E-3</v>
-      </c>
-      <c r="D372">
-        <f t="shared" si="5"/>
-        <v>36.270072540145073</v>
-      </c>
-    </row>
-    <row r="373" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A373" s="5">
-        <v>40</v>
-      </c>
-      <c r="B373" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C373" s="11">
-        <v>3.5650071300142596E-3</v>
-      </c>
-      <c r="D373">
-        <f t="shared" si="5"/>
-        <v>35.650071300142599</v>
-      </c>
-    </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A374" s="5">
-        <v>40</v>
-      </c>
-      <c r="B374" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C374" s="11">
-        <v>3.7820075640151276E-3</v>
-      </c>
-      <c r="D374">
-        <f t="shared" si="5"/>
-        <v>37.820075640151273</v>
-      </c>
-    </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A375" s="5">
-        <v>40</v>
-      </c>
-      <c r="B375" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C375" s="11">
-        <v>3.8130076260152516E-3</v>
-      </c>
-      <c r="D375">
-        <f t="shared" si="5"/>
-        <v>38.130076260152514</v>
-      </c>
-    </row>
-    <row r="376" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A376" s="5">
-        <v>40</v>
-      </c>
-      <c r="B376" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C376" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D376">
-        <f t="shared" si="5"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A377" s="5">
-        <v>50</v>
-      </c>
-      <c r="B377" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C377" s="11">
-        <v>3.6580073160146316E-3</v>
-      </c>
-      <c r="D377">
-        <f t="shared" si="5"/>
-        <v>36.580073160146313</v>
-      </c>
-    </row>
-    <row r="378" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A378" s="5">
-        <v>50</v>
-      </c>
-      <c r="B378" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C378" s="11">
-        <v>3.6890073780147556E-3</v>
-      </c>
-      <c r="D378">
-        <f t="shared" si="5"/>
-        <v>36.890073780147553</v>
-      </c>
-    </row>
-    <row r="379" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A379" s="5">
-        <v>50</v>
-      </c>
-      <c r="B379" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C379" s="11">
-        <v>3.9060078120156235E-3</v>
-      </c>
-      <c r="D379">
-        <f t="shared" si="5"/>
-        <v>39.060078120156234</v>
-      </c>
-    </row>
-    <row r="380" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A380" s="5">
-        <v>50</v>
-      </c>
-      <c r="B380" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C380" s="11">
-        <v>3.937007874015748E-3</v>
-      </c>
-      <c r="D380">
-        <f t="shared" si="5"/>
-        <v>39.370078740157481</v>
-      </c>
-    </row>
-    <row r="381" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A381" s="5">
-        <v>50</v>
-      </c>
-      <c r="B381" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C381" s="11">
-        <v>3.7510075020150036E-3</v>
-      </c>
-      <c r="D381">
-        <f t="shared" si="5"/>
-        <v>37.510075020150033</v>
-      </c>
-    </row>
-    <row r="382" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A382" s="5">
-        <v>60</v>
-      </c>
-      <c r="B382" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C382" s="11">
-        <v>3.7820075640151276E-3</v>
-      </c>
-      <c r="D382">
-        <f t="shared" si="5"/>
-        <v>37.820075640151273</v>
-      </c>
-    </row>
-    <row r="383" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A383" s="5">
-        <v>60</v>
-      </c>
-      <c r="B383" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C383" s="11">
-        <v>3.7510075020150036E-3</v>
-      </c>
-      <c r="D383">
-        <f t="shared" si="5"/>
-        <v>37.510075020150033</v>
-      </c>
-    </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A384" s="5">
-        <v>60</v>
-      </c>
-      <c r="B384" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C384" s="11">
-        <v>3.9060078120156235E-3</v>
-      </c>
-      <c r="D384">
-        <f t="shared" si="5"/>
-        <v>39.060078120156234</v>
-      </c>
-    </row>
-    <row r="385" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A385" s="5">
-        <v>60</v>
-      </c>
-      <c r="B385" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C385" s="11">
-        <v>3.8750077500154996E-3</v>
-      </c>
-      <c r="D385">
-        <f t="shared" si="5"/>
-        <v>38.750077500154994</v>
-      </c>
-    </row>
-    <row r="386" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A386" s="5">
-        <v>60</v>
-      </c>
-      <c r="B386" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C386" s="11">
-        <v>3.7510075020150036E-3</v>
-      </c>
-      <c r="D386">
-        <f t="shared" si="5"/>
-        <v>37.510075020150033</v>
-      </c>
-    </row>
-    <row r="387" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A387" s="4">
-        <v>0</v>
-      </c>
-      <c r="B387" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C387" s="11">
-        <v>0</v>
-      </c>
-      <c r="D387">
-        <f t="shared" ref="D387:D421" si="6">C387 * 10000</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="388" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A388" s="4">
-        <v>0</v>
-      </c>
-      <c r="B388" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C388" s="11">
-        <v>0</v>
-      </c>
-      <c r="D388">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="389" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A389" s="4">
-        <v>0</v>
-      </c>
-      <c r="B389" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C389" s="11">
-        <v>0</v>
-      </c>
-      <c r="D389">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="390" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A390" s="4">
-        <v>0</v>
-      </c>
-      <c r="B390" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C390" s="11">
-        <v>0</v>
-      </c>
-      <c r="D390">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="391" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A391" s="4">
-        <v>0</v>
-      </c>
-      <c r="B391" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C391" s="11">
-        <v>0</v>
-      </c>
-      <c r="D391">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="392" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A392" s="5">
-        <v>10</v>
-      </c>
-      <c r="B392" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C392" s="11">
-        <v>2.4180048360096704E-3</v>
-      </c>
-      <c r="D392">
-        <f t="shared" si="6"/>
-        <v>24.180048360096706</v>
-      </c>
-    </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A393" s="5">
-        <v>10</v>
-      </c>
-      <c r="B393" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C393" s="11">
-        <v>2.2940045880091762E-3</v>
-      </c>
-      <c r="D393">
-        <f t="shared" si="6"/>
-        <v>22.940045880091763</v>
-      </c>
-    </row>
-    <row r="394" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A394" s="5">
-        <v>10</v>
-      </c>
-      <c r="B394" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C394" s="11">
-        <v>2.2010044020088042E-3</v>
-      </c>
-      <c r="D394">
-        <f t="shared" si="6"/>
-        <v>22.010044020088042</v>
-      </c>
-    </row>
-    <row r="395" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A395" s="5">
-        <v>10</v>
-      </c>
-      <c r="B395" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C395" s="11">
-        <v>1.7360034720069438E-3</v>
-      </c>
-      <c r="D395">
-        <f t="shared" si="6"/>
-        <v>17.360034720069439</v>
-      </c>
-    </row>
-    <row r="396" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A396" s="5">
-        <v>10</v>
-      </c>
-      <c r="B396" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C396" s="11">
-        <v>1.7050034100068196E-3</v>
-      </c>
-      <c r="D396">
-        <f t="shared" si="6"/>
-        <v>17.050034100068196</v>
-      </c>
-    </row>
-    <row r="397" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A397" s="5">
-        <v>20</v>
-      </c>
-      <c r="B397" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C397" s="11">
-        <v>3.3480066960133912E-3</v>
-      </c>
-      <c r="D397">
-        <f t="shared" si="6"/>
-        <v>33.480066960133911</v>
-      </c>
-    </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A398" s="5">
-        <v>20</v>
-      </c>
-      <c r="B398" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C398" s="11">
-        <v>3.1620063240126472E-3</v>
-      </c>
-      <c r="D398">
-        <f t="shared" si="6"/>
-        <v>31.620063240126473</v>
-      </c>
-    </row>
-    <row r="399" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A399" s="5">
-        <v>20</v>
-      </c>
-      <c r="B399" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C399" s="11">
-        <v>3.2240064480128969E-3</v>
-      </c>
-      <c r="D399">
-        <f t="shared" si="6"/>
-        <v>32.240064480128972</v>
-      </c>
-    </row>
-    <row r="400" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A400" s="5">
-        <v>20</v>
-      </c>
-      <c r="B400" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C400" s="11">
-        <v>2.5110050220100424E-3</v>
-      </c>
-      <c r="D400">
-        <f t="shared" si="6"/>
-        <v>25.110050220100423</v>
-      </c>
-    </row>
-    <row r="401" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A401" s="5">
-        <v>20</v>
-      </c>
-      <c r="B401" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C401" s="11">
-        <v>2.8210056420112828E-3</v>
-      </c>
-      <c r="D401">
-        <f t="shared" si="6"/>
-        <v>28.210056420112828</v>
-      </c>
-    </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A402" s="5">
-        <v>30</v>
-      </c>
-      <c r="B402" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C402" s="11">
-        <v>3.5960071920143836E-3</v>
-      </c>
-      <c r="D402">
-        <f t="shared" si="6"/>
-        <v>35.960071920143832</v>
-      </c>
-    </row>
-    <row r="403" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A403" s="5">
-        <v>30</v>
-      </c>
-      <c r="B403" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C403" s="11">
-        <v>3.5340070680141356E-3</v>
-      </c>
-      <c r="D403">
-        <f t="shared" si="6"/>
-        <v>35.340070680141359</v>
-      </c>
-    </row>
-    <row r="404" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A404" s="5">
-        <v>30</v>
-      </c>
-      <c r="B404" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C404" s="11">
-        <v>3.5650071300142613E-3</v>
-      </c>
-      <c r="D404">
-        <f t="shared" si="6"/>
-        <v>35.650071300142613</v>
-      </c>
-    </row>
-    <row r="405" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A405" s="5">
-        <v>30</v>
-      </c>
-      <c r="B405" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C405" s="11">
-        <v>2.9760059520119028E-3</v>
-      </c>
-      <c r="D405">
-        <f t="shared" si="6"/>
-        <v>29.760059520119029</v>
-      </c>
-    </row>
-    <row r="406" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A406" s="5">
-        <v>30</v>
-      </c>
-      <c r="B406" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C406" s="11">
-        <v>3.0690061380122752E-3</v>
-      </c>
-      <c r="D406">
-        <f t="shared" si="6"/>
-        <v>30.690061380122753</v>
-      </c>
-    </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A407" s="5">
-        <v>40</v>
-      </c>
-      <c r="B407" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C407" s="11">
-        <v>3.8440076880153756E-3</v>
-      </c>
-      <c r="D407">
-        <f t="shared" si="6"/>
-        <v>38.440076880153754</v>
-      </c>
-    </row>
-    <row r="408" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A408" s="5">
-        <v>40</v>
-      </c>
-      <c r="B408" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C408" s="11">
-        <v>3.8130076260152516E-3</v>
-      </c>
-      <c r="D408">
-        <f t="shared" si="6"/>
-        <v>38.130076260152514</v>
-      </c>
-    </row>
-    <row r="409" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A409" s="5">
-        <v>40</v>
-      </c>
-      <c r="B409" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C409" s="11">
-        <v>3.7820075640151293E-3</v>
-      </c>
-      <c r="D409">
-        <f t="shared" si="6"/>
-        <v>37.820075640151295</v>
-      </c>
-    </row>
-    <row r="410" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A410" s="5">
-        <v>40</v>
-      </c>
-      <c r="B410" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C410" s="11">
-        <v>3.1620063240126472E-3</v>
-      </c>
-      <c r="D410">
-        <f t="shared" si="6"/>
-        <v>31.620063240126473</v>
-      </c>
-    </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A411" s="5">
-        <v>40</v>
-      </c>
-      <c r="B411" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C411" s="11">
-        <v>3.3480066960133912E-3</v>
-      </c>
-      <c r="D411">
-        <f t="shared" si="6"/>
-        <v>33.480066960133911</v>
-      </c>
-    </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A412" s="5">
-        <v>50</v>
-      </c>
-      <c r="B412" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C412" s="11">
-        <v>3.9680079360158715E-3</v>
-      </c>
-      <c r="D412">
-        <f t="shared" si="6"/>
-        <v>39.680079360158715</v>
-      </c>
-    </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A413" s="5">
-        <v>50</v>
-      </c>
-      <c r="B413" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C413" s="11">
-        <v>3.7820075640151276E-3</v>
-      </c>
-      <c r="D413">
-        <f t="shared" si="6"/>
-        <v>37.820075640151273</v>
-      </c>
-    </row>
-    <row r="414" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A414" s="5">
-        <v>50</v>
-      </c>
-      <c r="B414" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C414" s="11">
-        <v>3.8750077500155013E-3</v>
-      </c>
-      <c r="D414">
-        <f t="shared" si="6"/>
-        <v>38.750077500155015</v>
-      </c>
-    </row>
-    <row r="415" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A415" s="5">
-        <v>50</v>
-      </c>
-      <c r="B415" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C415" s="11">
-        <v>3.1930063860127712E-3</v>
-      </c>
-      <c r="D415">
-        <f t="shared" si="6"/>
-        <v>31.930063860127714</v>
-      </c>
-    </row>
-    <row r="416" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A416" s="5">
-        <v>50</v>
-      </c>
-      <c r="B416" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C416" s="11">
-        <v>3.3790067580135152E-3</v>
-      </c>
-      <c r="D416">
-        <f t="shared" si="6"/>
-        <v>33.790067580135151</v>
-      </c>
-    </row>
-    <row r="417" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A417" s="5">
-        <v>60</v>
-      </c>
-      <c r="B417" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C417">
-        <v>4.061008122016244E-3</v>
-      </c>
-      <c r="D417">
-        <f t="shared" si="6"/>
-        <v>40.610081220162442</v>
-      </c>
-    </row>
-    <row r="418" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A418" s="5">
-        <v>60</v>
-      </c>
-      <c r="B418" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C418">
-        <v>3.9680079360158715E-3</v>
-      </c>
-      <c r="D418">
-        <f t="shared" si="6"/>
-        <v>39.680079360158715</v>
-      </c>
-    </row>
-    <row r="419" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A419" s="5">
-        <v>60</v>
-      </c>
-      <c r="B419" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C419">
-        <v>3.9680079360158733E-3</v>
-      </c>
-      <c r="D419">
-        <f t="shared" si="6"/>
-        <v>39.680079360158736</v>
-      </c>
-    </row>
-    <row r="420" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A420" s="5">
-        <v>60</v>
-      </c>
-      <c r="B420" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C420">
-        <v>3.3170066340132672E-3</v>
-      </c>
-      <c r="D420">
-        <f t="shared" si="6"/>
-        <v>33.170066340132671</v>
-      </c>
-    </row>
-    <row r="421" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A421" s="5">
-        <v>60</v>
-      </c>
-      <c r="B421" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C421">
-        <v>3.5960071920143836E-3</v>
-      </c>
-      <c r="D421">
-        <f t="shared" si="6"/>
-        <v>35.960071920143832</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52EC2250-5D34-B040-9FCC-DF20636C09BE}">
   <dimension ref="A1:H421"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -64824,7 +55598,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B91D78A-59F5-754B-92FA-07DC9469041F}">
   <dimension ref="A1:D421"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
